--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B427DA4A-78D9-4F2F-8EAF-6591E08982CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4497F99-A021-408B-A773-BB85CF071D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>kg</t>
   </si>
@@ -334,10 +334,25 @@
     <t>deg</t>
   </si>
   <si>
-    <t>SV-tail</t>
-  </si>
-  <si>
-    <t>0.2205 </t>
+    <t>θ</t>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V-tail</t>
+    </r>
+  </si>
+  <si>
+    <t>V-tail surface area</t>
   </si>
 </sst>
 </file>
@@ -345,10 +360,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +389,19 @@
     <font>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -412,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -430,43 +458,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -592,15 +583,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -610,72 +592,118 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,8 +736,8 @@
       <xdr:rowOff>55805</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1226820" cy="412100"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -798,7 +826,9 @@
                         <m:rPr>
                           <m:sty m:val="p"/>
                         </m:rPr>
-                        <a:rPr lang="el-GR" i="1"/>
+                        <a:rPr lang="el-GR" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
                         <m:t>ν</m:t>
                       </m:r>
                     </m:den>
@@ -828,7 +858,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -910,8 +940,8 @@
       <xdr:rowOff>278130</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1242060" cy="285912"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1021,23 +1051,11 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="+mn-lt"/>
-                              <a:ea typeface="+mn-ea"/>
-                              <a:cs typeface="+mn-cs"/>
-                            </a:rPr>
-                            <m:t>𝑉</m:t>
-                          </m:r>
-                          <m:r>
-                            <a:rPr lang="en-GB" sz="1200" b="0" i="1">
-                              <a:solidFill>
-                                <a:schemeClr val="tx1"/>
-                              </a:solidFill>
-                              <a:effectLst/>
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="+mn-ea"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
-                            <m:t>𝑠𝑡𝑎𝑙𝑙</m:t>
+                            <m:t>𝑉𝑠𝑡𝑎𝑙𝑙</m:t>
                           </m:r>
                         </m:e>
                         <m:sup>
@@ -1070,7 +1088,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="+mn-lt"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="+mn-ea"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -1084,7 +1102,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="+mn-lt"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="+mn-ea"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -1101,7 +1119,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1268,7 +1286,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>163830</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>72503</xdr:rowOff>
+      <xdr:rowOff>61297</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1365,8 +1383,8 @@
       <xdr:rowOff>188259</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="628185" cy="193515"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1452,7 +1470,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -1534,7 +1552,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>39990</xdr:rowOff>
+      <xdr:rowOff>30465</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1575,8 +1593,8 @@
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="978088" cy="346505"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -1618,6 +1636,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1788,7 +1807,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -1852,8 +1871,8 @@
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1008866" cy="346505"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -1895,6 +1914,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2065,7 +2085,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -2131,8 +2151,8 @@
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2179,8 +2199,8 @@
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1248098" cy="345672"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -2222,6 +2242,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2404,7 +2425,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -2468,8 +2489,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1237710" cy="349070"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -2511,6 +2532,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2681,7 +2703,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -2745,8 +2767,8 @@
       <xdr:rowOff>72390</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1493358" cy="344453"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -2965,7 +2987,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -3030,6 +3052,330 @@
                 <a:t>(√(𝑆_𝑉𝑇/𝑆_𝐻𝑇 )〗  )</a:t>
               </a:r>
               <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>185736</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2324100" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9644B7-D2C0-1695-F5FC-2683CDF57196}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7705725" y="6119811"/>
+              <a:ext cx="2324100" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑣𝑡𝑎𝑖𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>∗</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐𝑜𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜃</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑠𝑖𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜃</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑉𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9644B7-D2C0-1695-F5FC-2683CDF57196}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7705725" y="6119811"/>
+              <a:ext cx="2324100" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑣𝑡𝑎𝑖𝑙∗(〖𝑐𝑜𝑠〗^2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> 𝜃+〖𝑠𝑖𝑛〗^2 𝜃)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=𝑆_𝐻𝑇+𝑆_𝑉𝑇</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3358,9 +3704,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -3379,246 +3725,247 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="B1:H19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="4">
         <v>15</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="6"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="12"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12">
+      <c r="C10" s="7"/>
+      <c r="D10" s="4">
         <v>14</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="6"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="12">
+      <c r="C11" s="7"/>
+      <c r="D11" s="4">
         <v>24</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="6"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="4">
         <v>1.4</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16" t="s">
+      <c r="E12" s="4"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="2:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="12">
+      <c r="C13" s="7"/>
+      <c r="D13" s="4">
         <f>(D11*D14)/D15</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="6"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="2:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
+    <row r="14" spans="2:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="4">
         <v>0.3</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="6"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="4">
         <v>1.4399999999999999E-5</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16" t="s">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="12"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="4">
         <v>1.17</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="12"/>
     </row>
-    <row r="17" spans="2:8" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="2:8" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="8">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="6"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="2:8" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="2:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="9">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="6"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="12"/>
     </row>
-    <row r="19" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
+    <row r="19" spans="2:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="47" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="16" t="s">
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3629,248 +3976,254 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="B1:H20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" customWidth="1"/>
+    <col min="8" max="8" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="17" t="s">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>0.03</v>
       </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="24"/>
     </row>
-    <row r="10" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+    <row r="10" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="23">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="28"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
-    <row r="11" spans="2:8" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="39" t="s">
+    <row r="11" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="36">
         <f>(D9*D12*D13)/D10</f>
         <v>8.3220284660732544E-2</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="22" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="37">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="19"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="24"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="32">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="6"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
     </row>
-    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="41"/>
+    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
     </row>
-    <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+    <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="19">
         <v>0.5</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="25" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="26"/>
+      <c r="H15" s="20"/>
     </row>
-    <row r="16" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+    <row r="16" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="23">
         <v>1</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="28"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
     </row>
-    <row r="17" spans="2:8" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="39" t="s">
+    <row r="17" spans="2:8" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.13745584772370487</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="33"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
     </row>
-    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="34"/>
+    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="38"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
     </row>
-    <row r="19" spans="2:8" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="48"/>
-      <c r="C19" s="23" t="s">
+    <row r="19" spans="2:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="33">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="26"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51" t="s">
+    <row r="20" spans="2:8" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="C20" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="32">
+        <f>D17+D11</f>
+        <v>0.2206761323844374</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="33"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4497F99-A021-408B-A773-BB85CF071D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E96A58A-9758-43AD-A053-8AE727531577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="30435" yWindow="3150" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>kg</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Assumed average viscosity of the air at standard conditions between 10 and 15deg and SOF atmospheric pressure</t>
-  </si>
-  <si>
-    <t>m^2/s</t>
   </si>
   <si>
     <t>m</t>
@@ -164,9 +161,6 @@
     <t>aspect ratio</t>
   </si>
   <si>
-    <t>m^2</t>
-  </si>
-  <si>
     <t>mean wing chord</t>
   </si>
   <si>
@@ -220,21 +214,6 @@
     <t>moment arm to the VT from wing AC to tail AC</t>
   </si>
   <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VT</t>
-    </r>
-  </si>
-  <si>
     <t>area of the vertical tail</t>
   </si>
   <si>
@@ -354,6 +333,67 @@
   <si>
     <t>V-tail surface area</t>
   </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VT</t>
+    </r>
+  </si>
+  <si>
+    <t>Final Results</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/s</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -363,7 +403,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +447,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -440,7 +496,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -583,11 +639,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -662,31 +744,25 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -703,6 +779,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1552,7 +1640,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>30465</xdr:rowOff>
+      <xdr:rowOff>18559</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2152,7 +2240,7 @@
       <xdr:col>22</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:rowOff>136684</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3067,8 +3155,8 @@
       <xdr:rowOff>185736</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2324100" cy="177228"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -3110,6 +3198,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3302,7 +3391,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -3759,34 +3848,34 @@
     </row>
     <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="44" t="s">
+      <c r="C8" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="43" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="47" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4">
         <v>15</v>
@@ -3815,7 +3904,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="4">
@@ -3830,10 +3919,10 @@
     </row>
     <row r="12" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4">
         <v>1.4</v>
@@ -3841,13 +3930,13 @@
       <c r="E12" s="4"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="4">
@@ -3864,13 +3953,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4">
         <v>0.3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="4"/>
@@ -3881,13 +3970,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="4">
         <v>1.4399999999999999E-5</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10" t="s">
@@ -3900,7 +3989,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4">
         <v>1.17</v>
@@ -3910,60 +3999,60 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="2:8" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="48" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="8">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="2:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="D18" s="9">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="2:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>34</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
-      <c r="G19" s="51" t="s">
-        <v>39</v>
+      <c r="G19" s="49" t="s">
+        <v>37</v>
       </c>
       <c r="H19" s="15"/>
     </row>
@@ -3975,7 +4064,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
-  <dimension ref="B1:H20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -4009,34 +4098,34 @@
     </row>
     <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="44" t="s">
+      <c r="C8" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="43" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="23">
         <v>0.03</v>
@@ -4044,96 +4133,96 @@
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
       <c r="G9" s="30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="23">
         <v>1</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="46" t="s">
-        <v>45</v>
+      <c r="B11" s="44" t="s">
+        <v>60</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="36">
+        <v>43</v>
+      </c>
+      <c r="D11" s="34">
         <f>(D9*D12*D13)/D10</f>
         <v>8.3220284660732544E-2</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="11" t="s">
-        <v>47</v>
+      <c r="B12" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="37">
+        <v>45</v>
+      </c>
+      <c r="D12" s="35">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="H12" s="24"/>
     </row>
-    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="47" t="s">
-        <v>49</v>
+    <row r="13" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="32">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="48"/>
+        <v>59</v>
+      </c>
+      <c r="F13" s="46"/>
       <c r="G13" s="27"/>
       <c r="H13" s="28"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
     </row>
     <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D15" s="19">
         <v>0.5</v>
@@ -4141,91 +4230,98 @@
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H15" s="20"/>
     </row>
     <row r="16" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D16" s="23">
         <v>1</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="24"/>
     </row>
-    <row r="17" spans="2:8" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="25" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" s="32">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.13745584772370487</v>
       </c>
-      <c r="E17" s="35" t="s">
-        <v>35</v>
+      <c r="E17" s="27" t="s">
+        <v>59</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28"/>
     </row>
-    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="38"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="36"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="34" t="s">
-        <v>59</v>
+    <row r="19" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>56</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" s="33">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="2:8" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="25" t="s">
-        <v>60</v>
+    <row r="20" spans="1:8" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="53"/>
+      <c r="B20" s="51" t="s">
+        <v>57</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D20" s="32">
         <f>D17+D11</f>
         <v>0.2206761323844374</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A19:A20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E96A58A-9758-43AD-A053-8AE727531577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1273721-6F22-4F95-BD3E-593306A8D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30435" yWindow="3150" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
     <sheet name="Wing" sheetId="1" r:id="rId2"/>
     <sheet name="V-tail" sheetId="3" r:id="rId3"/>
+    <sheet name="Fuselage" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
   <si>
     <t>kg</t>
   </si>
@@ -43,9 +44,6 @@
     <t>MTOW</t>
   </si>
   <si>
-    <t>Vstall</t>
-  </si>
-  <si>
     <t>m/s</t>
   </si>
   <si>
@@ -61,9 +59,6 @@
     <t>kg/m³</t>
   </si>
   <si>
-    <t>Dependencies</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -101,9 +96,6 @@
   </si>
   <si>
     <t>𝑅𝑒 at cruse speed</t>
-  </si>
-  <si>
-    <t>Vcruise</t>
   </si>
   <si>
     <r>
@@ -167,10 +159,6 @@
     <t>wing area</t>
   </si>
   <si>
-    <t>(NACA2412)
-Take a look at the graphs on the right (Cl vs alpha)</t>
-  </si>
-  <si>
     <t>Efficient for the beginning
 Could be lowered to 8-9 later if the wingspan is too wide to be build</t>
   </si>
@@ -178,129 +166,24 @@
     <t>wing ref area</t>
   </si>
   <si>
-    <r>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VT</t>
-    </r>
-  </si>
-  <si>
     <t>Vertical tail volume coefficient</t>
   </si>
   <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VT</t>
-    </r>
-  </si>
-  <si>
     <t>moment arm to the VT from wing AC to tail AC</t>
   </si>
   <si>
     <t>area of the vertical tail</t>
   </si>
   <si>
-    <r>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-  </si>
-  <si>
     <t>wing span</t>
   </si>
   <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HT</t>
-    </r>
-  </si>
-  <si>
     <t>Horizontal tail volume coefficient</t>
   </si>
   <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HT</t>
-    </r>
-  </si>
-  <si>
     <t>moment arm to the HT from wing AC to tail AC</t>
   </si>
   <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HT</t>
-    </r>
-  </si>
-  <si>
     <t>area of the horizontal tail</t>
   </si>
   <si>
@@ -314,21 +197,6 @@
   </si>
   <si>
     <t>θ</t>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V-tail</t>
-    </r>
   </si>
   <si>
     <t>V-tail surface area</t>
@@ -347,22 +215,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VT</t>
     </r>
   </si>
   <si>
@@ -394,6 +246,321 @@
       <t>/s</t>
     </r>
   </si>
+  <si>
+    <t>Reynolds number at cruise speed</t>
+  </si>
+  <si>
+    <t>Approximate value</t>
+  </si>
+  <si>
+    <r>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cruise</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stall</t>
+    </r>
+  </si>
+  <si>
+    <t>NACA2412</t>
+  </si>
+  <si>
+    <t>NACA0009</t>
+  </si>
+  <si>
+    <r>
+      <t>(NACA2412)
+α</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>max</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≈ 15deg
+Take a look at the graphs on the right (Cl vs alpha)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V-tail</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+  </si>
+  <si>
+    <t>Aspect Ratio</t>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V-tail</t>
+    </r>
+  </si>
+  <si>
+    <t>V-tail span</t>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V-tail</t>
+    </r>
+  </si>
+  <si>
+    <t>V-tail chord</t>
+  </si>
+  <si>
+    <t>λ</t>
+  </si>
+  <si>
+    <t>No taper for the first model.</t>
+  </si>
+  <si>
+    <t>V-tail taper</t>
+  </si>
+  <si>
+    <t>Aspect ration is chosen such than smaller span is achieved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep angle </t>
+  </si>
+  <si>
+    <t>Λ</t>
+  </si>
+  <si>
+    <t>Negative sweep angle to begin with. Could be further increased later if needed.</t>
+  </si>
+  <si>
+    <t>Could be lowered</t>
+  </si>
+  <si>
+    <t>Aileron</t>
+  </si>
+  <si>
+    <t>Single Aileron span</t>
+  </si>
+  <si>
+    <t>Single Aileron chord</t>
+  </si>
+  <si>
+    <t>Aileron start outbound to inbound</t>
+  </si>
+  <si>
+    <t>This is chosen by the design. Could be lower.</t>
+  </si>
+  <si>
+    <t>Elevon</t>
+  </si>
+  <si>
+    <t>Single Elevon span</t>
+  </si>
+  <si>
+    <t>Single Elevon chord</t>
+  </si>
+  <si>
+    <t>Elevon start outbound to inbound</t>
+  </si>
+  <si>
+    <t>40percent of the V-tail chord.
+25-50 is the acceptable range.</t>
+  </si>
+  <si>
+    <t>Almost the whole V-tail surface</t>
+  </si>
 </sst>
 </file>
 
@@ -403,7 +570,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,13 +608,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,7 +617,7 @@
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -669,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -756,9 +916,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -768,13 +925,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -783,15 +934,70 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,7 +1024,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>277010</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>55805</xdr:rowOff>
@@ -1022,7 +1228,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>449580</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>278130</xdr:rowOff>
@@ -1365,16 +1571,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>320040</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>58728</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>163830</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>61297</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>692188</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1415,16 +1621,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>213360</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>594360</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>393550</xdr:rowOff>
+      <xdr:rowOff>167191</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1465,7 +1671,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>640976</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>188259</xdr:rowOff>
@@ -1624,6 +1830,50 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>486700</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>86282</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{688B29BA-C9C7-4D74-BE72-50141DD92836}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9324975" y="7067385"/>
+          <a:ext cx="5573050" cy="3363047"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1631,16 +1881,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>358140</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>18559</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190009</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1675,7 +1925,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -1953,7 +2203,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>388620</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
@@ -2231,16 +2481,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>273879</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>136684</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>231934</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2281,7 +2531,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -2571,7 +2821,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -2849,7 +3099,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>373380</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>72390</xdr:rowOff>
@@ -3149,7 +3399,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>185736</xdr:rowOff>
@@ -3472,6 +3722,55 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>503845</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69138</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B222B88-1AD5-DABE-CEDA-F40B445B33C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6065520" y="1188720"/>
+          <a:ext cx="6630325" cy="4001058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3793,17 +4092,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>9.8066499999999994</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3813,69 +4112,71 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
-  <dimension ref="B1:H19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="28.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>54</v>
+      </c>
       <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="50"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="C8" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>8</v>
-      </c>
       <c r="G8" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="44" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4">
         <v>15</v>
@@ -3884,179 +4185,258 @@
         <v>0</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B10" s="11" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="4">
         <v>14</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B11" s="11" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="4">
         <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4">
         <v>1.4</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="D13" s="4">
         <f>(D11*D14)/D15</f>
         <v>500000</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="2:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4">
         <v>0.3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4">
         <v>1.4399999999999999E-5</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D16" s="4">
         <v>1.17</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="2:8" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="48" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="45" t="s">
+        <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D17" s="8">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="2:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="48" t="s">
-        <v>30</v>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="45" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D18" s="9">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="45" t="s">
-        <v>32</v>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="43" t="s">
+        <v>29</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="15"/>
+      <c r="F19" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="75"/>
+      <c r="C21" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="68">
+        <f>D18/4</f>
+        <v>0.75679105362627686</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
+    </row>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="69"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="4">
+        <f>D14/4</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="70"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="73">
+        <f>0.1*D18</f>
+        <v>0.30271642145051075</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="64"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="64"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="64"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="64"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="64"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="64"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="64"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="64"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="64"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="64"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A21:A23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4064,265 +4444,403 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="36" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>55</v>
+      </c>
       <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="C8" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>8</v>
-      </c>
       <c r="G8" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>39</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="52" t="s">
+        <v>62</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D9" s="23">
         <v>0.03</v>
       </c>
       <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row r="10" spans="2:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>41</v>
+      <c r="F9" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24"/>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="52" t="s">
+        <v>63</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D10" s="23">
         <v>1</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
-    </row>
-    <row r="11" spans="2:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="44" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="24"/>
+    </row>
+    <row r="11" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="53" t="s">
+        <v>64</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D11" s="34">
         <f>(D9*D12*D13)/D10</f>
         <v>8.3220284660732544E-2</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
-        <v>44</v>
+      <c r="G11" s="24"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="53" t="s">
+        <v>65</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D12" s="35">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="24"/>
-    </row>
-    <row r="13" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
-        <v>46</v>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="51" t="s">
+        <v>61</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D13" s="32">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="36"/>
       <c r="C14" s="37"/>
-      <c r="D14" s="36"/>
       <c r="E14" s="36"/>
-      <c r="F14" s="38"/>
+      <c r="F14" s="36"/>
       <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D15" s="19">
         <v>0.5</v>
       </c>
       <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="20"/>
-    </row>
-    <row r="16" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="F15" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="21" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D16" s="23">
         <v>1</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="24"/>
-    </row>
-    <row r="17" spans="1:8" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="24"/>
+    </row>
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="25" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D17" s="32">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.13745584772370487</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="36"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-    </row>
-    <row r="19" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>56</v>
+    </row>
+    <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>45</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D19" s="33">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="20"/>
-    </row>
-    <row r="20" spans="1:8" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
-      <c r="B20" s="51" t="s">
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="49"/>
+      <c r="B20" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>58</v>
+      <c r="C20" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="D20" s="32">
         <f>D17+D11</f>
         <v>0.2206761323844374</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="G20" s="28"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="18">
+        <v>4</v>
+      </c>
+      <c r="E22" s="58"/>
+      <c r="F22" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="59"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="34">
+        <f>SQRT(D20*D22)</f>
+        <v>0.93952356518490243</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="34">
+        <f>D23/D22</f>
+        <v>0.23488089129622561</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="23">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="27">
+        <v>-10</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="75"/>
+      <c r="C28" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="68"/>
+      <c r="E28" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="59"/>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="74"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="56">
+        <f>0.4*D24</f>
+        <v>9.3952356518490251E-2</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="49"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="27">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="46"/>
+      <c r="G30" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A28:A30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1273721-6F22-4F95-BD3E-593306A8D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40E54B1-9374-4B45-A4DA-A091BDB4537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="96">
   <si>
     <t>kg</t>
   </si>
@@ -216,9 +216,6 @@
       </rPr>
       <t>2</t>
     </r>
-  </si>
-  <si>
-    <t>Final Results</t>
   </si>
   <si>
     <r>
@@ -560,6 +557,63 @@
   </si>
   <si>
     <t>Almost the whole V-tail surface</t>
+  </si>
+  <si>
+    <t>Wing</t>
+  </si>
+  <si>
+    <t>Vertical Tail</t>
+  </si>
+  <si>
+    <t>Horizontal Tail</t>
+  </si>
+  <si>
+    <t>V-Tail</t>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <t>Elevon spans across almost the whole V-tail surface</t>
   </si>
 </sst>
 </file>
@@ -656,7 +710,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -821,6 +875,97 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -845,14 +990,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -863,9 +1004,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -892,9 +1030,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -905,9 +1040,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -922,82 +1054,99 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1580,7 +1729,7 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>163830</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>692188</xdr:rowOff>
+      <xdr:rowOff>682663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1890,7 +2039,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>190009</xdr:rowOff>
+      <xdr:rowOff>180484</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2490,7 +2639,7 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>231934</xdr:rowOff>
+      <xdr:rowOff>12859</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4112,7 +4261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4126,8 +4275,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>54</v>
+      <c r="A1" s="36" t="s">
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
@@ -4149,47 +4298,51 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="50"/>
+      <c r="C7" s="36"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="53" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="44" t="s">
+      <c r="A9" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="38">
         <v>15</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="12"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="B10" s="11" t="s">
-        <v>53</v>
+      <c r="A10" s="56"/>
+      <c r="B10" s="48" t="s">
+        <v>52</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="4">
@@ -4199,11 +4352,12 @@
         <v>2</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="B11" s="11" t="s">
-        <v>52</v>
+      <c r="A11" s="56"/>
+      <c r="B11" s="48" t="s">
+        <v>51</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="4">
@@ -4213,10 +4367,11 @@
         <v>2</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="56"/>
+      <c r="B12" s="48" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -4227,16 +4382,17 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="12"/>
+        <v>55</v>
+      </c>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="56"/>
+      <c r="B13" s="48" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="4">
         <f>(D11*D14)/D15</f>
@@ -4244,12 +4400,13 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="56"/>
+      <c r="B14" s="48" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -4262,10 +4419,11 @@
         <v>18</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="56"/>
+      <c r="B15" s="48" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -4275,15 +4433,16 @@
         <v>1.4399999999999999E-5</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="56"/>
+      <c r="B16" s="48" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -4298,10 +4457,11 @@
       <c r="F16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="49" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -4315,10 +4475,11 @@
         <v>47</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="A18" s="56"/>
+      <c r="B18" s="49" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -4332,48 +4493,49 @@
         <v>18</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="43" t="s">
+      <c r="A19" s="57"/>
+      <c r="B19" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>10</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="46" t="s">
+      <c r="E19" s="13"/>
+      <c r="F19" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="14"/>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="46"/>
+      <c r="C21" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="68">
+      <c r="D21" s="42">
         <f>D18/4</f>
         <v>0.75679105362627686</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="65"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D22" s="4">
         <f>D14/4</f>
@@ -4383,59 +4545,30 @@
         <v>18</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="70"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="73">
+      <c r="A23" s="57"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="45">
         <f>0.1*D18</f>
         <v>0.30271642145051075</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="15"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="64"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="64"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="64"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="64"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="64"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="64"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="64"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="64"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="64"/>
+      <c r="F23" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A9:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4444,21 +4577,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="36" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="31" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>55</v>
+      <c r="A1" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
@@ -4480,355 +4613,377 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="53" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="A9" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="16">
         <v>0.03</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="30" t="s">
+      <c r="E9" s="16"/>
+      <c r="F9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="24"/>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="52" t="s">
+      <c r="A10" s="56"/>
+      <c r="B10" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="20">
+        <v>1</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="57"/>
+      <c r="B11" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="23">
-        <v>1</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="24"/>
-    </row>
-    <row r="11" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="70">
         <f>(D9*D12*D13)/D10</f>
         <v>8.3220284660732544E-2</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="65">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="24"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="28">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="A15" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="17">
         <v>0.5</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19" t="s">
+      <c r="E15" s="16"/>
+      <c r="F15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="22" t="s">
+      <c r="A16" s="56"/>
+      <c r="B16" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <v>1</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="24"/>
+      <c r="F16" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="31" t="s">
+      <c r="A17" s="57"/>
+      <c r="B17" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="28">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.13745584772370487</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="36"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="47" t="s">
+      <c r="A19" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="29">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="20"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="18"/>
     </row>
-    <row r="20" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="49"/>
-      <c r="B20" s="54" t="s">
-        <v>57</v>
+    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="59"/>
+      <c r="B20" s="71" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="72">
         <f>D17+D11</f>
         <v>0.2206761323844374</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="28"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="21"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="16" t="s">
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="59"/>
+      <c r="B21" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C21" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="20">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="59"/>
+      <c r="B22" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="18">
-        <v>4</v>
-      </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="59"/>
+      <c r="C22" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="30">
+        <f>SQRT(D20*D21)</f>
+        <v>0.93952356518490243</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="55" t="s">
+      <c r="A23" s="59"/>
+      <c r="B23" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="34">
-        <f>SQRT(D20*D22)</f>
-        <v>0.93952356518490243</v>
+      <c r="C23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="30">
+        <f>D22/D21</f>
+        <v>0.23488089129622561</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="55" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="59"/>
+      <c r="B24" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="34">
-        <f>D23/D22</f>
-        <v>0.23488089129622561</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="C24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="20">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="60"/>
+      <c r="B25" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="24">
+        <v>-10</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A27" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="47"/>
+      <c r="E27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="12"/>
+      <c r="F27" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="39"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="23">
+    <row r="28" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
+      <c r="A28" s="59"/>
+      <c r="B28" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="30">
+        <f>0.4*D23</f>
+        <v>9.3952356518490251E-2</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="60"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="24">
         <v>0</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="27">
-        <v>-10</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="15"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="75"/>
-      <c r="C28" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="68"/>
-      <c r="E28" s="58" t="s">
+      <c r="E29" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="59"/>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="74"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="56">
-        <f>0.4*D24</f>
-        <v>9.3952356518490251E-2</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="49"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="27">
-        <v>0</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="15"/>
+      <c r="F29" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A28:A30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A19:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40E54B1-9374-4B45-A4DA-A091BDB4537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874334E-40DB-44BE-A73E-C0DE62C9EC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
   <si>
     <t>kg</t>
   </si>
@@ -614,6 +614,31 @@
   </si>
   <si>
     <t>Elevon spans across almost the whole V-tail surface</t>
+  </si>
+  <si>
+    <t>Aircraft Performance lecture slide on the right.</t>
+  </si>
+  <si>
+    <t>Aerodynamic Center of the wing</t>
+  </si>
+  <si>
+    <r>
+      <t>AC</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+  </si>
+  <si>
+    <t>Around 25% of the wing chord from the wing tip. Could be calculated at a later stage when the preliminary design is done.</t>
   </si>
 </sst>
 </file>
@@ -974,7 +999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -991,7 +1016,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1077,31 +1101,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1146,6 +1148,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1981,16 +2007,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>171285</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>361785</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>486700</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>86282</xdr:rowOff>
+      <xdr:colOff>220000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>95807</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2013,8 +2039,332 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9324975" y="7067385"/>
+          <a:off x="9058275" y="8381835"/>
           <a:ext cx="5573050" cy="3363047"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>742950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>340641</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2834F5-F9D8-29DA-1825-DE761F7F57DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9229725" y="5324475"/>
+          <a:ext cx="3693441" cy="2771775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{688B08BC-995B-4362-E5FC-A128D600F8C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15621000" y="5448300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F526B9F3-4525-9140-61C9-43985D3A3E06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15011400" y="7117080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F3F33E-8AC4-DCFA-628B-902A5D259161}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15011400" y="7117080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>699412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>142978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4376B2A1-B747-AEE8-BFAC-F9580847DCB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18183225" y="5280937"/>
+          <a:ext cx="5048249" cy="2882091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8EF206B-D831-9E9E-DA95-771B1A8A2907}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15011400" y="5448300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>729438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>185642</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FF2FDF2-8722-E3CD-C1A9-E16A46B83A27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12973050" y="5310963"/>
+          <a:ext cx="5057774" cy="2894729"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2062,8 +2412,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10088880" y="396240"/>
-          <a:ext cx="3872097" cy="2935590"/>
+          <a:off x="9854565" y="392430"/>
+          <a:ext cx="3872097" cy="2921779"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3871,6 +4221,194 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2049" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34EC048A-AE5F-618D-5C8F-E6720EA6C52B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10706100" y="4168140"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2051" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF0A2B44-BD6F-28D1-8210-878032004166}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10687050" y="4143375"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2052" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951B3235-4606-C332-7BEE-8AE865C65F5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10096500" y="4168140"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>201030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>295275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4478376F-B1B0-8C9F-6AB3-189DA517B3B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10144125" y="3525255"/>
+          <a:ext cx="3724274" cy="2237370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4261,7 +4799,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4275,7 +4813,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -4298,50 +4836,50 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="36"/>
+      <c r="C7" s="35"/>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="49" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="37">
         <v>15</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A10" s="56"/>
-      <c r="B10" s="48" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="7"/>
@@ -4355,8 +4893,8 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="7"/>
@@ -4370,8 +4908,8 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
-      <c r="B12" s="48" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -4387,8 +4925,8 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
-      <c r="B13" s="48" t="s">
+      <c r="A13" s="66"/>
+      <c r="B13" s="39" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -4405,8 +4943,8 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="56"/>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="66"/>
+      <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -4422,8 +4960,8 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="48" t="s">
+      <c r="A15" s="66"/>
+      <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -4441,8 +4979,8 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="66"/>
+      <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -4460,8 +4998,8 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
-      <c r="B17" s="49" t="s">
+      <c r="A17" s="66"/>
+      <c r="B17" s="71" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -4478,8 +5016,8 @@
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="49" t="s">
+      <c r="A18" s="66"/>
+      <c r="B18" s="71" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -4495,80 +5033,102 @@
       <c r="F18" s="4"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="57"/>
-      <c r="B19" s="50" t="s">
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="66"/>
+      <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="4">
         <v>10</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="35" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
+    <row r="20" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="67"/>
+      <c r="B20" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="12">
+        <f>0.25*D14</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E20" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="74" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="41" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D22" s="41">
         <f>D18/4</f>
         <v>0.75679105362627686</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E22" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="56"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="6" t="s">
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="66"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D23" s="4">
         <f>D14/4</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="11"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="57"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44" t="s">
+    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="67"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D24" s="44">
         <f>0.1*D18</f>
         <v>0.30271642145051075</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E24" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F24" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="14"/>
+      <c r="G24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A9:A19"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A9:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4583,14 +5143,14 @@
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="30" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -4614,233 +5174,233 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="D8" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="49" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>0.03</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>1</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="57"/>
-      <c r="B11" s="37" t="s">
+      <c r="A11" s="67"/>
+      <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="59">
         <f>(D9*D12*D13)/D10</f>
         <v>8.3220284660732544E-2</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="25"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="54">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="57"/>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="25"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>0.5</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17" t="s">
+      <c r="E15" s="15"/>
+      <c r="F15" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="61" t="s">
+      <c r="A16" s="66"/>
+      <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="19">
         <v>1</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="57"/>
-      <c r="B17" s="37" t="s">
+      <c r="A17" s="67"/>
+      <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.13745584772370487</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="25"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="31"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="18"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
-      <c r="B20" s="71" t="s">
+      <c r="A20" s="69"/>
+      <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="61">
         <f>D17+D11</f>
         <v>0.2206761323844374</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="21"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
-      <c r="B21" s="73" t="s">
+      <c r="A21" s="69"/>
+      <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <v>4</v>
       </c>
       <c r="E21" s="4"/>
@@ -4850,14 +5410,14 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="71" t="s">
+      <c r="A22" s="69"/>
+      <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <f>SQRT(D20*D21)</f>
         <v>0.93952356518490243</v>
       </c>
@@ -4868,14 +5428,14 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
-      <c r="B23" s="71" t="s">
+      <c r="A23" s="69"/>
+      <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <f>D22/D21</f>
         <v>0.23488089129622561</v>
       </c>
@@ -4886,14 +5446,14 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="59"/>
-      <c r="B24" s="73" t="s">
+      <c r="A24" s="69"/>
+      <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="19">
         <v>0</v>
       </c>
       <c r="E24" s="4"/>
@@ -4903,57 +5463,57 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="60"/>
-      <c r="B25" s="75" t="s">
+      <c r="A25" s="70"/>
+      <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <v>-10</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="16" t="s">
+      <c r="D27" s="46"/>
+      <c r="E27" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="38" t="s">
+      <c r="F27" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="39"/>
+      <c r="G27" s="38"/>
     </row>
     <row r="28" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
-      <c r="A28" s="59"/>
-      <c r="B28" s="40" t="s">
+      <c r="A28" s="69"/>
+      <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="29">
         <f>0.4*D23</f>
         <v>9.3952356518490251E-2</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="10" t="s">
@@ -4962,21 +5522,21 @@
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="60"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="44" t="s">
+      <c r="A29" s="70"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>0</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874334E-40DB-44BE-A73E-C0DE62C9EC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47ADB889-0AD4-4C18-8138-B8966D0BDFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -2334,13 +2334,13 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>729438</xdr:rowOff>
+      <xdr:rowOff>700863</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>571499</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>185642</xdr:rowOff>
+      <xdr:rowOff>157067</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2363,7 +2363,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12973050" y="5310963"/>
+          <a:off x="12973050" y="5282388"/>
           <a:ext cx="5057774" cy="2894729"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47ADB889-0AD4-4C18-8138-B8966D0BDFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA68316-25DB-48FA-8138-51A2A436717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
     <sheet name="Wing" sheetId="1" r:id="rId2"/>
     <sheet name="V-tail" sheetId="3" r:id="rId3"/>
     <sheet name="Fuselage" sheetId="4" r:id="rId4"/>
+    <sheet name="Neutral point" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="117">
   <si>
     <t>kg</t>
   </si>
@@ -640,6 +641,105 @@
   <si>
     <t>Around 25% of the wing chord from the wing tip. Could be calculated at a later stage when the preliminary design is done.</t>
   </si>
+  <si>
+    <t>Fuselage</t>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>front</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aft</t>
+    </r>
+  </si>
+  <si>
+    <t>Front fuselage</t>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <t>Aft fuselage</t>
+  </si>
+  <si>
+    <t>estimated from the right picture (subject  to change)</t>
+  </si>
+  <si>
+    <t>Fuselage lenght</t>
+  </si>
+  <si>
+    <t>From moment lever arm from v-tail</t>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <t>Diameter of fuselage</t>
+  </si>
+  <si>
+    <t>from LxWxH (subject to change if too big)</t>
+  </si>
+  <si>
+    <t>Wing contribution</t>
+  </si>
+  <si>
+    <t>Position of Aerodynamic Center</t>
+  </si>
+  <si>
+    <t>Moment Coeff. Of the wing</t>
+  </si>
+  <si>
+    <t>Lift coeff. Depending on the angle of attack</t>
+  </si>
+  <si>
+    <t>polhamus formula</t>
+  </si>
 </sst>
 </file>
 
@@ -649,7 +749,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,6 +802,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -735,7 +842,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -995,11 +1102,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1149,6 +1328,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1167,11 +1351,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1471,7 +1690,13 @@
                         <a:rPr lang="en-GB" sz="1200" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>2∗</m:t>
+                        <m:t>2</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-GB" sz="1200" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>∗</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="en-GB" sz="1200" b="0" i="1">
@@ -3721,7 +3946,13 @@
                             <a:rPr lang="en-GB" sz="1100" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
-                            <m:t>−1</m:t>
+                            <m:t>−</m:t>
+                          </m:r>
+                          <m:r>
+                            <a:rPr lang="en-GB" sz="1100" i="1">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>1</m:t>
                           </m:r>
                         </m:sup>
                       </m:sSup>
@@ -4424,7 +4655,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>503845</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>69138</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4458,6 +4689,1845 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>320138</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>535727</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F5FC672-108B-448D-985A-A6D8456530A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9540338" y="190500"/>
+          <a:ext cx="6921189" cy="4371975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>120174</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88455</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="718026" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EDCDE1-0BA2-CDE2-4DDB-6AF0AD8E70FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="777399" y="2593530"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="+mn-lt"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="+mn-lt"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="+mn-lt"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="+mn-lt"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="+mn-lt"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EDCDE1-0BA2-CDE2-4DDB-6AF0AD8E70FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="777399" y="2593530"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑥 ̅</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝐴𝐶,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1975284" cy="351186"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00D935CC-4C27-78F0-2278-2BD5BE7C93F3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7124700" y="2519362"/>
+              <a:ext cx="1975284" cy="351186"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="bg-BG" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>0</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑊</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>+(</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐴𝐶</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑊</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟𝑜𝑜𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑊</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>)</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑀𝐴𝐶</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00D935CC-4C27-78F0-2278-2BD5BE7C93F3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7124700" y="2519362"/>
+              <a:ext cx="1975284" cy="351186"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̅_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐴𝐶,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=(𝑥_(0,𝑊)+(𝑛_(𝐴𝐶,𝑊)∗𝑐_(𝑟𝑜𝑜𝑡,𝑊)))/𝑐_𝑀𝐴𝐶 </a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="830740" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DE02C36-E9F2-6182-2BB2-7E1C9B780BB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4352925" y="2614612"/>
+              <a:ext cx="830740" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>25</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>%</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DE02C36-E9F2-6182-2BB2-7E1C9B780BB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4352925" y="2614612"/>
+              <a:ext cx="830740" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐴𝐶,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=25%</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="895350" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBCE2798-42CE-0BC0-6D2A-E1F227C4FC36}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="695325" y="2005012"/>
+              <a:ext cx="895350" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBCE2798-42CE-0BC0-6D2A-E1F227C4FC36}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="695325" y="2005012"/>
+              <a:ext cx="895350" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1479892" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A67F05-2B73-47BD-DCD9-F0453439C37F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7277100" y="2024062"/>
+              <a:ext cx="1479892" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐿</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>∗</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A67F05-2B73-47BD-DCD9-F0453439C37F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7277100" y="2024062"/>
+              <a:ext cx="1479892" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=−𝐶_(𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∗𝑥 ̅_(𝐴𝐶,𝑊)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360099" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69BFB39D-C44A-3CA3-60AB-399BD779004F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="923925" y="2481262"/>
+              <a:ext cx="360099" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐿</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69BFB39D-C44A-3CA3-60AB-399BD779004F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="923925" y="2481262"/>
+              <a:ext cx="360099" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>184350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>77572</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19764</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E43F4123-1600-4B68-6085-9DD864FDF715}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9582149" y="4613475"/>
+          <a:ext cx="7030823" cy="3654939"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>598713</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>53563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>159222</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>183083</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01C0A1A5-0C11-4AA4-C82C-F3C462A8C6A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16559892" y="434563"/>
+          <a:ext cx="6296044" cy="3408841"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>179343</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>566188</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="644857" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="TextBox 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ED666B2-4A0F-42F6-FF67-471E7BE3BCBC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="833669" y="2860471"/>
+              <a:ext cx="644857" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>tan</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>⁡(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="el-GR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Λ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>50</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>%</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="TextBox 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ED666B2-4A0F-42F6-FF67-471E7BE3BCBC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="833669" y="2860471"/>
+              <a:ext cx="644857" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>tan⁡(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="el-GR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>Λ</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(50%))</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4779,9 +6849,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -4800,19 +6870,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
@@ -4820,25 +6890,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -4858,11 +6928,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="66" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="40" t="s">
@@ -4877,8 +6947,8 @@
       <c r="F9" s="37"/>
       <c r="G9" s="38"/>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A10" s="66"/>
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="69"/>
       <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
@@ -4892,8 +6962,8 @@
       <c r="F10" s="4"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A11" s="66"/>
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="69"/>
       <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
@@ -4907,8 +6977,8 @@
       <c r="F11" s="4"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="66"/>
+    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="69"/>
       <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
@@ -4924,8 +6994,8 @@
       </c>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="66"/>
+    <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="69"/>
       <c r="B13" s="39" t="s">
         <v>19</v>
       </c>
@@ -4942,8 +7012,8 @@
       </c>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66"/>
+    <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="69"/>
       <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
@@ -4959,8 +7029,8 @@
       <c r="F14" s="4"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="69"/>
       <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
@@ -4978,8 +7048,8 @@
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="66"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
       <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
@@ -4997,9 +7067,9 @@
       </c>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66"/>
-      <c r="B17" s="71" t="s">
+    <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="69"/>
+      <c r="B17" s="65" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -5015,9 +7085,9 @@
       <c r="F17" s="4"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="66"/>
-      <c r="B18" s="71" t="s">
+    <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="69"/>
+      <c r="B18" s="65" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -5033,8 +7103,8 @@
       <c r="F18" s="4"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="66"/>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="69"/>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
@@ -5050,8 +7120,8 @@
       </c>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="67"/>
+    <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="70"/>
       <c r="B20" s="42" t="s">
         <v>98</v>
       </c>
@@ -5062,19 +7132,19 @@
         <f>0.25*D14</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E20" s="73" t="s">
+      <c r="E20" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="74" t="s">
+      <c r="G20" s="67" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="65" t="s">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="68" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="45"/>
@@ -5091,8 +7161,8 @@
       <c r="F22" s="37"/>
       <c r="G22" s="38"/>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="66"/>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="69"/>
       <c r="B23" s="39"/>
       <c r="C23" s="6" t="s">
         <v>80</v>
@@ -5107,8 +7177,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="67"/>
+    <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="70"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
         <v>81</v>
@@ -5138,18 +7208,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>54</v>
       </c>
@@ -5157,23 +7227,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -5193,8 +7263,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+    <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="58" t="s">
@@ -5212,8 +7282,8 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="66"/>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="69"/>
       <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
@@ -5221,7 +7291,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>18</v>
@@ -5231,8 +7301,8 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="67"/>
+    <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="70"/>
       <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
@@ -5241,7 +7311,7 @@
       </c>
       <c r="D11" s="59">
         <f>(D9*D12*D13)/D10</f>
-        <v>8.3220284660732544E-2</v>
+        <v>9.2466982956369487E-2</v>
       </c>
       <c r="E11" s="23" t="s">
         <v>47</v>
@@ -5249,7 +7319,7 @@
       <c r="F11" s="23"/>
       <c r="G11" s="24"/>
     </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B12" s="52" t="s">
         <v>64</v>
       </c>
@@ -5266,7 +7336,7 @@
       <c r="F12" s="56"/>
       <c r="G12" s="57"/>
     </row>
-    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
@@ -5283,15 +7353,15 @@
       <c r="F13" s="23"/>
       <c r="G13" s="24"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="30"/>
       <c r="C14" s="31"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="68" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="58" t="s">
@@ -5309,8 +7379,8 @@
       </c>
       <c r="G15" s="17"/>
     </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="66"/>
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
       <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
@@ -5318,7 +7388,7 @@
         <v>40</v>
       </c>
       <c r="D16" s="19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>18</v>
@@ -5328,8 +7398,8 @@
       </c>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="67"/>
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
       <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
@@ -5338,7 +7408,7 @@
       </c>
       <c r="D17" s="27">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
-        <v>0.13745584772370487</v>
+        <v>0.15272871969300542</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>47</v>
@@ -5346,7 +7416,7 @@
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="30"/>
       <c r="C18" s="32"/>
       <c r="D18" s="33"/>
@@ -5354,8 +7424,8 @@
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
     </row>
-    <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="68" t="s">
+    <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="71" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="63" t="s">
@@ -5374,8 +7444,8 @@
       <c r="F19" s="15"/>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="69"/>
+    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72"/>
       <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
@@ -5384,7 +7454,7 @@
       </c>
       <c r="D20" s="61">
         <f>D17+D11</f>
-        <v>0.2206761323844374</v>
+        <v>0.2451957026493749</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>47</v>
@@ -5392,8 +7462,8 @@
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="69"/>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="72"/>
       <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
@@ -5409,8 +7479,8 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
+    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="72"/>
       <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
@@ -5419,7 +7489,7 @@
       </c>
       <c r="D22" s="29">
         <f>SQRT(D20*D21)</f>
-        <v>0.93952356518490243</v>
+        <v>0.99034479379532236</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>18</v>
@@ -5427,8 +7497,8 @@
       <c r="F22" s="4"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="69"/>
+    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="72"/>
       <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
@@ -5437,7 +7507,7 @@
       </c>
       <c r="D23" s="29">
         <f>D22/D21</f>
-        <v>0.23488089129622561</v>
+        <v>0.24758619844883059</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>18</v>
@@ -5445,8 +7515,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="69"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="72"/>
       <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
@@ -5462,8 +7532,8 @@
       </c>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="70"/>
+    <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
       <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
@@ -5481,9 +7551,9 @@
       </c>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A27" s="68" t="s">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="71" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="45" t="s">
@@ -5501,8 +7571,8 @@
       </c>
       <c r="G27" s="38"/>
     </row>
-    <row r="28" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
-      <c r="A28" s="69"/>
+    <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="72"/>
       <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
@@ -5511,7 +7581,7 @@
       </c>
       <c r="D28" s="29">
         <f>0.4*D23</f>
-        <v>9.3952356518490251E-2</v>
+        <v>9.9034479379532248E-2</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>18</v>
@@ -5521,8 +7591,8 @@
       </c>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="70"/>
+    <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="73"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>86</v>
@@ -5552,9 +7622,513 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="35"/>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="30"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="30"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="30"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="19">
+        <f>1.5*Wing!D14</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="75"/>
+      <c r="B10" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="19">
+        <f>3*Wing!D14</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="76"/>
+      <c r="B11" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="29">
+        <f>D9+D10+Wing!D14</f>
+        <v>1.65</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="22"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="68"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="71"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="72"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="72"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="72"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="72"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A19:A25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1379866-2160-4925-834D-A41ED5331C38}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="35"/>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="30"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="30"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="30"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="86" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="81" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="89" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="90"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="19">
+        <f>(Fuselage!D9+Wing!$D$14*0.25)/Wing!$D$14</f>
+        <v>1.7499999999999998</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="90"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="90"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="29"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="90"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="87"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="68"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="71"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="72"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="72"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="72"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="72"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="72"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A8:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA68316-25DB-48FA-8138-51A2A436717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FECD7D6-3258-47D2-A1AF-00D033C89B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="119">
   <si>
     <t>kg</t>
   </si>
@@ -739,6 +739,12 @@
   </si>
   <si>
     <t>polhamus formula</t>
+  </si>
+  <si>
+    <t>50% of sweep</t>
+  </si>
+  <si>
+    <t>For Polhamus</t>
   </si>
 </sst>
 </file>
@@ -1333,33 +1339,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1379,9 +1358,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1389,7 +1365,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -1690,13 +1696,7 @@
                         <a:rPr lang="en-GB" sz="1200" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>2</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-GB" sz="1200" b="0" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>∗</m:t>
+                        <m:t>2∗</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="en-GB" sz="1200" b="0" i="1">
@@ -3946,13 +3946,7 @@
                             <a:rPr lang="en-GB" sz="1100" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
-                            <m:t>−</m:t>
-                          </m:r>
-                          <m:r>
-                            <a:rPr lang="en-GB" sz="1100" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                            </a:rPr>
-                            <m:t>1</m:t>
+                            <m:t>−1</m:t>
                           </m:r>
                         </m:sup>
                       </m:sSup>
@@ -4746,8 +4740,8 @@
       <xdr:rowOff>88455</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="718026" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -4789,6 +4783,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4813,7 +4808,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -4826,7 +4821,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -4842,7 +4837,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4854,7 +4849,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4866,7 +4861,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4882,7 +4877,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -4988,8 +4983,8 @@
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1975284" cy="351186"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -5031,6 +5026,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5122,13 +5118,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>0</m:t>
-                            </m:r>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>,</m:t>
+                              <m:t>0,</m:t>
                             </m:r>
                             <m:r>
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
@@ -5267,7 +5257,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -5355,8 +5345,8 @@
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="830740" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -5398,6 +5388,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5445,19 +5436,7 @@
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>25</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>%</m:t>
+                      <m:t>=25%</m:t>
                     </m:r>
                   </m:oMath>
                 </m:oMathPara>
@@ -5467,7 +5446,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -5555,8 +5534,8 @@
       <xdr:rowOff>90487</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="895350" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -5598,6 +5577,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5658,7 +5638,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -5748,8 +5728,8 @@
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1479892" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -5791,6 +5771,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5958,7 +5939,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -6067,8 +6048,8 @@
       <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="360099" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -6110,6 +6091,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6170,7 +6152,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -6348,8 +6330,8 @@
       <xdr:rowOff>566188</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="644857" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -6391,6 +6373,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6436,13 +6419,7 @@
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>50</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>%</m:t>
+                          <m:t>50%</m:t>
                         </m:r>
                       </m:sub>
                     </m:sSub>
@@ -6460,7 +6437,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -6929,7 +6906,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="80" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="66" t="s">
@@ -6948,7 +6925,7 @@
       <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="69"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
@@ -6963,7 +6940,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="69"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
@@ -6978,7 +6955,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="69"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
@@ -6995,7 +6972,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="39" t="s">
         <v>19</v>
       </c>
@@ -7013,7 +6990,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="69"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
@@ -7030,7 +7007,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="69"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
@@ -7049,7 +7026,7 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
@@ -7068,7 +7045,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="69"/>
+      <c r="A17" s="81"/>
       <c r="B17" s="65" t="s">
         <v>11</v>
       </c>
@@ -7086,7 +7063,7 @@
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69"/>
+      <c r="A18" s="81"/>
       <c r="B18" s="65" t="s">
         <v>27</v>
       </c>
@@ -7104,7 +7081,7 @@
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="69"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
@@ -7121,7 +7098,7 @@
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="70"/>
+      <c r="A20" s="82"/>
       <c r="B20" s="42" t="s">
         <v>98</v>
       </c>
@@ -7144,7 +7121,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="80" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="45"/>
@@ -7162,7 +7139,7 @@
       <c r="G22" s="38"/>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="39"/>
       <c r="C23" s="6" t="s">
         <v>80</v>
@@ -7178,7 +7155,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="70"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
         <v>81</v>
@@ -7264,7 +7241,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="80" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="58" t="s">
@@ -7283,7 +7260,7 @@
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="69"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
@@ -7302,7 +7279,7 @@
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="70"/>
+      <c r="A11" s="82"/>
       <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
@@ -7361,7 +7338,7 @@
       <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="80" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="58" t="s">
@@ -7380,7 +7357,7 @@
       <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
@@ -7399,7 +7376,7 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
+      <c r="A17" s="82"/>
       <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
@@ -7425,7 +7402,7 @@
       <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="83" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="63" t="s">
@@ -7445,7 +7422,7 @@
       <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
@@ -7463,7 +7440,7 @@
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
@@ -7480,7 +7457,7 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
@@ -7498,7 +7475,7 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="72"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
@@ -7516,7 +7493,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
@@ -7533,7 +7510,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
@@ -7553,7 +7530,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="83" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="45" t="s">
@@ -7572,7 +7549,7 @@
       <c r="G27" s="38"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="72"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
@@ -7592,7 +7569,7 @@
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>86</v>
@@ -7669,30 +7646,30 @@
       <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="80" t="s">
+      <c r="F8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="82" t="s">
+      <c r="G8" s="73" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="74" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -7705,14 +7682,14 @@
       <c r="E9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="68" t="s">
         <v>106</v>
       </c>
       <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="83" t="s">
+      <c r="A10" s="89"/>
+      <c r="B10" s="74" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -7731,8 +7708,8 @@
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="84" t="s">
+      <c r="A11" s="90"/>
+      <c r="B11" s="75" t="s">
         <v>104</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -7749,19 +7726,19 @@
       <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="76" t="s">
         <v>109</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="69">
         <v>0.3</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="68" t="s">
         <v>111</v>
       </c>
       <c r="G12" s="20"/>
@@ -7782,7 +7759,7 @@
       <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="68"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="58"/>
       <c r="C15" s="14"/>
       <c r="D15" s="16"/>
@@ -7791,7 +7768,7 @@
       <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="50"/>
       <c r="C16" s="18"/>
       <c r="D16" s="19"/>
@@ -7800,7 +7777,7 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
+      <c r="A17" s="82"/>
       <c r="B17" s="36"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -7817,7 +7794,7 @@
       <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="71"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="63"/>
       <c r="C19" s="14"/>
       <c r="D19" s="28"/>
@@ -7826,7 +7803,7 @@
       <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="60"/>
       <c r="C20" s="25"/>
       <c r="D20" s="61"/>
@@ -7835,7 +7812,7 @@
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="62"/>
       <c r="C21" s="18"/>
       <c r="D21" s="19"/>
@@ -7844,7 +7821,7 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="60"/>
       <c r="C22" s="18"/>
       <c r="D22" s="29"/>
@@ -7853,7 +7830,7 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="72"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="60"/>
       <c r="C23" s="18"/>
       <c r="D23" s="29"/>
@@ -7862,7 +7839,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="62"/>
       <c r="C24" s="18"/>
       <c r="D24" s="19"/>
@@ -7871,7 +7848,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="64"/>
       <c r="C25" s="26"/>
       <c r="D25" s="23"/>
@@ -7942,27 +7919,27 @@
       <c r="A8" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="81" t="s">
+      <c r="C8" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="89" t="s">
+      <c r="G8" s="79" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="90"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="65"/>
       <c r="C9" s="18" t="s">
         <v>113</v>
@@ -7972,11 +7949,11 @@
         <v>1.7499999999999998</v>
       </c>
       <c r="E9" s="19"/>
-      <c r="F9" s="77"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="90"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="65"/>
       <c r="C10" s="18" t="s">
         <v>114</v>
@@ -7987,7 +7964,7 @@
       <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="90"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="60"/>
       <c r="C11" s="18" t="s">
         <v>115</v>
@@ -8000,16 +7977,23 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="65"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="78"/>
+      <c r="C12" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" s="69">
+        <f>TAN(0)-((4/10)*(50/100))</f>
+        <v>-0.2</v>
+      </c>
       <c r="E12" s="19"/>
-      <c r="F12" s="77"/>
+      <c r="F12" s="68" t="s">
+        <v>118</v>
+      </c>
       <c r="G12" s="19"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="4"/>
       <c r="C13" s="25"/>
       <c r="D13" s="61"/>
@@ -8026,7 +8010,7 @@
       <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="68"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="58"/>
       <c r="C15" s="14"/>
       <c r="D15" s="16"/>
@@ -8035,7 +8019,7 @@
       <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="50"/>
       <c r="C16" s="18"/>
       <c r="D16" s="19"/>
@@ -8044,7 +8028,7 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
+      <c r="A17" s="82"/>
       <c r="B17" s="36"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -8061,7 +8045,7 @@
       <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="71"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="63"/>
       <c r="C19" s="14"/>
       <c r="D19" s="28"/>
@@ -8070,7 +8054,7 @@
       <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="60"/>
       <c r="C20" s="25"/>
       <c r="D20" s="61"/>
@@ -8079,7 +8063,7 @@
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="62"/>
       <c r="C21" s="18"/>
       <c r="D21" s="19"/>
@@ -8088,7 +8072,7 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="60"/>
       <c r="C22" s="18"/>
       <c r="D22" s="29"/>
@@ -8097,7 +8081,7 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="72"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="60"/>
       <c r="C23" s="18"/>
       <c r="D23" s="29"/>
@@ -8106,7 +8090,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="62"/>
       <c r="C24" s="18"/>
       <c r="D24" s="19"/>
@@ -8115,7 +8099,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="64"/>
       <c r="C25" s="26"/>
       <c r="D25" s="23"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FECD7D6-3258-47D2-A1AF-00D033C89B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2690223E-9399-4EBD-A92C-3541B7E635AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Wing" sheetId="1" r:id="rId2"/>
     <sheet name="V-tail" sheetId="3" r:id="rId3"/>
     <sheet name="Fuselage" sheetId="4" r:id="rId4"/>
-    <sheet name="Neutral point" sheetId="5" r:id="rId5"/>
+    <sheet name="Overall AC" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="120">
   <si>
     <t>kg</t>
   </si>
@@ -729,9 +729,6 @@
     <t>Wing contribution</t>
   </si>
   <si>
-    <t>Position of Aerodynamic Center</t>
-  </si>
-  <si>
     <t>Moment Coeff. Of the wing</t>
   </si>
   <si>
@@ -745,6 +742,12 @@
   </si>
   <si>
     <t>For Polhamus</t>
+  </si>
+  <si>
+    <t>Overall Aerodynamic Center</t>
+  </si>
+  <si>
+    <t>Non-dimensional position of  Wing Aerodynamic Center</t>
   </si>
 </sst>
 </file>
@@ -1383,12 +1386,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1396,6 +1393,12 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -4698,7 +4701,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>535727</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6288,7 +6291,7 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>159222</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>183083</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7666,7 +7669,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="86" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="74" t="s">
@@ -7688,7 +7691,7 @@
       <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="89"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="74" t="s">
         <v>102</v>
       </c>
@@ -7708,7 +7711,7 @@
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="75" t="s">
         <v>104</v>
       </c>
@@ -7882,7 +7885,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
+      <c r="A1" s="35" t="s">
+        <v>118</v>
+      </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
@@ -7916,7 +7921,7 @@
       <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="89" t="s">
         <v>112</v>
       </c>
       <c r="B8" s="78" t="s">
@@ -7938,14 +7943,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="87"/>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="90"/>
       <c r="B9" s="65"/>
       <c r="C9" s="18" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D9" s="19">
-        <f>(Fuselage!D9+Wing!$D$14*0.25)/Wing!$D$14</f>
+        <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
       <c r="E9" s="19"/>
@@ -7953,10 +7958,10 @@
       <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="87"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="65"/>
       <c r="C10" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -7964,23 +7969,23 @@
       <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="87"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="60"/>
       <c r="C11" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="87"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="65"/>
       <c r="C12" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="69">
         <f>TAN(0)-((4/10)*(50/100))</f>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G12" s="19"/>
     </row>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2690223E-9399-4EBD-A92C-3541B7E635AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321820D9-F77D-4EBE-AFD8-D515BF22E359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="V-tail" sheetId="3" r:id="rId3"/>
     <sheet name="Fuselage" sheetId="4" r:id="rId4"/>
     <sheet name="Overall AC" sheetId="5" r:id="rId5"/>
+    <sheet name="Weight and Balance" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
   <si>
     <t>kg</t>
   </si>
@@ -720,34 +721,347 @@
     </r>
   </si>
   <si>
-    <t>Diameter of fuselage</t>
-  </si>
-  <si>
     <t>from LxWxH (subject to change if too big)</t>
   </si>
   <si>
     <t>Wing contribution</t>
   </si>
   <si>
-    <t>Moment Coeff. Of the wing</t>
-  </si>
-  <si>
-    <t>Lift coeff. Depending on the angle of attack</t>
-  </si>
-  <si>
-    <t>polhamus formula</t>
-  </si>
-  <si>
     <t>50% of sweep</t>
   </si>
   <si>
-    <t>For Polhamus</t>
-  </si>
-  <si>
     <t>Overall Aerodynamic Center</t>
   </si>
   <si>
     <t>Non-dimensional position of  Wing Aerodynamic Center</t>
+  </si>
+  <si>
+    <t>Wing Moment coefficient slope</t>
+  </si>
+  <si>
+    <t>Max Diameter of fuselage</t>
+  </si>
+  <si>
+    <t>The change of pitching moment coefficient with angle of attack, caused by the wing, about your chosen aircraft reference point.</t>
+  </si>
+  <si>
+    <t>polhamus formula (reference on the right)</t>
+  </si>
+  <si>
+    <t>Lift coeff. Depending on the angle of attack of the wing</t>
+  </si>
+  <si>
+    <t>t/c</t>
+  </si>
+  <si>
+    <t>Relative thickness</t>
+  </si>
+  <si>
+    <t>Airfoilf/Pressure Influence</t>
+  </si>
+  <si>
+    <t>Compressibility effect</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Used for Airfoilf/Pressure Influence
+t - root overall thickness of the airfoil (12% of the chord for NACA2412)
+c - wing chord</t>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ϐ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Used in Polhamus formula
+Mach infinity (in the undisturbed airflow) is the Speed of the aircraft over the speed of the sound. - 0.07</t>
+  </si>
+  <si>
+    <r>
+      <t>rad</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <t>Used in Polhamus formula
+Rectangular wing - no sweep angle</t>
+  </si>
+  <si>
+    <t>Used in Polhamus formula
+Formula for t/c between 8% and 12%</t>
+  </si>
+  <si>
+    <t>Horizontal Tail contribution</t>
+  </si>
+  <si>
+    <t>Non-dimensional position of  Horizontal Tail  Aerodynamic Center</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0,HT</t>
+    </r>
+  </si>
+  <si>
+    <t>Distance from the beginning of the fuselage to the beginning of the Horizontal tail</t>
+  </si>
+  <si>
+    <t>Fuselage overall length minus chord length of the tail</t>
+  </si>
+  <si>
+    <t>Horizontal Tail Moment coefficient slope</t>
+  </si>
+  <si>
+    <t>Lift coeff. Depending on the angle of attack of the Horizontal Tail</t>
+  </si>
+  <si>
+    <t>The change of pitching moment coefficient with angle of attack, caused by the horizontal tail, about your chosen aircraft reference point.</t>
+  </si>
+  <si>
+    <t>Estimation (could be changed in the range from the slide on the right)</t>
+  </si>
+  <si>
+    <t>Dynamic pressure correction</t>
+  </si>
+  <si>
+    <t>Downwash correction</t>
+  </si>
+  <si>
+    <t>Area Ratio</t>
+  </si>
+  <si>
+    <t>Used in Polhamus formula
+Assumed Rectangular wing - no sweep angle</t>
+  </si>
+  <si>
+    <t>Fuselage contribution</t>
+  </si>
+  <si>
+    <t>Fuselage Moment coefficient slope</t>
+  </si>
+  <si>
+    <r>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <t>Fuselage width</t>
+  </si>
+  <si>
+    <t>Empirical pitching moment factor</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c,root,25</t>
+    </r>
+  </si>
+  <si>
+    <t>Position of root quarter chord</t>
+  </si>
+  <si>
+    <r>
+      <t>Estimated from the graph on the right using x</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fus</t>
+    </r>
+  </si>
+  <si>
+    <t>The maximum diameter of the fuselage is used here</t>
+  </si>
+  <si>
+    <t>Overall results</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AC</t>
+    </r>
+  </si>
+  <si>
+    <t>Non-dimensional position of  Overall Aerodynamic Center</t>
+  </si>
+  <si>
+    <t>Dimensional position of the overall Aerodynamic Center</t>
+  </si>
+  <si>
+    <t>CG should be abfront this point so that we achieve static stability</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>motors</t>
+  </si>
+  <si>
+    <t>propellers</t>
+  </si>
+  <si>
+    <t>ESCs</t>
+  </si>
+  <si>
+    <t>servos</t>
+  </si>
+  <si>
+    <t>flight controller</t>
+  </si>
+  <si>
+    <t>payload</t>
+  </si>
+  <si>
+    <t>landing gear</t>
+  </si>
+  <si>
+    <t>wing structure</t>
+  </si>
+  <si>
+    <t>fuselage structure</t>
+  </si>
+  <si>
+    <t>tail structure</t>
+  </si>
+  <si>
+    <t>wiring and mounts</t>
+  </si>
+  <si>
+    <t>Then calculate:</t>
+  </si>
+  <si>
+    <t>total mass</t>
+  </si>
+  <si>
+    <t>actual CG location</t>
+  </si>
+  <si>
+    <t>CG travel range</t>
+  </si>
+  <si>
+    <t>Estiamted Weight</t>
+  </si>
+  <si>
+    <t>Outer Dimensions</t>
   </si>
 </sst>
 </file>
@@ -758,7 +1072,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,8 +1132,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -850,8 +1180,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1115,34 +1451,40 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1160,15 +1502,36 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1179,15 +1542,28 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1348,26 +1724,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1386,20 +1742,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2617,7 +3011,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>180484</xdr:rowOff>
+      <xdr:rowOff>63942</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3216,8 +3610,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>12859</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>102506</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4604,7 +4998,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>104774</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
+      <xdr:rowOff>124946</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4644,16 +5038,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>243841</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>503845</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>69138</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>546913</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4676,8 +5070,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6065520" y="1188720"/>
-          <a:ext cx="6630325" cy="4001058"/>
+          <a:off x="9730741" y="114300"/>
+          <a:ext cx="4570272" cy="2773680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4694,15 +5088,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>320138</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>320139</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>67734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>535727</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>33867</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>380687</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4725,8 +5119,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9540338" y="190500"/>
-          <a:ext cx="6921189" cy="4371975"/>
+          <a:off x="9938272" y="1566334"/>
+          <a:ext cx="6419328" cy="3767353"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6237,94 +6631,6 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>361949</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>184350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>77572</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>19764</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E43F4123-1600-4B68-6085-9DD864FDF715}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9582149" y="4613475"/>
-          <a:ext cx="7030823" cy="3654939"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>598713</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>53563</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>159222</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>183083</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01C0A1A5-0C11-4AA4-C82C-F3C462A8C6A4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16559892" y="434563"/>
-          <a:ext cx="6296044" cy="3408841"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -6499,6 +6805,4326 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>_(50%))</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>118534</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>307298</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>203989</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C2CC9C-7B24-6652-5DA7-1DC31250C969}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16442267" y="1498602"/>
+          <a:ext cx="6284764" cy="3658387"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>154041</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>173122</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="718026" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEA8823E-79C5-4B79-9F55-E9AE37B5D08C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="831374" y="6057455"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEA8823E-79C5-4B79-9F55-E9AE37B5D08C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="831374" y="6057455"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑥 ̅_(𝐴𝐶,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>265642</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2138149" cy="351186"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="TextBox 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FAFDE84-E883-4D18-850D-3E0DD8ECA1CE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7386109" y="6051020"/>
+              <a:ext cx="2138149" cy="351186"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="bg-BG" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>0,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>+(</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐴𝐶</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟𝑜𝑜𝑡</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>)</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑀𝐴𝐶</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="TextBox 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FAFDE84-E883-4D18-850D-3E0DD8ECA1CE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7386109" y="6051020"/>
+              <a:ext cx="2138149" cy="351186"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̅_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐴𝐶,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=(𝑥_(0,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)+(𝑛_(𝐴𝐶,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)∗𝑐_(𝑟𝑜𝑜𝑡,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)))/𝑐_𝑀𝐴𝐶 </a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="871457" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B73E88E-CB59-4334-BAE4-120B1F44F5E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4607983" y="5993870"/>
+              <a:ext cx="871457" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=25%</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B73E88E-CB59-4334-BAE4-120B1F44F5E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4607983" y="5993870"/>
+              <a:ext cx="871457" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐴𝐶,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=25%</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>46566</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>259820</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="895350" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB57A903-C105-4FF8-B8AE-4F13D5224CA3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="723899" y="7795153"/>
+              <a:ext cx="895350" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB57A903-C105-4FF8-B8AE-4F13D5224CA3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="723899" y="7795153"/>
+              <a:ext cx="895350" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>37042</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177271</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2761269" cy="369588"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA03545-0480-4984-A9E5-7174B32BBDE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7157509" y="7712604"/>
+              <a:ext cx="2761269" cy="369588"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=−</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑞</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑞</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>∗</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝜕𝛼</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜕𝛼</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>∗</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑆</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑆</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟𝑒𝑓</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>′</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐿</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>∗</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑊</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA03545-0480-4984-A9E5-7174B32BBDE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7157509" y="7712604"/>
+              <a:ext cx="2761269" cy="369588"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=−</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑞_𝐻𝑇/𝑞∗〖</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜕𝛼〗_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜕𝛼</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∗𝑆_𝐻𝑇/𝑆_𝑟𝑒𝑓 )</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>〖𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>′</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>〗_(𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>∗𝑥 ̅_(𝐴𝐶,𝑊)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="445507" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="TextBox 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B309CB0D-B78D-4465-967F-553CF6B26967}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="944033" y="10532004"/>
+              <a:ext cx="445507" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>′</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐿</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐻𝑇</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="TextBox 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B309CB0D-B78D-4465-967F-553CF6B26967}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="944033" y="10532004"/>
+              <a:ext cx="445507" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>〖</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>′</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>〗_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>196276</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>117455</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="644857" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8F4025-D4F6-4053-A257-8D08F59FEB43}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="873609" y="9083655"/>
+              <a:ext cx="644857" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>tan</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>⁡(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="el-GR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Λ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>50%</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8F4025-D4F6-4053-A257-8D08F59FEB43}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="873609" y="9083655"/>
+              <a:ext cx="644857" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>tan⁡(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="el-GR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>Λ</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(50%))</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>355601</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>681428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>567653</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>201886</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47C39244-63D2-713E-B3D4-A93A164F0974}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9973734" y="6565761"/>
+          <a:ext cx="6308052" cy="3516725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>372534</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>110066</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="249107" cy="318421"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="TextBox 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37D2E609-EDED-3453-F59B-262C31FBB688}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1049867" y="8348133"/>
+              <a:ext cx="249107" cy="318421"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑞</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑞</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="TextBox 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37D2E609-EDED-3453-F59B-262C31FBB688}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1049867" y="8348133"/>
+              <a:ext cx="249107" cy="318421"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑞_𝐻𝑇/𝑞</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321734</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="338939" cy="320793"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77213E0-AE5B-2798-DF87-767FF743D6AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="999067" y="8847667"/>
+              <a:ext cx="338939" cy="320793"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝜕𝛼</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜕𝛼</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77213E0-AE5B-2798-DF87-767FF743D6AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="999067" y="8847667"/>
+              <a:ext cx="338939" cy="320793"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>〖</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜕𝛼〗_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐻𝑇/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜕𝛼</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>364067</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>93133</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="275525" cy="365678"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8474259-19C5-6C47-F996-64CE0D778AD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1041400" y="9381066"/>
+              <a:ext cx="275525" cy="365678"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑆</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑆</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟𝑒𝑓</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8474259-19C5-6C47-F996-64CE0D778AD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1041400" y="9381066"/>
+              <a:ext cx="275525" cy="365678"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆_𝐻𝑇/𝑆_𝑟𝑒𝑓 </a:t>
+              </a:r>
+              <a:endParaRPr lang="en-GB" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>67733</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>160867</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="895350" cy="182807"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="TextBox 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5A4FB95-4132-4894-BF27-8F85890B7308}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="745066" y="13148734"/>
+              <a:ext cx="895350" cy="182807"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓𝑢𝑠</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="TextBox 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5A4FB95-4132-4894-BF27-8F85890B7308}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="745066" y="13148734"/>
+              <a:ext cx="895350" cy="182807"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑓𝑢𝑠</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>237068</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>452204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>198319</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>395554</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E914BEC6-EEA1-5483-8747-DABDA9FF0FFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10210801" y="12517204"/>
+          <a:ext cx="5447651" cy="2940550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>347134</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>67733</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1960152" cy="402611"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="TextBox 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7728635E-8C6D-45A6-A421-6941025058ED}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7467601" y="13055600"/>
+              <a:ext cx="1960152" cy="402611"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="bg-BG" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐶</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑀</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛼</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓𝑢𝑠</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>45∗</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑘</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑓𝑢𝑠</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                        <m:sSubSup>
+                          <m:sSubSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑤</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑓𝑢𝑠</m:t>
+                            </m:r>
+                          </m:sub>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSubSup>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑙</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑓𝑢𝑠</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑐</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑀𝐴𝐶</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑆</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟𝑒𝑓</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="TextBox 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7728635E-8C6D-45A6-A421-6941025058ED}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7467601" y="13055600"/>
+              <a:ext cx="1960152" cy="402611"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛼,</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑓𝑢𝑠</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="bg-BG" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>45∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑓𝑢𝑠∗𝑤_𝑓𝑢𝑠^2∗𝑙_𝑓𝑢𝑠</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>)/(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑐</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑀𝐴𝐶∗𝑆_𝑟𝑒𝑓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> )</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>143933</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>245533</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>238902</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>59266</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4326404-6D80-F8DF-FCCE-FEF2D5E12D9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10117666" y="15722600"/>
+          <a:ext cx="5581369" cy="3175000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>118533</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="718026" cy="176651"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="TextBox 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C62E548-CA12-4676-9288-77D9329AF3AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="795866" y="15189200"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="TextBox 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C62E548-CA12-4676-9288-77D9329AF3AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="795866" y="15189200"/>
+              <a:ext cx="718026" cy="176651"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑥 ̅_𝐴𝐶</a:t>
+              </a:r>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>321733</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>110067</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1955800" cy="364267"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="33" name="TextBox 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB7F621F-FB65-461F-A15D-07C03ACCC0CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7442200" y="15163800"/>
+              <a:ext cx="1955800" cy="364267"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝐴𝐶</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐶</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑀</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝛼</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑊</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>−</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐶</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑀</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝛼</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑓𝑢𝑠</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐶</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑀</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝛼</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐶</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐿</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝛼</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝑊</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐶</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐿</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝛼</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>,</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-GB" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="tx1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>𝐻𝑇</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="bg-BG" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="33" name="TextBox 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB7F621F-FB65-461F-A15D-07C03ACCC0CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7442200" y="15163800"/>
+              <a:ext cx="1955800" cy="364267"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑥 ̅_𝐴𝐶</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>=(𝐶_(𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)−𝐶_(𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝛼,𝑓𝑢𝑠</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)+𝐶_(𝑀</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝛼,𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>))/(𝐶_(𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝛼,𝑊</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)+𝐶_(𝐿</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝛼,𝐻𝑇</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>) )</a:t>
               </a:r>
               <a:endParaRPr lang="bg-BG" sz="1100"/>
             </a:p>
@@ -6829,9 +11455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -6850,19 +11476,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
@@ -6870,25 +11496,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="35"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -6908,8 +11534,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="70" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="66" t="s">
@@ -6927,8 +11553,8 @@
       <c r="F9" s="37"/>
       <c r="G9" s="38"/>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="81"/>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A10" s="71"/>
       <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
@@ -6942,8 +11568,8 @@
       <c r="F10" s="4"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="81"/>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A11" s="71"/>
       <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
@@ -6957,8 +11583,8 @@
       <c r="F11" s="4"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="81"/>
+    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="71"/>
       <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
@@ -6974,8 +11600,8 @@
       </c>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="81"/>
+    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="71"/>
       <c r="B13" s="39" t="s">
         <v>19</v>
       </c>
@@ -6992,8 +11618,8 @@
       </c>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="81"/>
+    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="71"/>
       <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
@@ -7009,8 +11635,8 @@
       <c r="F14" s="4"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="81"/>
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="71"/>
       <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
@@ -7028,8 +11654,8 @@
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="71"/>
       <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
@@ -7047,8 +11673,8 @@
       </c>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81"/>
+    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="71"/>
       <c r="B17" s="65" t="s">
         <v>11</v>
       </c>
@@ -7065,8 +11691,8 @@
       <c r="F17" s="4"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="81"/>
+    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="71"/>
       <c r="B18" s="65" t="s">
         <v>27</v>
       </c>
@@ -7083,8 +11709,8 @@
       <c r="F18" s="4"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="81"/>
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="71"/>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
@@ -7100,8 +11726,8 @@
       </c>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="82"/>
+    <row r="20" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="72"/>
       <c r="B20" s="42" t="s">
         <v>98</v>
       </c>
@@ -7122,9 +11748,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="80" t="s">
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="70" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="45"/>
@@ -7141,8 +11767,8 @@
       <c r="F22" s="37"/>
       <c r="G22" s="38"/>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="81"/>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="71"/>
       <c r="B23" s="39"/>
       <c r="C23" s="6" t="s">
         <v>80</v>
@@ -7157,8 +11783,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="72"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
         <v>81</v>
@@ -7188,18 +11814,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="30" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>54</v>
       </c>
@@ -7207,23 +11833,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -7243,8 +11869,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
+    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="70" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="58" t="s">
@@ -7262,8 +11888,8 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="81"/>
+    <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="71"/>
       <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
@@ -7281,8 +11907,8 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
+    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="72"/>
       <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
@@ -7299,7 +11925,7 @@
       <c r="F11" s="23"/>
       <c r="G11" s="24"/>
     </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="52" t="s">
         <v>64</v>
       </c>
@@ -7316,7 +11942,7 @@
       <c r="F12" s="56"/>
       <c r="G12" s="57"/>
     </row>
-    <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
@@ -7333,15 +11959,15 @@
       <c r="F13" s="23"/>
       <c r="G13" s="24"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="30"/>
       <c r="C14" s="31"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="80" t="s">
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="70" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="58" t="s">
@@ -7359,8 +11985,8 @@
       </c>
       <c r="G15" s="17"/>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="71"/>
       <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
@@ -7378,8 +12004,8 @@
       </c>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="72"/>
       <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
@@ -7396,7 +12022,7 @@
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="30"/>
       <c r="C18" s="32"/>
       <c r="D18" s="33"/>
@@ -7404,8 +12030,8 @@
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
     </row>
-    <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+    <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="63" t="s">
@@ -7424,8 +12050,8 @@
       <c r="F19" s="15"/>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
+    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="74"/>
       <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
@@ -7442,8 +12068,8 @@
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="74"/>
       <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
@@ -7459,8 +12085,8 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="74"/>
       <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
@@ -7477,8 +12103,8 @@
       <c r="F22" s="4"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="74"/>
       <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
@@ -7495,8 +12121,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="74"/>
       <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
@@ -7512,8 +12138,8 @@
       </c>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
+    <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="75"/>
       <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
@@ -7531,9 +12157,9 @@
       </c>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="83" t="s">
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A27" s="73" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="45" t="s">
@@ -7551,8 +12177,8 @@
       </c>
       <c r="G27" s="38"/>
     </row>
-    <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="84"/>
+    <row r="28" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
+      <c r="A28" s="74"/>
       <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
@@ -7571,8 +12197,8 @@
       </c>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="85"/>
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="75"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>86</v>
@@ -7602,97 +12228,98 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="35"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="30"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="30"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D5" s="30"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D6" s="30"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D7" s="30"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="70" t="s">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="99"/>
+      <c r="B8" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="96" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="86" t="s">
+    <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="55">
         <f>1.5*Wing!D14</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="F9" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="57"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="87"/>
-      <c r="B10" s="74" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="82"/>
+      <c r="B10" s="50" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -7710,9 +12337,9 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="75" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="82"/>
+      <c r="B11" s="79" t="s">
         <v>104</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -7728,142 +12355,36 @@
       <c r="F11" s="19"/>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="76" t="s">
+    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="83"/>
+      <c r="B12" s="98" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="69">
-        <v>0.3</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="24"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="22"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="80"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-    </row>
-    <row r="19" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17"/>
-    </row>
-    <row r="20" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="11"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="11"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="13"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A19:A25"/>
+  <mergeCells count="1">
+    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7872,253 +12393,694 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1379866-2160-4925-834D-A41ED5331C38}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="30"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="30"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D5" s="30"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D6" s="30"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D7" s="30"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="78" t="s">
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="84"/>
+      <c r="B8" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="86" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="90"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="19">
+    <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="15">
         <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="19"/>
+      <c r="E9" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="90"/>
-      <c r="B10" s="65"/>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="82"/>
+      <c r="B10" s="78"/>
       <c r="C10" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+        <v>115</v>
+      </c>
+      <c r="D10" s="69">
+        <f>-D11*D9</f>
+        <v>-9.6764591226254897</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>129</v>
+      </c>
       <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="90"/>
-      <c r="B11" s="60"/>
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="82"/>
+      <c r="B11" s="79"/>
       <c r="C11" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19" t="s">
-        <v>115</v>
+        <v>119</v>
+      </c>
+      <c r="D11" s="69">
+        <f>(2*(22/7)*Wing!D19)/(2+(SQRT((Wing!D19^2)*('Overall AC'!D13)/'Overall AC'!D14+4)))</f>
+        <v>5.529405212928852</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
-      <c r="B12" s="65"/>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="82"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" s="69">
-        <f>TAN(0)-((4/10)*(50/100))</f>
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="19"/>
-      <c r="F12" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="19"/>
+      <c r="F12" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="82"/>
+      <c r="B13" s="87" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="61">
+        <f>1-(0.07)^2</f>
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="82"/>
+      <c r="B14" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="69">
+        <f>(1+0.75*D15)^2</f>
+        <v>1.1881000000000002</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="80"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+    <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="83"/>
+      <c r="B15" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="88">
+        <f>(0.12*0.3)/0.3</f>
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
+    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="77"/>
+      <c r="C17" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="28">
+        <f>(D18+(0.25*'V-tail'!D23))/'V-tail'!D23</f>
+        <v>5.9143456312893408</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="82"/>
+      <c r="B18" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="69">
+        <f>Fuselage!D11-'V-tail'!D23</f>
+        <v>1.4024138015511693</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17"/>
+    <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="82"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="69">
+        <f>-(D20*D21*D22)*D23*D17</f>
+        <v>-2.5300219037859915</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="82"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="69">
+        <v>0.9</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>140</v>
+      </c>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11"/>
+    <row r="21" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="82"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="69">
+        <v>0.7</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="11"/>
+    <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="82"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="69">
+        <f>'V-tail'!D17/Wing!D17</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="11"/>
+    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="82"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="69">
+        <f>(2*(22/7)*'V-tail'!D21)/(2+(SQRT(('V-tail'!D21^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
+        <v>4.0740680719180196</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="11"/>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="82"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="69">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="13"/>
+    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="82"/>
+      <c r="B25" s="87" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="61">
+        <f>1-(0.07)^2</f>
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="E25" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="82"/>
+      <c r="B26" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="69">
+        <f>(1+0.75*D27)^2</f>
+        <v>1.1881000000000002</v>
+      </c>
+      <c r="E26" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="83"/>
+      <c r="B27" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="88">
+        <f>(0.12*0.248)/0.248</f>
+        <v>0.12</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="77"/>
+      <c r="C29" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="89">
+        <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
+        <v>0.20412193386970173</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A30" s="82"/>
+      <c r="B30" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
+      <c r="A31" s="82"/>
+      <c r="B31" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="9">
+        <f>Fuselage!D12</f>
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A32" s="82"/>
+      <c r="B32" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="9">
+        <f>D33/Fuselage!D11</f>
+        <v>0.31818181818181812</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="1:7" ht="30" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="83"/>
+      <c r="B33" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="12">
+        <f>Fuselage!D9+Wing!D14*0.25</f>
+        <v>0.52499999999999991</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="90" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="77"/>
+      <c r="C35" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="89">
+        <f>(D10-D29+D19)/D11+D23</f>
+        <v>1.8295946643148437</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+    </row>
+    <row r="36" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="91"/>
+      <c r="B36" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="92">
+        <f>D35*0.3</f>
+        <v>0.54887839929445315</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A8:A12"/>
+  <mergeCells count="4">
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A17:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
+  <dimension ref="B2:D20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="100" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="100" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="100"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="100" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="100" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="100" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321820D9-F77D-4EBE-AFD8-D515BF22E359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B9F9BB-205D-438B-809A-CBCDED3938AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -1724,6 +1724,44 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1742,15 +1780,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1760,40 +1789,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6866,8 +6866,8 @@
       <xdr:rowOff>173122</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="718026" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -7003,7 +7003,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -7098,8 +7098,8 @@
       <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2138149" cy="351186"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -7372,7 +7372,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -7503,8 +7503,8 @@
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="871457" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -7604,7 +7604,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -7699,8 +7699,8 @@
       <xdr:rowOff>259820</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="895350" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -7803,7 +7803,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -7901,8 +7901,8 @@
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2761269" cy="369588"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -8295,7 +8295,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -8462,8 +8462,8 @@
       <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="445507" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -8572,7 +8572,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -8682,8 +8682,8 @@
       <xdr:rowOff>117455</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="644857" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -8789,7 +8789,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -8910,8 +8910,8 @@
       <xdr:rowOff>110066</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="249107" cy="318421"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -8953,6 +8953,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9011,7 +9012,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -9075,8 +9076,8 @@
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="338939" cy="320793"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -9118,6 +9119,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9178,7 +9180,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -9262,8 +9264,8 @@
       <xdr:rowOff>93133</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="275525" cy="365678"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -9305,6 +9307,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9382,7 +9385,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -9446,8 +9449,8 @@
       <xdr:rowOff>160867</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="895350" cy="182807"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -9550,7 +9553,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -9692,8 +9695,8 @@
       <xdr:rowOff>67733</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1960152" cy="402611"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -9972,7 +9975,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -10180,8 +10183,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="718026" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -10293,7 +10296,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -10364,8 +10367,8 @@
       <xdr:rowOff>110067</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1955800" cy="364267"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -10939,7 +10942,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -11455,9 +11458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -11476,19 +11479,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
@@ -11496,25 +11499,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -11534,8 +11537,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="70" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="90" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="66" t="s">
@@ -11553,8 +11556,8 @@
       <c r="F9" s="37"/>
       <c r="G9" s="38"/>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A10" s="71"/>
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="91"/>
       <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
@@ -11568,8 +11571,8 @@
       <c r="F10" s="4"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A11" s="71"/>
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="91"/>
       <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
@@ -11583,8 +11586,8 @@
       <c r="F11" s="4"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
+    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="91"/>
       <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
@@ -11600,9 +11603,9 @@
       </c>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="39" t="s">
+    <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="91"/>
+      <c r="B13" s="65" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -11618,8 +11621,8 @@
       </c>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
+    <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="91"/>
       <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
@@ -11635,8 +11638,8 @@
       <c r="F14" s="4"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="91"/>
       <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
@@ -11654,8 +11657,8 @@
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="91"/>
       <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
@@ -11673,8 +11676,8 @@
       </c>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="71"/>
+    <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="91"/>
       <c r="B17" s="65" t="s">
         <v>11</v>
       </c>
@@ -11691,8 +11694,8 @@
       <c r="F17" s="4"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="71"/>
+    <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="91"/>
       <c r="B18" s="65" t="s">
         <v>27</v>
       </c>
@@ -11709,8 +11712,8 @@
       <c r="F18" s="4"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="71"/>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="91"/>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
@@ -11726,9 +11729,9 @@
       </c>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="72"/>
-      <c r="B20" s="42" t="s">
+    <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="92"/>
+      <c r="B20" s="65" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="43" t="s">
@@ -11748,9 +11751,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="70" t="s">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="90" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="45"/>
@@ -11767,8 +11770,8 @@
       <c r="F22" s="37"/>
       <c r="G22" s="38"/>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="71"/>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="91"/>
       <c r="B23" s="39"/>
       <c r="C23" s="6" t="s">
         <v>80</v>
@@ -11783,8 +11786,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="72"/>
+    <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="92"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
         <v>81</v>
@@ -11814,18 +11817,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>54</v>
       </c>
@@ -11833,23 +11836,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
@@ -11869,8 +11872,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="70" t="s">
+    <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="90" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="58" t="s">
@@ -11888,8 +11891,8 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
+    <row r="10" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91"/>
       <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
@@ -11907,8 +11910,8 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="72"/>
+    <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="92"/>
       <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
@@ -11925,7 +11928,7 @@
       <c r="F11" s="23"/>
       <c r="G11" s="24"/>
     </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B12" s="52" t="s">
         <v>64</v>
       </c>
@@ -11942,7 +11945,7 @@
       <c r="F12" s="56"/>
       <c r="G12" s="57"/>
     </row>
-    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
@@ -11959,15 +11962,15 @@
       <c r="F13" s="23"/>
       <c r="G13" s="24"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="30"/>
       <c r="C14" s="31"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="70" t="s">
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="90" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="58" t="s">
@@ -11985,8 +11988,8 @@
       </c>
       <c r="G15" s="17"/>
     </row>
-    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="91"/>
       <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
@@ -12004,8 +12007,8 @@
       </c>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="72"/>
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="92"/>
       <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
@@ -12022,7 +12025,7 @@
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="30"/>
       <c r="C18" s="32"/>
       <c r="D18" s="33"/>
@@ -12030,8 +12033,8 @@
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
     </row>
-    <row r="19" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
+    <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="93" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="63" t="s">
@@ -12050,8 +12053,8 @@
       <c r="F19" s="15"/>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="74"/>
+    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="94"/>
       <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
@@ -12068,8 +12071,8 @@
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="74"/>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="94"/>
       <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
@@ -12085,8 +12088,8 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="74"/>
+    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="94"/>
       <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
@@ -12103,8 +12106,8 @@
       <c r="F22" s="4"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="74"/>
+    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="94"/>
       <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
@@ -12121,8 +12124,8 @@
       <c r="F23" s="4"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="74"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="94"/>
       <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
@@ -12138,8 +12141,8 @@
       </c>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="75"/>
+    <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="95"/>
       <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
@@ -12157,9 +12160,9 @@
       </c>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A27" s="73" t="s">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="93" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="45" t="s">
@@ -12177,8 +12180,8 @@
       </c>
       <c r="G27" s="38"/>
     </row>
-    <row r="28" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
-      <c r="A28" s="74"/>
+    <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="94"/>
       <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
@@ -12197,8 +12200,8 @@
       </c>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="75"/>
+    <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="95"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>86</v>
@@ -12229,77 +12232,77 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="30"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="30"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D5" s="30"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="30"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="30"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="99"/>
-      <c r="B8" s="94" t="s">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="88"/>
+      <c r="B8" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="F8" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="96" t="s">
+      <c r="G8" s="85" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="81" t="s">
+    <row r="9" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="96" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="86" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="53" t="s">
@@ -12317,8 +12320,8 @@
       </c>
       <c r="G9" s="57"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="97"/>
       <c r="B10" s="50" t="s">
         <v>102</v>
       </c>
@@ -12337,9 +12340,9 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
-      <c r="B11" s="79" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="97"/>
+      <c r="B11" s="73" t="s">
         <v>104</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -12355,26 +12358,26 @@
       <c r="F11" s="19"/>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="83"/>
-      <c r="B12" s="98" t="s">
+    <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="98"/>
+      <c r="B12" s="87" t="s">
         <v>109</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="79">
         <v>0.3</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="93" t="s">
+      <c r="F12" s="82" t="s">
         <v>110</v>
       </c>
       <c r="G12" s="24"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="30"/>
       <c r="C13" s="31"/>
       <c r="D13" s="30"/>
@@ -12394,18 +12397,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1379866-2160-4925-834D-A41ED5331C38}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="41.5546875" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>113</v>
       </c>
@@ -12414,36 +12417,36 @@
       </c>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="30"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="30"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D5" s="30"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="30"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="30"/>
     </row>
-    <row r="8" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84"/>
-      <c r="B8" s="85" t="s">
+    <row r="8" spans="1:7" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="76" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="51" t="s">
@@ -12458,15 +12461,15 @@
       <c r="F8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="77" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="81" t="s">
+    <row r="9" spans="1:7" ht="85.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="77"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="14" t="s">
         <v>114</v>
       </c>
@@ -12480,9 +12483,9 @@
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
-      <c r="B10" s="78"/>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="97"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="18" t="s">
         <v>115</v>
       </c>
@@ -12496,9 +12499,9 @@
       <c r="F10" s="19"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
-      <c r="B11" s="79"/>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="97"/>
+      <c r="B11" s="73"/>
       <c r="C11" s="18" t="s">
         <v>119</v>
       </c>
@@ -12516,9 +12519,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
-      <c r="B12" s="78"/>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="97"/>
+      <c r="B12" s="72"/>
       <c r="C12" s="18" t="s">
         <v>112</v>
       </c>
@@ -12531,9 +12534,9 @@
       </c>
       <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
-      <c r="B13" s="87" t="s">
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="97"/>
+      <c r="B13" s="78" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="25" t="s">
@@ -12551,9 +12554,9 @@
       </c>
       <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
-      <c r="B14" s="78" t="s">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="97"/>
+      <c r="B14" s="72" t="s">
         <v>126</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -12571,15 +12574,15 @@
       </c>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="83"/>
-      <c r="B15" s="80" t="s">
+    <row r="15" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="98"/>
+      <c r="B15" s="74" t="s">
         <v>120</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="88">
+      <c r="D15" s="79">
         <f>(0.12*0.3)/0.3</f>
         <v>0.12</v>
       </c>
@@ -12591,7 +12594,7 @@
       </c>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="30"/>
       <c r="C16" s="31"/>
       <c r="D16" s="30"/>
@@ -12599,11 +12602,11 @@
       <c r="F16" s="30"/>
       <c r="G16" s="30"/>
     </row>
-    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
+    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="14" t="s">
         <v>133</v>
       </c>
@@ -12617,9 +12620,9 @@
       <c r="F17" s="16"/>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
-      <c r="B18" s="79" t="s">
+    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="97"/>
+      <c r="B18" s="73" t="s">
         <v>134</v>
       </c>
       <c r="C18" s="18" t="s">
@@ -12637,9 +12640,9 @@
       </c>
       <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
-      <c r="B19" s="78"/>
+    <row r="19" spans="1:7" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="97"/>
+      <c r="B19" s="72"/>
       <c r="C19" s="18" t="s">
         <v>137</v>
       </c>
@@ -12653,9 +12656,9 @@
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
-      <c r="B20" s="78"/>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="97"/>
+      <c r="B20" s="72"/>
       <c r="C20" s="18" t="s">
         <v>141</v>
       </c>
@@ -12670,9 +12673,9 @@
       </c>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
-      <c r="B21" s="78"/>
+    <row r="21" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="97"/>
+      <c r="B21" s="72"/>
       <c r="C21" s="18" t="s">
         <v>142</v>
       </c>
@@ -12685,9 +12688,9 @@
       </c>
       <c r="G21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
-      <c r="B22" s="78"/>
+    <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="97"/>
+      <c r="B22" s="72"/>
       <c r="C22" s="18" t="s">
         <v>143</v>
       </c>
@@ -12701,9 +12704,9 @@
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
     </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="82"/>
-      <c r="B23" s="79"/>
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="97"/>
+      <c r="B23" s="73"/>
       <c r="C23" s="18" t="s">
         <v>138</v>
       </c>
@@ -12721,9 +12724,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
-      <c r="B24" s="78"/>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="97"/>
+      <c r="B24" s="72"/>
       <c r="C24" s="18" t="s">
         <v>112</v>
       </c>
@@ -12736,9 +12739,9 @@
       </c>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="82"/>
-      <c r="B25" s="87" t="s">
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="97"/>
+      <c r="B25" s="78" t="s">
         <v>127</v>
       </c>
       <c r="C25" s="25" t="s">
@@ -12756,9 +12759,9 @@
       </c>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="82"/>
-      <c r="B26" s="78" t="s">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="97"/>
+      <c r="B26" s="72" t="s">
         <v>126</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -12776,15 +12779,15 @@
       </c>
       <c r="G26" s="20"/>
     </row>
-    <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="83"/>
-      <c r="B27" s="80" t="s">
+    <row r="27" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="98"/>
+      <c r="B27" s="74" t="s">
         <v>120</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="88">
+      <c r="D27" s="79">
         <f>(0.12*0.248)/0.248</f>
         <v>0.12</v>
       </c>
@@ -12796,16 +12799,16 @@
       </c>
       <c r="G27" s="24"/>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="81" t="s">
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="77"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="89">
+      <c r="D29" s="80">
         <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
         <v>0.20412193386970173</v>
       </c>
@@ -12815,9 +12818,9 @@
       <c r="F29" s="37"/>
       <c r="G29" s="38"/>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.35">
-      <c r="A30" s="82"/>
-      <c r="B30" s="78" t="s">
+    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="A30" s="97"/>
+      <c r="B30" s="72" t="s">
         <v>147</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -12834,9 +12837,9 @@
       </c>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="1:7" ht="29.4" x14ac:dyDescent="0.35">
-      <c r="A31" s="82"/>
-      <c r="B31" s="78" t="s">
+    <row r="31" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="97"/>
+      <c r="B31" s="72" t="s">
         <v>148</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -12854,9 +12857,9 @@
       </c>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A32" s="82"/>
-      <c r="B32" s="78" t="s">
+    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A32" s="97"/>
+      <c r="B32" s="72" t="s">
         <v>151</v>
       </c>
       <c r="C32" s="7"/>
@@ -12870,9 +12873,9 @@
       <c r="F32" s="4"/>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="1:7" ht="30" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="83"/>
-      <c r="B33" s="80" t="s">
+    <row r="33" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="98"/>
+      <c r="B33" s="74" t="s">
         <v>152</v>
       </c>
       <c r="C33" s="43" t="s">
@@ -12888,16 +12891,16 @@
       <c r="F33" s="12"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="90" t="s">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="99" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="77"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="89">
+      <c r="D35" s="80">
         <f>(D10-D29+D19)/D11+D23</f>
         <v>1.8295946643148437</v>
       </c>
@@ -12907,15 +12910,15 @@
       <c r="F35" s="37"/>
       <c r="G35" s="38"/>
     </row>
-    <row r="36" spans="1:7" ht="44.4" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="91"/>
-      <c r="B36" s="80" t="s">
+    <row r="36" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="100"/>
+      <c r="B36" s="74" t="s">
         <v>157</v>
       </c>
       <c r="C36" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="92">
+      <c r="D36" s="81">
         <f>D35*0.3</f>
         <v>0.54887839929445315</v>
       </c>
@@ -12942,14 +12945,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
   <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
         <v>177</v>
@@ -12958,123 +12961,123 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="100" t="s">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="89" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="100" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="89" t="s">
         <v>162</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="100" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="89" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="100" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="89" t="s">
         <v>164</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="100" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="89" t="s">
         <v>165</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="100" t="s">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="89" t="s">
         <v>166</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="100" t="s">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="89" t="s">
         <v>167</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="100" t="s">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="89" t="s">
         <v>168</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="100" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="89" t="s">
         <v>169</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="100" t="s">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="89" t="s">
         <v>170</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="100" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="89" t="s">
         <v>171</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="100" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="89" t="s">
         <v>172</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>173</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="100"/>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="89"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="100" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="89" t="s">
         <v>174</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="100" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="89" t="s">
         <v>175</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="100" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="89" t="s">
         <v>176</v>
       </c>
       <c r="C20" s="4"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B9F9BB-205D-438B-809A-CBCDED3938AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E1E84C-7BDC-4408-9FC3-3CE0D7028582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="191">
   <si>
     <t>kg</t>
   </si>
@@ -721,9 +721,6 @@
     </r>
   </si>
   <si>
-    <t>from LxWxH (subject to change if too big)</t>
-  </si>
-  <si>
     <t>Wing contribution</t>
   </si>
   <si>
@@ -1058,10 +1055,96 @@
     <t>CG travel range</t>
   </si>
   <si>
-    <t>Estiamted Weight</t>
-  </si>
-  <si>
-    <t>Outer Dimensions</t>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>front</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 1.5 x wing chord</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 3 x wing chord</t>
+    </r>
+  </si>
+  <si>
+    <t>from max cargo dimensions
+(subject to change if too big)</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Estimated Weight (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model assumed </t>
+  </si>
+  <si>
+    <t>Turnigy BoltX LiHV 6S 10500mAh 22.8V 80C LiPo Battery Pack w/XT90</t>
+  </si>
+  <si>
+    <t>BrotherHobby Avenger 3120 Motors 500KV FPV Drone Motor</t>
+  </si>
+  <si>
+    <t>Φ37.5</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>22inch</t>
+  </si>
+  <si>
+    <t>FLAME 80A 12S V2.0 Multi-Rotor UAVs ESC</t>
+  </si>
+  <si>
+    <t>Fixed</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1232,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1186,8 +1269,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1559,11 +1654,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1759,9 +1932,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1795,6 +1965,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5047,7 +5276,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>546913</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6634,13 +6863,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>179343</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>566188</xdr:rowOff>
+      <xdr:colOff>158176</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>121688</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="644857" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -6654,7 +6883,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="833669" y="2860471"/>
+              <a:off x="814343" y="3868188"/>
               <a:ext cx="644857" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6746,7 +6975,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -6760,7 +6989,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="833669" y="2860471"/>
+              <a:off x="814343" y="3868188"/>
               <a:ext cx="644857" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6788,6 +7017,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -11137,6 +11367,55 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>159003</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>426819</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B7FBB58-2B84-B60A-B919-40159FB0E04A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9324975" y="159003"/>
+          <a:ext cx="5313144" cy="4498721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11538,7 +11817,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="89" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="66" t="s">
@@ -11557,7 +11836,7 @@
       <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="91"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="39" t="s">
         <v>52</v>
       </c>
@@ -11572,7 +11851,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="91"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="39" t="s">
         <v>51</v>
       </c>
@@ -11587,7 +11866,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="39" t="s">
         <v>20</v>
       </c>
@@ -11604,7 +11883,7 @@
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
+      <c r="A13" s="90"/>
       <c r="B13" s="65" t="s">
         <v>19</v>
       </c>
@@ -11622,7 +11901,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="91"/>
+      <c r="A14" s="90"/>
       <c r="B14" s="39" t="s">
         <v>15</v>
       </c>
@@ -11639,7 +11918,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="91"/>
+      <c r="A15" s="90"/>
       <c r="B15" s="39" t="s">
         <v>16</v>
       </c>
@@ -11658,7 +11937,7 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="91"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="39" t="s">
         <v>5</v>
       </c>
@@ -11677,7 +11956,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="91"/>
+      <c r="A17" s="90"/>
       <c r="B17" s="65" t="s">
         <v>11</v>
       </c>
@@ -11695,7 +11974,7 @@
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="91"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="65" t="s">
         <v>27</v>
       </c>
@@ -11713,7 +11992,7 @@
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="91"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
@@ -11730,7 +12009,7 @@
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="92"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="65" t="s">
         <v>98</v>
       </c>
@@ -11753,7 +12032,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="89" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="45"/>
@@ -11771,7 +12050,7 @@
       <c r="G22" s="38"/>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="39"/>
       <c r="C23" s="6" t="s">
         <v>80</v>
@@ -11787,7 +12066,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
         <v>81</v>
@@ -11873,7 +12152,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="89" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="58" t="s">
@@ -11892,7 +12171,7 @@
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
@@ -11911,7 +12190,7 @@
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="36" t="s">
         <v>63</v>
       </c>
@@ -11970,7 +12249,7 @@
       <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="89" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="58" t="s">
@@ -11989,7 +12268,7 @@
       <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="91"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="50" t="s">
         <v>58</v>
       </c>
@@ -12008,7 +12287,7 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="92"/>
+      <c r="A17" s="91"/>
       <c r="B17" s="36" t="s">
         <v>59</v>
       </c>
@@ -12034,7 +12313,7 @@
       <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="93" t="s">
+      <c r="A19" s="92" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="63" t="s">
@@ -12054,7 +12333,7 @@
       <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="94"/>
+      <c r="A20" s="93"/>
       <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
@@ -12072,7 +12351,7 @@
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="94"/>
+      <c r="A21" s="93"/>
       <c r="B21" s="62" t="s">
         <v>29</v>
       </c>
@@ -12089,7 +12368,7 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="94"/>
+      <c r="A22" s="93"/>
       <c r="B22" s="60" t="s">
         <v>66</v>
       </c>
@@ -12107,7 +12386,7 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="94"/>
+      <c r="A23" s="93"/>
       <c r="B23" s="60" t="s">
         <v>68</v>
       </c>
@@ -12125,7 +12404,7 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="94"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="62" t="s">
         <v>70</v>
       </c>
@@ -12142,7 +12421,7 @@
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="95"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="64" t="s">
         <v>75</v>
       </c>
@@ -12162,7 +12441,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="92" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="45" t="s">
@@ -12181,7 +12460,7 @@
       <c r="G27" s="38"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="39" t="s">
         <v>94</v>
       </c>
@@ -12201,7 +12480,7 @@
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="95"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>86</v>
@@ -12299,7 +12578,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="95" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="86" t="s">
@@ -12318,10 +12597,12 @@
       <c r="F9" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="57"/>
+      <c r="G9" s="57" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="97"/>
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="96"/>
       <c r="B10" s="50" t="s">
         <v>102</v>
       </c>
@@ -12338,10 +12619,12 @@
       <c r="F10" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="97"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="73" t="s">
         <v>104</v>
       </c>
@@ -12359,12 +12642,12 @@
       <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="87" t="s">
         <v>109</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="79">
         <v>0.3</v>
@@ -12373,7 +12656,7 @@
         <v>18</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="G12" s="24"/>
     </row>
@@ -12410,7 +12693,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
@@ -12466,131 +12749,131 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="85.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
-        <v>111</v>
+      <c r="A9" s="95" t="s">
+        <v>110</v>
       </c>
       <c r="B9" s="71"/>
       <c r="C9" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="15">
         <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="97"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="72"/>
       <c r="C10" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" s="69">
         <f>-D11*D9</f>
         <v>-9.6764591226254897</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="97"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="73"/>
       <c r="C11" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" s="69">
         <f>(2*(22/7)*Wing!D19)/(2+(SQRT((Wing!D19^2)*('Overall AC'!D13)/'Overall AC'!D14+4)))</f>
         <v>5.529405212928852</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F11" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>117</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="72"/>
       <c r="C12" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="69">
         <v>0</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="97"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" s="61">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
       <c r="E13" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="97"/>
+      <c r="A14" s="96"/>
       <c r="B14" s="72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14" s="69">
         <f>(1+0.75*D15)^2</f>
         <v>1.1881000000000002</v>
       </c>
       <c r="E14" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="98"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="22" t="s">
         <v>120</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>121</v>
       </c>
       <c r="D15" s="79">
         <f>(0.12*0.3)/0.3</f>
         <v>0.12</v>
       </c>
       <c r="E15" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>124</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>125</v>
       </c>
       <c r="G15" s="24"/>
     </row>
@@ -12603,30 +12886,30 @@
       <c r="G16" s="30"/>
     </row>
     <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="96" t="s">
-        <v>132</v>
+      <c r="A17" s="95" t="s">
+        <v>131</v>
       </c>
       <c r="B17" s="71"/>
       <c r="C17" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="28">
         <f>(D18+(0.25*'V-tail'!D23))/'V-tail'!D23</f>
         <v>5.9143456312893408</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="97"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>134</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>135</v>
       </c>
       <c r="D18" s="69">
         <f>Fuselage!D11-'V-tail'!D23</f>
@@ -12636,214 +12919,214 @@
         <v>18</v>
       </c>
       <c r="F18" s="68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="97"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="72"/>
       <c r="C19" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D19" s="69">
         <f>-(D20*D21*D22)*D23*D17</f>
         <v>-2.5300219037859915</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="97"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="72"/>
       <c r="C20" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20" s="69">
         <v>0.9</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F20" s="68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="97"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="72"/>
       <c r="C21" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="69">
         <v>0.7</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="97"/>
+      <c r="A22" s="96"/>
       <c r="B22" s="72"/>
       <c r="C22" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D22" s="69">
         <f>'V-tail'!D17/Wing!D17</f>
         <v>0.16666666666666669</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="97"/>
+      <c r="A23" s="96"/>
       <c r="B23" s="73"/>
       <c r="C23" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D23" s="69">
         <f>(2*(22/7)*'V-tail'!D21)/(2+(SQRT(('V-tail'!D21^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
         <v>4.0740680719180196</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="97"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="72"/>
       <c r="C24" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24" s="69">
         <v>0</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="97"/>
+      <c r="A25" s="96"/>
       <c r="B25" s="78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D25" s="61">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="97"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D26" s="69">
         <f>(1+0.75*D27)^2</f>
         <v>1.1881000000000002</v>
       </c>
       <c r="E26" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="98"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>120</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>121</v>
       </c>
       <c r="D27" s="79">
         <f>(0.12*0.248)/0.248</f>
         <v>0.12</v>
       </c>
       <c r="E27" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="26" t="s">
         <v>124</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>125</v>
       </c>
       <c r="G27" s="24"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="96" t="s">
-        <v>145</v>
+      <c r="A29" s="95" t="s">
+        <v>144</v>
       </c>
       <c r="B29" s="71"/>
       <c r="C29" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29" s="80">
         <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
         <v>0.20412193386970173</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F29" s="37"/>
       <c r="G29" s="38"/>
     </row>
     <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.35">
-      <c r="A30" s="97"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="72" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D30" s="4">
         <v>0.01</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G30" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="97"/>
+      <c r="A31" s="96"/>
       <c r="B31" s="72" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="D31" s="9">
         <f>Fuselage!D12</f>
@@ -12853,14 +13136,14 @@
         <v>18</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="97"/>
+      <c r="A32" s="96"/>
       <c r="B32" s="72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="9">
@@ -12868,18 +13151,18 @@
         <v>0.31818181818181812</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="98"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" s="43" t="s">
         <v>152</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>153</v>
       </c>
       <c r="D33" s="12">
         <f>Fuselage!D9+Wing!D14*0.25</f>
@@ -12893,30 +13176,30 @@
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="99" t="s">
-        <v>156</v>
+      <c r="A35" s="98" t="s">
+        <v>155</v>
       </c>
       <c r="B35" s="71"/>
       <c r="C35" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D35" s="80">
         <f>(D10-D29+D19)/D11+D23</f>
         <v>1.8295946643148437</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="38"/>
     </row>
     <row r="36" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="100"/>
+      <c r="A36" s="99"/>
       <c r="B36" s="74" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D36" s="81">
         <f>D35*0.3</f>
@@ -12926,7 +13209,7 @@
         <v>18</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G36" s="13"/>
     </row>
@@ -12944,146 +13227,301 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="113" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>178</v>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="129" t="s">
+        <v>190</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="89" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="130" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="103"/>
+      <c r="C4" s="108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="117" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="102" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="118" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="108" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="123" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="104" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="109">
+        <v>1150</v>
+      </c>
+      <c r="D5" s="119">
+        <v>66</v>
+      </c>
+      <c r="E5" s="101">
+        <v>48</v>
+      </c>
+      <c r="F5" s="120">
+        <v>175</v>
+      </c>
+      <c r="G5" s="114">
+        <v>2</v>
+      </c>
+      <c r="H5" s="124" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="C6" s="111">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="D6" s="121">
+        <v>53.2</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="116"/>
+      <c r="G6" s="110">
+        <v>4</v>
+      </c>
+      <c r="H6" s="125" t="s">
+        <v>185</v>
+      </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="89" t="s">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="105" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C7" s="111">
+        <v>180</v>
+      </c>
+      <c r="D7" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="107"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="110">
+        <v>4</v>
+      </c>
+      <c r="H7" s="125"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="105" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C8" s="111">
+        <v>110</v>
+      </c>
+      <c r="D8" s="121">
+        <v>19.5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="F8" s="11">
+        <v>84</v>
+      </c>
+      <c r="G8" s="110">
+        <v>4</v>
+      </c>
+      <c r="H8" s="125" t="s">
+        <v>189</v>
+      </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="89" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="125"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="89" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="105" t="s">
         <v>165</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="110">
+        <v>1</v>
+      </c>
+      <c r="H10" s="125"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="89" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C11" s="111">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="121"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="110">
+        <v>1</v>
+      </c>
+      <c r="H11" s="125"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="89" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="125"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="89" t="s">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="105" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="110">
+        <v>1</v>
+      </c>
+      <c r="H13" s="125"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="89" t="s">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="110">
+        <v>1</v>
+      </c>
+      <c r="H14" s="125"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="89" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="110">
+        <v>1</v>
+      </c>
+      <c r="H15" s="125"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="89" t="s">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="105" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="125"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="89" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="105"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="125"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="105" t="s">
         <v>172</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="125"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="105"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="125"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="125"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="89"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="105" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="111"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="125"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="89" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="89" t="s">
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="89" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="126"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E1E84C-7BDC-4408-9FC3-3CE0D7028582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894EE9DD-AAE0-4A07-8EF3-9232A7F81AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="199">
   <si>
     <t>kg</t>
   </si>
@@ -697,9 +697,6 @@
     <t>Aft fuselage</t>
   </si>
   <si>
-    <t>estimated from the right picture (subject  to change)</t>
-  </si>
-  <si>
     <t>Fuselage lenght</t>
   </si>
   <si>
@@ -1031,22 +1028,7 @@
     <t>landing gear</t>
   </si>
   <si>
-    <t>wing structure</t>
-  </si>
-  <si>
-    <t>fuselage structure</t>
-  </si>
-  <si>
-    <t>tail structure</t>
-  </si>
-  <si>
     <t>wiring and mounts</t>
-  </si>
-  <si>
-    <t>Then calculate:</t>
-  </si>
-  <si>
-    <t>total mass</t>
   </si>
   <si>
     <t>actual CG location</t>
@@ -1145,6 +1127,72 @@
   </si>
   <si>
     <t>Fixed</t>
+  </si>
+  <si>
+    <t>CF structure</t>
+  </si>
+  <si>
+    <t>Result Weight (g)</t>
+  </si>
+  <si>
+    <t>wing structure PLA</t>
+  </si>
+  <si>
+    <t>fuselage structure PLA</t>
+  </si>
+  <si>
+    <t>tail structure PLA</t>
+  </si>
+  <si>
+    <t>Total mass</t>
+  </si>
+  <si>
+    <t>5-10% from AC</t>
+  </si>
+  <si>
+    <t>From SOLIDWORKS, can be exported</t>
+  </si>
+  <si>
+    <t>Aft Diameter of fuselage</t>
+  </si>
+  <si>
+    <t>Most aft diameter of fuselage</t>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aftfus</t>
+    </r>
+  </si>
+  <si>
+    <t>Estimated from the right picture (subject  to change)</t>
+  </si>
+  <si>
+    <t>Horizontal tail wing span</t>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HT</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1282,7 +1330,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1644,17 +1692,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1732,180 +1769,116 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
@@ -1915,23 +1888,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1965,65 +1968,192 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2911,7 +3041,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>340641</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>88106</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3099,7 +3229,7 @@
       <xdr:col>30</xdr:col>
       <xdr:colOff>285749</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>142978</xdr:rowOff>
+      <xdr:rowOff>154884</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3191,7 +3321,7 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>571499</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>157067</xdr:rowOff>
+      <xdr:rowOff>168973</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3839,8 +3969,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>102506</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>124918</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4451,7 +4581,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>373380</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>72390</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1493358" cy="344453"/>
@@ -4751,7 +4881,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>185736</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2324100" cy="177228"/>
@@ -5227,7 +5357,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>104774</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>124946</xdr:rowOff>
+      <xdr:rowOff>35299</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5275,8 +5405,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>546913</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>293370</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5361,13 +5491,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>120174</xdr:colOff>
+      <xdr:colOff>151924</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>88455</xdr:rowOff>
+      <xdr:rowOff>448288</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="718026" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -5381,7 +5511,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="777399" y="2593530"/>
+              <a:off x="808091" y="1972288"/>
               <a:ext cx="718026" cy="176651"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5503,7 +5633,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -5517,7 +5647,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="777399" y="2593530"/>
+              <a:off x="808091" y="1972288"/>
               <a:ext cx="718026" cy="176651"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5545,53 +5675,18 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                   <a:effectLst/>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:rPr>
-                <a:t>𝑥 ̅</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:effectLst/>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:rPr>
-                <a:t>_(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:effectLst/>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:rPr>
-                <a:t>𝐴𝐶,𝑊</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:effectLst/>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:rPr>
-                <a:t>)</a:t>
+                <a:t>𝑥 ̅_(𝐴𝐶,𝑊)</a:t>
               </a:r>
               <a:endParaRPr lang="bg-BG" sz="1100"/>
             </a:p>
@@ -6868,8 +6963,8 @@
       <xdr:rowOff>121688</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="644857" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -6975,7 +7070,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -9884,7 +9979,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>198319</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>395554</xdr:rowOff>
+      <xdr:rowOff>437887</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -10372,7 +10467,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>238902</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>59266</xdr:rowOff>
+      <xdr:rowOff>80433</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11374,13 +11469,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>159003</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>426819</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>57149</xdr:rowOff>
@@ -11771,7 +11866,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -11794,294 +11889,299 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="35"/>
+      <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="82">
         <v>15</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="90"/>
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="54"/>
+      <c r="B10" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="4">
+      <c r="C10" s="91"/>
+      <c r="D10" s="83">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="11"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="90"/>
-      <c r="B11" s="39" t="s">
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="54"/>
+      <c r="B11" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="4">
+      <c r="C11" s="91"/>
+      <c r="D11" s="83">
         <v>24</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
-      <c r="B12" s="39" t="s">
+      <c r="A12" s="54"/>
+      <c r="B12" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="83">
         <v>1.4</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="83"/>
+      <c r="F12" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="90"/>
-      <c r="B13" s="65" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="83">
         <f>(D11*D14)/D15</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="83"/>
+      <c r="F13" s="118" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="90"/>
-      <c r="B14" s="39" t="s">
+      <c r="A14" s="54"/>
+      <c r="B14" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="83">
         <v>0.3</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="11"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="90"/>
-      <c r="B15" s="39" t="s">
+      <c r="A15" s="54"/>
+      <c r="B15" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="83">
         <v>1.4399999999999999E-5</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="90"/>
-      <c r="B16" s="39" t="s">
+      <c r="A16" s="54"/>
+      <c r="B16" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="83">
         <v>1.17</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="90"/>
-      <c r="B17" s="65" t="s">
+      <c r="A17" s="54"/>
+      <c r="B17" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="84">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="11"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="90"/>
-      <c r="B18" s="65" t="s">
+      <c r="A18" s="54"/>
+      <c r="B18" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="85">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="90"/>
-      <c r="B19" s="39" t="s">
+      <c r="A19" s="54"/>
+      <c r="B19" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="83">
         <v>10</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="10" t="s">
+      <c r="E19" s="83"/>
+      <c r="F19" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="91"/>
-      <c r="B20" s="65" t="s">
+    <row r="20" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="55"/>
+      <c r="B20" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="86">
         <f>0.25*D14</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="120" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="67" t="s">
+      <c r="G20" s="116" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="121"/>
+    </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="40" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="88">
         <f>D18/4</f>
         <v>0.75679105362627686</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="E22" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="6" t="s">
+      <c r="A23" s="54"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="83">
         <f>D14/4</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="11"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="91"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43" t="s">
+      <c r="A24" s="55"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="44">
-        <f>0.1*D18</f>
-        <v>0.30271642145051075</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="D24" s="89">
+        <f>0.05*D18</f>
+        <v>0.15135821072525538</v>
+      </c>
+      <c r="E24" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="13"/>
+      <c r="G24" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12095,20 +12195,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="12" customWidth="1"/>
     <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -12132,376 +12232,400 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="82">
         <v>0.03</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16" t="s">
+      <c r="E9" s="82"/>
+      <c r="F9" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="90"/>
-      <c r="B10" s="50" t="s">
+      <c r="A10" s="54"/>
+      <c r="B10" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="83">
         <v>0.9</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="36" t="s">
+      <c r="A11" s="55"/>
+      <c r="B11" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="98">
         <f>(D9*D12*D13)/D10</f>
         <v>9.2466982956369487E-2</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="101">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="57"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="104">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="129" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="105">
         <v>0.5</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16" t="s">
+      <c r="E15" s="82"/>
+      <c r="F15" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="90"/>
-      <c r="B16" s="50" t="s">
+      <c r="A16" s="76"/>
+      <c r="B16" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="83">
         <v>0.9</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="10"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
-      <c r="B17" s="36" t="s">
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="84">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.15272871969300542</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+    <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="77"/>
+      <c r="B18" s="128" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="104">
+        <v>0.78129899999999997</v>
+      </c>
+      <c r="E18" s="86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="123"/>
+      <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="92" t="s">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="87"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B20" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C20" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D20" s="108">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E20" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="9"/>
     </row>
-    <row r="20" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="93"/>
-      <c r="B20" s="60" t="s">
+    <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="57"/>
+      <c r="B21" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C21" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D21" s="84">
         <f>D17+D11</f>
         <v>0.2451957026493749</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E21" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="10"/>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="93"/>
-      <c r="B21" s="62" t="s">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="57"/>
+      <c r="B22" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C22" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D22" s="83">
         <v>4</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="10" t="s">
+      <c r="E22" s="83"/>
+      <c r="F22" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="93"/>
-      <c r="B22" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="29">
-        <f>SQRT(D20*D21)</f>
-        <v>0.99034479379532236</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="11"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="93"/>
-      <c r="B23" s="60" t="s">
+      <c r="A23" s="57"/>
+      <c r="B23" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="109">
+        <f>SQRT(D21*D22)</f>
+        <v>0.99034479379532236</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="118"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="57"/>
+      <c r="B24" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C24" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="29">
-        <f>D22/D21</f>
+      <c r="D24" s="109">
+        <f>D23/D22</f>
         <v>0.24758619844883059</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E24" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="11"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="6"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="93"/>
-      <c r="B24" s="62" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="57"/>
+      <c r="B25" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C25" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D25" s="83">
         <v>0</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4" t="s">
+      <c r="E25" s="83"/>
+      <c r="F25" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G25" s="6"/>
     </row>
-    <row r="25" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="94"/>
-      <c r="B25" s="64" t="s">
+    <row r="26" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="58"/>
+      <c r="B26" s="110" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C26" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D26" s="86">
         <v>-10</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E26" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F26" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="13"/>
+      <c r="G26" s="8"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="92" t="s">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="121"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B28" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C28" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="15" t="s">
+      <c r="D28" s="88"/>
+      <c r="E28" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F28" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="38"/>
+      <c r="G28" s="14"/>
     </row>
-    <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="93"/>
-      <c r="B28" s="39" t="s">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="57"/>
+      <c r="B29" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C29" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="29">
-        <f>0.4*D23</f>
+      <c r="D29" s="109">
+        <f>0.4*D24</f>
         <v>9.9034479379532248E-2</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E29" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F29" s="119" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G29" s="6"/>
     </row>
-    <row r="29" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="94"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43" t="s">
+    <row r="30" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="58"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D30" s="86">
         <v>0</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E30" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F30" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="G29" s="13"/>
+      <c r="G30" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A28:A30"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A15:A18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12523,154 +12647,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
+      <c r="A1" s="13"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="30"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="30"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5" s="30"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="30"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="30"/>
+      <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="83" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="71"/>
+      <c r="B8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="84" t="s">
+      <c r="E8" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="74" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="83">
         <f>1.5*Wing!D14</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="E9" s="55" t="s">
+      <c r="E9" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" s="57" t="s">
-        <v>176</v>
+      <c r="F9" s="119" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="96"/>
-      <c r="B10" s="50" t="s">
+      <c r="A10" s="76"/>
+      <c r="B10" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="83">
         <f>3*Wing!D14</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>177</v>
+      <c r="F10" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="96"/>
-      <c r="B11" s="73" t="s">
+      <c r="A11" s="76"/>
+      <c r="B11" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="29">
+      <c r="C11" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="109">
         <f>D9+D10+Wing!D14</f>
         <v>1.65</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
-      <c r="B12" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="79">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="78" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="85">
         <v>0.3</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="82" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" s="24"/>
+      <c r="F12" s="119" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="77"/>
+      <c r="B13" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="86">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="123" t="s">
+        <v>194</v>
+      </c>
+      <c r="G13" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A9:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12692,526 +12827,538 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>112</v>
+      <c r="A1" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="30"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="30"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5" s="30"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="30"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="30"/>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:7" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="76" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="77" t="s">
+      <c r="G8" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="85.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="A9" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="112"/>
+      <c r="C9" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="82">
         <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
-      <c r="E9" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="E9" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="122"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="96"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="69">
+      <c r="A10" s="60"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="85">
         <f>-D11*D9</f>
         <v>-9.6764591226254897</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
+      <c r="E10" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="118"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="96"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="69">
+      <c r="A11" s="60"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="85">
         <f>(2*(22/7)*Wing!D19)/(2+(SQRT((Wing!D19^2)*('Overall AC'!D13)/'Overall AC'!D14+4)))</f>
         <v>5.529405212928852</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="18" t="s">
+      <c r="E11" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="127" t="s">
         <v>116</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="96"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="69">
+      <c r="A12" s="60"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="85">
         <v>0</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="G12" s="20"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="96"/>
-      <c r="B13" s="78" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="61">
+      <c r="A13" s="60"/>
+      <c r="B13" s="114" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="91" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="84">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E13" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="20"/>
+      <c r="E13" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="96"/>
-      <c r="B14" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="69">
+      <c r="A14" s="60"/>
+      <c r="B14" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="85">
         <f>(1+0.75*D15)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E14" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" s="20"/>
+      <c r="E14" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="97"/>
-      <c r="B15" s="74" t="s">
+      <c r="A15" s="61"/>
+      <c r="B15" s="96" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="97" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="79">
+      <c r="D15" s="89">
         <f>(0.12*0.3)/0.3</f>
         <v>0.12</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="126" t="s">
         <v>123</v>
       </c>
-      <c r="F15" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="112"/>
+      <c r="C17" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="28">
-        <f>(D18+(0.25*'V-tail'!D23))/'V-tail'!D23</f>
+      <c r="D17" s="108">
+        <f>(D18+(0.25*'V-tail'!D24))/'V-tail'!D24</f>
         <v>5.9143456312893408</v>
       </c>
-      <c r="E17" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
+      <c r="E17" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="122"/>
+      <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="96"/>
-      <c r="B18" s="73" t="s">
+      <c r="A18" s="60"/>
+      <c r="B18" s="113" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="85">
+        <f>Fuselage!D11-'V-tail'!D24</f>
+        <v>1.4024138015511693</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="69">
-        <f>Fuselage!D11-'V-tail'!D23</f>
-        <v>1.4024138015511693</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="96"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="69">
+      <c r="A19" s="60"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="85">
         <f>-(D20*D21*D22)*D23*D17</f>
         <v>-2.5300219037859915</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="E19" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="118"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="96"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="69">
+      <c r="A20" s="60"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="85">
         <v>0.9</v>
       </c>
-      <c r="E20" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="G20" s="20"/>
+      <c r="E20" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="96"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="69">
+      <c r="A21" s="60"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="85">
         <v>0.7</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="20"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="96"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="69">
+      <c r="A22" s="60"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="85">
         <f>'V-tail'!D17/Wing!D17</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
+      <c r="E22" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="118"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="96"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="18" t="s">
+      <c r="A23" s="60"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="85">
+        <f>(2*(22/7)*'V-tail'!D22)/(2+(SQRT(('V-tail'!D22^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
+        <v>4.0740680719180196</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="125" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="69">
-        <f>(2*(22/7)*'V-tail'!D21)/(2+(SQRT(('V-tail'!D21^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
-        <v>4.0740680719180196</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>117</v>
+      <c r="G23" s="127" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="96"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="69">
+      <c r="A24" s="60"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="85">
         <v>0</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="G24" s="20"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="125" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="96"/>
-      <c r="B25" s="78" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="61">
+      <c r="A25" s="60"/>
+      <c r="B25" s="114" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="91" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="84">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E25" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="G25" s="20"/>
+      <c r="E25" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="96"/>
-      <c r="B26" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="69">
+      <c r="A26" s="60"/>
+      <c r="B26" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="85">
         <f>(1+0.75*D27)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E26" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="20"/>
+      <c r="E26" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="97"/>
-      <c r="B27" s="74" t="s">
+      <c r="A27" s="61"/>
+      <c r="B27" s="96" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="97" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="79">
+      <c r="D27" s="89">
         <f>(0.12*0.248)/0.248</f>
         <v>0.12</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="126" t="s">
         <v>123</v>
       </c>
-      <c r="F27" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="24"/>
+      <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="121"/>
+    </row>
     <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="95" t="s">
+      <c r="A29" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="112"/>
+      <c r="C29" s="90" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="80">
+      <c r="D29" s="108">
         <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
         <v>0.20412193386970173</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="E29" s="82" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="117"/>
+      <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.35">
-      <c r="A30" s="96"/>
-      <c r="B30" s="72" t="s">
+    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A30" s="60"/>
+      <c r="B30" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="92" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="83">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="125" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="60"/>
+      <c r="B31" s="113" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G30" s="11"/>
-    </row>
-    <row r="31" spans="1:7" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="96"/>
-      <c r="B31" s="72" t="s">
+      <c r="C31" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="D31" s="85">
         <f>Fuselage!D12</f>
         <v>0.3</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="11"/>
+      <c r="F31" s="125" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="96"/>
-      <c r="B32" s="72" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="9">
+    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="60"/>
+      <c r="B32" s="113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="91"/>
+      <c r="D32" s="85">
         <f>D33/Fuselage!D11</f>
         <v>0.31818181818181812</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="11"/>
+      <c r="E32" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="118"/>
+      <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="97"/>
-      <c r="B33" s="74" t="s">
+    <row r="33" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="61"/>
+      <c r="B33" s="96" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="93" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="D33" s="86">
         <f>Fuselage!D9+Wing!D14*0.25</f>
         <v>0.52499999999999991</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="121"/>
+    </row>
     <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="98" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D35" s="80">
+      <c r="A35" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="112"/>
+      <c r="C35" s="90" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="108">
         <f>(D10-D29+D19)/D11+D23</f>
         <v>1.8295946643148437</v>
       </c>
-      <c r="E35" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35" s="37"/>
-      <c r="G35" s="38"/>
+      <c r="E35" s="82" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="117"/>
+      <c r="G35" s="14"/>
     </row>
-    <row r="36" spans="1:7" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="99"/>
-      <c r="B36" s="74" t="s">
-        <v>156</v>
-      </c>
-      <c r="C36" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="D36" s="81">
+    <row r="36" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="63"/>
+      <c r="B36" s="96" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="115">
         <f>D35*0.3</f>
         <v>0.54887839929445315</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="G36" s="13"/>
+      <c r="F36" s="120" t="s">
+        <v>158</v>
+      </c>
+      <c r="G36" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13227,299 +13374,373 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
-  <dimension ref="B1:H22"/>
+  <dimension ref="B1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="113" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="64" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="129" t="s">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="28"/>
+      <c r="C4" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="33">
+        <v>1150</v>
+      </c>
+      <c r="D5" s="64"/>
+      <c r="E5" s="42">
+        <v>66</v>
+      </c>
+      <c r="F5" s="26">
+        <v>48</v>
+      </c>
+      <c r="G5" s="43">
+        <v>175</v>
+      </c>
+      <c r="H5" s="38">
+        <v>2</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="35">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="44">
+        <v>53.2</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="52"/>
+      <c r="H6" s="34">
+        <v>4</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="35">
+        <v>180</v>
+      </c>
+      <c r="D7" s="65"/>
+      <c r="E7" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" s="68"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="34">
+        <v>4</v>
+      </c>
+      <c r="I7" s="47"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="35">
+        <v>110</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="44">
+        <v>19.5</v>
+      </c>
+      <c r="F8" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="G8" s="6">
+        <v>84</v>
+      </c>
+      <c r="H8" s="34">
+        <v>4</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="35">
+        <v>70</v>
+      </c>
+      <c r="D9" s="65"/>
+      <c r="E9" s="44">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="F9" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="H9" s="34">
+        <v>4</v>
+      </c>
+      <c r="I9" s="47"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="35">
+        <v>50</v>
+      </c>
+      <c r="D10" s="65"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="4">
+        <v>56</v>
+      </c>
+      <c r="G10" s="6">
+        <v>85</v>
+      </c>
+      <c r="H10" s="34">
+        <v>1</v>
+      </c>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="35">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="65"/>
+      <c r="E11" s="44">
+        <v>230</v>
+      </c>
+      <c r="F11" s="4">
+        <v>300</v>
+      </c>
+      <c r="G11" s="6">
+        <v>200</v>
+      </c>
+      <c r="H11" s="34">
+        <v>1</v>
+      </c>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="35">
+        <v>200</v>
+      </c>
+      <c r="D12" s="65"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="34">
+        <v>1</v>
+      </c>
+      <c r="I12" s="47"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="35">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="65"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="34">
+        <v>1</v>
+      </c>
+      <c r="I13" s="47"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="35">
+        <v>1000</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="34">
+        <v>1</v>
+      </c>
+      <c r="I14" s="47"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="35">
+        <v>400</v>
+      </c>
+      <c r="D15" s="65"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="34">
+        <v>1</v>
+      </c>
+      <c r="I15" s="47"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="35">
+        <v>250</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="34">
+        <v>4</v>
+      </c>
+      <c r="I16" s="47"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="35">
+        <v>2000</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="47"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
         <v>190</v>
       </c>
+      <c r="C18" s="35">
+        <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C10+C11+C12+C13+C14+C15+C16*H16</f>
+        <v>11160.8</v>
+      </c>
+      <c r="D18" s="65"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="47"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="130" t="s">
-        <v>4</v>
-      </c>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="30"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="47"/>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="103"/>
-      <c r="C4" s="108" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="117" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="102" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="118" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="108" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="123" t="s">
-        <v>183</v>
-      </c>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="30"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="47"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="104" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="109">
-        <v>1150</v>
-      </c>
-      <c r="D5" s="119">
-        <v>66</v>
-      </c>
-      <c r="E5" s="101">
-        <v>48</v>
-      </c>
-      <c r="F5" s="120">
-        <v>175</v>
-      </c>
-      <c r="G5" s="114">
-        <v>2</v>
-      </c>
-      <c r="H5" s="124" t="s">
-        <v>184</v>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="47" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="105" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="111">
-        <v>142.69999999999999</v>
-      </c>
-      <c r="D6" s="121">
-        <v>53.2</v>
-      </c>
-      <c r="E6" s="100" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="110">
-        <v>4</v>
-      </c>
-      <c r="H6" s="125" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="105" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="111">
-        <v>180</v>
-      </c>
-      <c r="D7" s="127" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" s="107"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="110">
-        <v>4</v>
-      </c>
-      <c r="H7" s="125"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="105" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="111">
-        <v>110</v>
-      </c>
-      <c r="D8" s="121">
-        <v>19.5</v>
-      </c>
-      <c r="E8" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="F8" s="11">
-        <v>84</v>
-      </c>
-      <c r="G8" s="110">
-        <v>4</v>
-      </c>
-      <c r="H8" s="125" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="105" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="125"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="105" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="110">
-        <v>1</v>
-      </c>
-      <c r="H10" s="125"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="105" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="111">
-        <v>3000</v>
-      </c>
-      <c r="D11" s="121"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="110">
-        <v>1</v>
-      </c>
-      <c r="H11" s="125"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="125"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="110">
-        <v>1</v>
-      </c>
-      <c r="H13" s="125"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="105" t="s">
+    <row r="22" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="110">
-        <v>1</v>
-      </c>
-      <c r="H14" s="125"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="105" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="110">
-        <v>1</v>
-      </c>
-      <c r="H15" s="125"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="105" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="125"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="105"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="125"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="105" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="125"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="105"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="125"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="105" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="125"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="105" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="125"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="106" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="112"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="126"/>
+      <c r="C22" s="36">
+        <f>'Overall AC'!D36-0.05*'Overall AC'!D36</f>
+        <v>0.52143447932973053</v>
+      </c>
+      <c r="D22" s="66">
+        <f>'Overall AC'!D36-0.1*'Overall AC'!D36</f>
+        <v>0.4939905593650078</v>
+      </c>
+      <c r="E22" s="45"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="48" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="E7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894EE9DD-AAE0-4A07-8EF3-9232A7F81AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85457B-0D25-480C-9A9E-B3C7C3DA79AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="198">
   <si>
     <t>kg</t>
   </si>
@@ -1124,9 +1124,6 @@
   </si>
   <si>
     <t>FLAME 80A 12S V2.0 Multi-Rotor UAVs ESC</t>
-  </si>
-  <si>
-    <t>Fixed</t>
   </si>
   <si>
     <t>CF structure</t>
@@ -1330,7 +1327,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1784,19 +1781,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1839,11 +1823,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1851,7 +1898,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1895,7 +1941,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1904,14 +1949,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1923,60 +1964,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1989,22 +1982,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2151,8 +2135,96 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5496,8 +5568,8 @@
       <xdr:rowOff>448288</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="718026" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -5633,7 +5705,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -11478,7 +11550,7 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>426819</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:rowOff>49529</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11832,9 +11904,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -11853,335 +11925,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="13"/>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="12"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="57">
         <v>15</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="117"/>
-      <c r="G9" s="14"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
-      <c r="B10" s="78" t="s">
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="105"/>
+      <c r="B10" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="83">
+      <c r="C10" s="66"/>
+      <c r="D10" s="58">
         <v>14</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="93"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
-      <c r="B11" s="78" t="s">
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="105"/>
+      <c r="B11" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="83">
+      <c r="C11" s="66"/>
+      <c r="D11" s="58">
         <v>24</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="93"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="78" t="s">
+    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="105"/>
+      <c r="B12" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="58">
         <v>1.4</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="119" t="s">
+      <c r="E12" s="58"/>
+      <c r="F12" s="94" t="s">
         <v>55</v>
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="54"/>
-      <c r="B13" s="79" t="s">
+    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="105"/>
+      <c r="B13" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="58">
         <f>(D11*D14)/D15</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="83"/>
-      <c r="F13" s="118" t="s">
+      <c r="E13" s="58"/>
+      <c r="F13" s="93" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="54"/>
-      <c r="B14" s="78" t="s">
+    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="105"/>
+      <c r="B14" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="58">
         <v>0.3</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="118"/>
+      <c r="F14" s="93"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="54"/>
-      <c r="B15" s="78" t="s">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="105"/>
+      <c r="B15" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="83">
+      <c r="D15" s="58">
         <v>1.4399999999999999E-5</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="119" t="s">
+      <c r="F15" s="94" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="78" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="105"/>
+      <c r="B16" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="58">
         <v>1.17</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="118" t="s">
+      <c r="F16" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="54"/>
-      <c r="B17" s="79" t="s">
+    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="105"/>
+      <c r="B17" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="59">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="118"/>
+      <c r="F17" s="93"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="79" t="s">
+    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="105"/>
+      <c r="B18" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="85">
+      <c r="D18" s="60">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="118"/>
+      <c r="F18" s="93"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="78" t="s">
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="105"/>
+      <c r="B19" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="83">
+      <c r="D19" s="58">
         <v>10</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="119" t="s">
+      <c r="E19" s="58"/>
+      <c r="F19" s="94" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="79" t="s">
+    <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="106"/>
+      <c r="B20" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="61">
         <f>0.25*D14</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E20" s="86" t="s">
+      <c r="E20" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="120" t="s">
+      <c r="F20" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="116" t="s">
+      <c r="G20" s="91" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="121"/>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="96"/>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="90" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="88">
+      <c r="D22" s="63">
         <f>D18/4</f>
         <v>0.75679105362627686</v>
       </c>
-      <c r="E22" s="82" t="s">
+      <c r="E22" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="117"/>
-      <c r="G22" s="14"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="92" t="s">
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="105"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="83">
+      <c r="D23" s="58">
         <f>D14/4</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="93"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="93" t="s">
+    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="106"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="89">
+      <c r="D24" s="64">
         <f>0.05*D18</f>
         <v>0.15135821072525538</v>
       </c>
-      <c r="E24" s="86" t="s">
+      <c r="E24" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="120" t="s">
+      <c r="F24" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12196,429 +12268,429 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="57">
         <v>0.03</v>
       </c>
-      <c r="E9" s="82"/>
-      <c r="F9" s="122" t="s">
+      <c r="E9" s="57"/>
+      <c r="F9" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
-      <c r="B10" s="95" t="s">
+    <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="105"/>
+      <c r="B10" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="58">
         <v>0.9</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="118" t="s">
+      <c r="F10" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55"/>
-      <c r="B11" s="96" t="s">
+    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="106"/>
+      <c r="B11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="98">
+      <c r="D11" s="73">
         <f>(D9*D12*D13)/D10</f>
         <v>9.2466982956369487E-2</v>
       </c>
-      <c r="E11" s="86" t="s">
+      <c r="E11" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="123"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="B12" s="99" t="s">
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="100" t="s">
+      <c r="C12" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="101">
+      <c r="D12" s="76">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="103" t="s">
+    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="104">
+      <c r="D13" s="79">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="86" t="s">
+      <c r="E13" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="123"/>
-      <c r="G13" s="11"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="87"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="12"/>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="62"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="129" t="s">
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="90" t="s">
+      <c r="C15" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="105">
+      <c r="D15" s="80">
         <v>0.5</v>
       </c>
-      <c r="E15" s="82"/>
-      <c r="F15" s="122" t="s">
+      <c r="E15" s="57"/>
+      <c r="F15" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="9"/>
+      <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
-      <c r="B16" s="78" t="s">
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="111"/>
+      <c r="B16" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="58">
         <v>0.9</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="118" t="s">
+      <c r="F16" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76"/>
-      <c r="B17" s="79" t="s">
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="111"/>
+      <c r="B17" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="59">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.15272871969300542</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="118"/>
-      <c r="G17" s="10"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="77"/>
-      <c r="B18" s="128" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="93" t="s">
+    <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="112"/>
+      <c r="B18" s="103" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="104">
+      <c r="C18" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="79">
         <v>0.78129899999999997</v>
       </c>
-      <c r="E18" s="86" t="s">
+      <c r="E18" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="123"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="87"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="12"/>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="62"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+    <row r="20" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="107" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="107" t="s">
+      <c r="B20" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="108">
+      <c r="D20" s="83">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="117"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57"/>
-      <c r="B21" s="79" t="s">
+    <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="108"/>
+      <c r="B21" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="84">
+      <c r="D21" s="59">
         <f>D17+D11</f>
         <v>0.2451957026493749</v>
       </c>
-      <c r="E21" s="83" t="s">
+      <c r="E21" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="118"/>
-      <c r="G21" s="10"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
-      <c r="B22" s="78" t="s">
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="83">
+      <c r="D22" s="58">
         <v>4</v>
       </c>
-      <c r="E22" s="83"/>
-      <c r="F22" s="119" t="s">
+      <c r="E22" s="58"/>
+      <c r="F22" s="94" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
-      <c r="B23" s="79" t="s">
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="108"/>
+      <c r="B23" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="109">
+      <c r="D23" s="84">
         <f>SQRT(D21*D22)</f>
         <v>0.99034479379532236</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="93"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
-      <c r="B24" s="79" t="s">
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="108"/>
+      <c r="B24" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="92" t="s">
+      <c r="C24" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="109">
+      <c r="D24" s="84">
         <f>D23/D22</f>
         <v>0.24758619844883059</v>
       </c>
-      <c r="E24" s="83" t="s">
+      <c r="E24" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="118"/>
+      <c r="F24" s="93"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="57"/>
-      <c r="B25" s="78" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="108"/>
+      <c r="B25" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="83">
+      <c r="D25" s="58">
         <v>0</v>
       </c>
-      <c r="E25" s="83"/>
-      <c r="F25" s="118" t="s">
+      <c r="E25" s="58"/>
+      <c r="F25" s="93" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="58"/>
-      <c r="B26" s="110" t="s">
+    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="109"/>
+      <c r="B26" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="86">
+      <c r="D26" s="61">
         <v>-10</v>
       </c>
-      <c r="E26" s="86" t="s">
+      <c r="E26" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="120" t="s">
+      <c r="F26" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="8"/>
+      <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="121"/>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="96"/>
     </row>
-    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="111" t="s">
+      <c r="B28" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="88"/>
-      <c r="E28" s="82" t="s">
+      <c r="D28" s="63"/>
+      <c r="E28" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="117" t="s">
+      <c r="F28" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="14"/>
+      <c r="G28" s="13"/>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="57"/>
-      <c r="B29" s="78" t="s">
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="109">
+      <c r="D29" s="84">
         <f>0.4*D24</f>
         <v>9.9034479379532248E-2</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="119" t="s">
+      <c r="F29" s="94" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58"/>
-      <c r="B30" s="110"/>
-      <c r="C30" s="93" t="s">
+    <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="109"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="86">
+      <c r="D30" s="61">
         <v>0</v>
       </c>
-      <c r="E30" s="86" t="s">
+      <c r="E30" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="120" t="s">
+      <c r="F30" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="8"/>
+      <c r="G30" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12635,173 +12707,173 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="12"/>
+      <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="12"/>
+      <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5" s="12"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="12"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="12"/>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="49"/>
+      <c r="B8" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="52" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="75" t="s">
+    <row r="9" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="113" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="92" t="s">
+      <c r="C9" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="58">
         <f>1.5*Wing!D14</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="119" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="94" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="78" t="s">
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="111"/>
+      <c r="B10" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="58">
         <f>3*Wing!D14</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="118" t="s">
+      <c r="F10" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="76"/>
-      <c r="B11" s="79" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="111"/>
+      <c r="B11" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="84">
         <f>D9+D10+Wing!D14</f>
         <v>1.65</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="118"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="76"/>
-      <c r="B12" s="78" t="s">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="111"/>
+      <c r="B12" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="85">
+      <c r="D12" s="60">
         <v>0.3</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="119" t="s">
+      <c r="F12" s="94" t="s">
         <v>172</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77"/>
-      <c r="B13" s="80" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="93" t="s">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="112"/>
+      <c r="B13" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="61">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="98" t="s">
         <v>193</v>
       </c>
-      <c r="D13" s="86">
-        <v>0.1</v>
-      </c>
-      <c r="E13" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="123" t="s">
-        <v>194</v>
-      </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12815,550 +12887,550 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1379866-2160-4925-834D-A41ED5331C38}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="41.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>111</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="12"/>
+      <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="12"/>
+      <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5" s="12"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="12"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="12"/>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24" t="s">
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="22"/>
+      <c r="B8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="85.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+    <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="90" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="57">
         <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
-      <c r="E9" s="84" t="s">
+      <c r="E9" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="122"/>
-      <c r="G9" s="9"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="113"/>
-      <c r="C10" s="92" t="s">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="115"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="85">
+      <c r="D10" s="60">
         <f>-D11*D9</f>
         <v>-9.6764591226254897</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="118"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="60"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="92" t="s">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="115"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="85">
+      <c r="D11" s="60">
         <f>(2*(22/7)*Wing!D19)/(2+(SQRT((Wing!D19^2)*('Overall AC'!D13)/'Overall AC'!D14+4)))</f>
         <v>5.529405212928852</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="125" t="s">
+      <c r="F11" s="100" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="127" t="s">
+      <c r="G11" s="102" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="60"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="92" t="s">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="115"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="85">
+      <c r="D12" s="60">
         <v>0</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="125" t="s">
+      <c r="E12" s="58"/>
+      <c r="F12" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
-      <c r="B13" s="114" t="s">
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="115"/>
+      <c r="B13" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="84">
+      <c r="D13" s="59">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E13" s="84" t="s">
+      <c r="E13" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="125" t="s">
+      <c r="F13" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="10"/>
+      <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="60"/>
-      <c r="B14" s="113" t="s">
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="115"/>
+      <c r="B14" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="60">
         <f>(1+0.75*D15)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="125" t="s">
+      <c r="F14" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
-      <c r="B15" s="96" t="s">
+    <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="116"/>
+      <c r="B15" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="89">
+      <c r="D15" s="64">
         <f>(0.12*0.3)/0.3</f>
         <v>0.12</v>
       </c>
-      <c r="E15" s="86" t="s">
+      <c r="E15" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="126" t="s">
+      <c r="F15" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="87"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="12"/>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="62"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
+    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="90" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="108">
+      <c r="D17" s="83">
         <f>(D18+(0.25*'V-tail'!D24))/'V-tail'!D24</f>
         <v>5.9143456312893408</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="122"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="60"/>
-      <c r="B18" s="113" t="s">
+    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="115"/>
+      <c r="B18" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="85">
+      <c r="D18" s="60">
         <f>Fuselage!D11-'V-tail'!D24</f>
         <v>1.4024138015511693</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="119" t="s">
+      <c r="F18" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="60"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="92" t="s">
+    <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="115"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="85">
+      <c r="D19" s="60">
         <f>-(D20*D21*D22)*D23*D17</f>
         <v>-2.5300219037859915</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="118"/>
-      <c r="G19" s="10"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="60"/>
-      <c r="B20" s="113"/>
-      <c r="C20" s="92" t="s">
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="115"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="85">
+      <c r="D20" s="60">
         <v>0.9</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="119" t="s">
+      <c r="F20" s="94" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="60"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="92" t="s">
+    <row r="21" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="115"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="85">
+      <c r="D21" s="60">
         <v>0.7</v>
       </c>
-      <c r="E21" s="83"/>
-      <c r="F21" s="119" t="s">
+      <c r="E21" s="58"/>
+      <c r="F21" s="94" t="s">
         <v>138</v>
       </c>
-      <c r="G21" s="10"/>
+      <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="60"/>
-      <c r="B22" s="113"/>
-      <c r="C22" s="92" t="s">
+    <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="115"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="85">
+      <c r="D22" s="60">
         <f>'V-tail'!D17/Wing!D17</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="E22" s="83" t="s">
+      <c r="E22" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F22" s="118"/>
-      <c r="G22" s="10"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="60"/>
-      <c r="B23" s="113"/>
-      <c r="C23" s="92" t="s">
+    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="115"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="60">
         <f>(2*(22/7)*'V-tail'!D22)/(2+(SQRT(('V-tail'!D22^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
         <v>4.0740680719180196</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="125" t="s">
+      <c r="F23" s="100" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="127" t="s">
+      <c r="G23" s="102" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="60"/>
-      <c r="B24" s="113"/>
-      <c r="C24" s="92" t="s">
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="115"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="85">
+      <c r="D24" s="60">
         <v>0</v>
       </c>
-      <c r="E24" s="83"/>
-      <c r="F24" s="125" t="s">
+      <c r="E24" s="58"/>
+      <c r="F24" s="100" t="s">
         <v>142</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="60"/>
-      <c r="B25" s="114" t="s">
+    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="115"/>
+      <c r="B25" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="59">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="125" t="s">
+      <c r="F25" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="10"/>
+      <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="60"/>
-      <c r="B26" s="113" t="s">
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="115"/>
+      <c r="B26" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="85">
+      <c r="D26" s="60">
         <f>(1+0.75*D27)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E26" s="84" t="s">
+      <c r="E26" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="125" t="s">
+      <c r="F26" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="G26" s="10"/>
+      <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
-      <c r="B27" s="96" t="s">
+    <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="116"/>
+      <c r="B27" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="97" t="s">
+      <c r="C27" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="89">
+      <c r="D27" s="64">
         <f>(0.12*0.248)/0.248</f>
         <v>0.12</v>
       </c>
-      <c r="E27" s="86" t="s">
+      <c r="E27" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="G27" s="11"/>
+      <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="87"/>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="121"/>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="96"/>
     </row>
-    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="59" t="s">
+    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="114" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="112"/>
-      <c r="C29" s="90" t="s">
+      <c r="B29" s="87"/>
+      <c r="C29" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="108">
+      <c r="D29" s="83">
         <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
         <v>0.20412193386970173</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="117"/>
-      <c r="G29" s="14"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A30" s="60"/>
-      <c r="B30" s="113" t="s">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.3">
+      <c r="A30" s="115"/>
+      <c r="B30" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="92" t="s">
+      <c r="C30" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="83">
+      <c r="D30" s="58">
         <v>0.01</v>
       </c>
-      <c r="E30" s="83" t="s">
+      <c r="E30" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="125" t="s">
+      <c r="F30" s="100" t="s">
         <v>152</v>
       </c>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="60"/>
-      <c r="B31" s="113" t="s">
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="115"/>
+      <c r="B31" s="88" t="s">
         <v>146</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="85">
+      <c r="D31" s="60">
         <f>Fuselage!D12</f>
         <v>0.3</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="125" t="s">
+      <c r="F31" s="100" t="s">
         <v>153</v>
       </c>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A32" s="60"/>
-      <c r="B32" s="113" t="s">
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="115"/>
+      <c r="B32" s="88" t="s">
         <v>149</v>
       </c>
-      <c r="C32" s="91"/>
-      <c r="D32" s="85">
+      <c r="C32" s="66"/>
+      <c r="D32" s="60">
         <f>D33/Fuselage!D11</f>
         <v>0.31818181818181812</v>
       </c>
-      <c r="E32" s="83" t="s">
+      <c r="E32" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="118"/>
+      <c r="F32" s="93"/>
       <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
-      <c r="B33" s="96" t="s">
+    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="116"/>
+      <c r="B33" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="93" t="s">
+      <c r="C33" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="86">
+      <c r="D33" s="61">
         <f>Fuselage!D9+Wing!D14*0.25</f>
         <v>0.52499999999999991</v>
       </c>
-      <c r="E33" s="86" t="s">
+      <c r="E33" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="123"/>
-      <c r="G33" s="8"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="121"/>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="96"/>
     </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="62" t="s">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="117" t="s">
         <v>154</v>
       </c>
-      <c r="B35" s="112"/>
-      <c r="C35" s="90" t="s">
+      <c r="B35" s="87"/>
+      <c r="C35" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="83">
         <f>(D10-D29+D19)/D11+D23</f>
         <v>1.8295946643148437</v>
       </c>
-      <c r="E35" s="82" t="s">
+      <c r="E35" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="117"/>
-      <c r="G35" s="14"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="63"/>
-      <c r="B36" s="96" t="s">
+    <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="118"/>
+      <c r="B36" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="115">
+      <c r="D36" s="90">
         <f>D35*0.3</f>
         <v>0.54887839929445315</v>
       </c>
-      <c r="E36" s="86" t="s">
+      <c r="E36" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="120" t="s">
+      <c r="F36" s="95" t="s">
         <v>158</v>
       </c>
-      <c r="G36" s="8"/>
+      <c r="G36" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13374,127 +13446,123 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
-  <dimension ref="B1:I22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="34" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="49" t="s">
-        <v>184</v>
-      </c>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B1" s="43"/>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="44"/>
+    </row>
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="27"/>
+      <c r="C4" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="31">
+        <v>1150</v>
+      </c>
+      <c r="D5" s="45"/>
+      <c r="E5" s="38">
+        <v>66</v>
+      </c>
+      <c r="F5" s="25">
+        <v>48</v>
+      </c>
+      <c r="G5" s="39">
+        <v>175</v>
+      </c>
+      <c r="H5" s="35">
+        <v>2</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="33">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="40">
+        <v>53.2</v>
+      </c>
+      <c r="F6" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="120"/>
+      <c r="H6" s="32">
         <v>4</v>
       </c>
+      <c r="I6" s="42" t="s">
+        <v>179</v>
+      </c>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28"/>
-      <c r="C4" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>177</v>
-      </c>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="33">
+        <v>180</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="121" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" s="122"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="32">
+        <v>4</v>
+      </c>
+      <c r="I7" s="42"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="33">
-        <v>1150</v>
-      </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="42">
-        <v>66</v>
-      </c>
-      <c r="F5" s="26">
-        <v>48</v>
-      </c>
-      <c r="G5" s="43">
-        <v>175</v>
-      </c>
-      <c r="H5" s="38">
-        <v>2</v>
-      </c>
-      <c r="I5" s="46" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="35">
-        <v>142.69999999999999</v>
-      </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="44">
-        <v>53.2</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="52"/>
-      <c r="H6" s="34">
-        <v>4</v>
-      </c>
-      <c r="I6" s="47" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" s="35">
-        <v>180</v>
-      </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="34">
-        <v>4</v>
-      </c>
-      <c r="I7" s="47"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="33">
         <v>110</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="44">
+      <c r="D8" s="46"/>
+      <c r="E8" s="40">
         <v>19.5</v>
       </c>
       <c r="F8" s="4">
@@ -13503,22 +13571,22 @@
       <c r="G8" s="6">
         <v>84</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="32">
         <v>4</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="42" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <v>70</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="44">
+      <c r="D9" s="46"/>
+      <c r="E9" s="40">
         <v>38.700000000000003</v>
       </c>
       <c r="F9" s="4">
@@ -13527,40 +13595,40 @@
       <c r="G9" s="6">
         <v>40.299999999999997</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="32">
         <v>4</v>
       </c>
-      <c r="I9" s="47"/>
+      <c r="I9" s="42"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="33">
         <v>50</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="44"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="40"/>
       <c r="F10" s="4">
         <v>56</v>
       </c>
       <c r="G10" s="6">
         <v>85</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="32">
         <v>1</v>
       </c>
-      <c r="I10" s="47"/>
+      <c r="I10" s="42"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="33">
         <v>3000</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="44">
+      <c r="D11" s="46"/>
+      <c r="E11" s="40">
         <v>230</v>
       </c>
       <c r="F11" s="4">
@@ -13569,178 +13637,191 @@
       <c r="G11" s="6">
         <v>200</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="32">
         <v>1</v>
       </c>
-      <c r="I11" s="47"/>
+      <c r="I11" s="42"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="33">
         <v>200</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="44"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="4"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="34">
+      <c r="H12" s="32">
         <v>1</v>
       </c>
-      <c r="I12" s="47"/>
+      <c r="I12" s="42"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="35">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="33">
         <v>1200</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="44"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="4"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="34">
+      <c r="H13" s="32">
         <v>1</v>
       </c>
-      <c r="I13" s="47"/>
+      <c r="I13" s="42"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="35">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="33">
         <v>1000</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="44"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="4"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="34">
+      <c r="H14" s="32">
         <v>1</v>
       </c>
-      <c r="I14" s="47"/>
+      <c r="I14" s="42"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="35">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="33">
         <v>400</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="44"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="4"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="34">
+      <c r="H15" s="32">
         <v>1</v>
       </c>
-      <c r="I15" s="47"/>
+      <c r="I15" s="42"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <v>250</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="44"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="4"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="34">
+      <c r="H16" s="32">
         <v>4</v>
       </c>
-      <c r="I16" s="47"/>
+      <c r="I16" s="42"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="35">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="123" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="124">
         <v>2000</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="47"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="129">
+        <v>1</v>
+      </c>
+      <c r="I17" s="130"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="35">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="131" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="27">
         <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C10+C11+C12+C13+C14+C15+C16*H16</f>
         <v>11160.8</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="47"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="136" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="137"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="30"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="47"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="138"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="138"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="30"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="47"/>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="142" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="146"/>
+      <c r="E20" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" s="144" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="47" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="31" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="142" t="s">
         <v>169</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C21" s="145">
         <f>'Overall AC'!D36-0.05*'Overall AC'!D36</f>
         <v>0.52143447932973053</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D21" s="145">
         <f>'Overall AC'!D36-0.1*'Overall AC'!D36</f>
         <v>0.4939905593650078</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="48" t="s">
-        <v>191</v>
+      <c r="E21" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="144" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="E7:G7"/>
+    <mergeCell ref="C20:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85457B-0D25-480C-9A9E-B3C7C3DA79AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173B746A-BEF6-433C-B857-613A564B81A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="199">
   <si>
     <t>kg</t>
   </si>
@@ -1016,9 +1016,6 @@
     <t>ESCs</t>
   </si>
   <si>
-    <t>servos</t>
-  </si>
-  <si>
     <t>flight controller</t>
   </si>
   <si>
@@ -1108,9 +1105,6 @@
     <t xml:space="preserve">Model assumed </t>
   </si>
   <si>
-    <t>Turnigy BoltX LiHV 6S 10500mAh 22.8V 80C LiPo Battery Pack w/XT90</t>
-  </si>
-  <si>
     <t>BrotherHobby Avenger 3120 Motors 500KV FPV Drone Motor</t>
   </si>
   <si>
@@ -1190,6 +1184,15 @@
       </rPr>
       <t>HT</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Arduino Mega 2560 </t>
+  </si>
+  <si>
+    <t>servos flight controls</t>
+  </si>
+  <si>
+    <t>servos motors</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2135,6 +2138,32 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2192,40 +2221,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11984,7 +11983,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="124" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="56" t="s">
@@ -12003,7 +12002,7 @@
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="53" t="s">
         <v>52</v>
       </c>
@@ -12018,7 +12017,7 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="105"/>
+      <c r="A11" s="125"/>
       <c r="B11" s="53" t="s">
         <v>51</v>
       </c>
@@ -12033,7 +12032,7 @@
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="105"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="53" t="s">
         <v>20</v>
       </c>
@@ -12050,7 +12049,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
+      <c r="A13" s="125"/>
       <c r="B13" s="54" t="s">
         <v>19</v>
       </c>
@@ -12068,7 +12067,7 @@
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="105"/>
+      <c r="A14" s="125"/>
       <c r="B14" s="53" t="s">
         <v>15</v>
       </c>
@@ -12085,7 +12084,7 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
+      <c r="A15" s="125"/>
       <c r="B15" s="53" t="s">
         <v>16</v>
       </c>
@@ -12104,7 +12103,7 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="53" t="s">
         <v>5</v>
       </c>
@@ -12123,7 +12122,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105"/>
+      <c r="A17" s="125"/>
       <c r="B17" s="54" t="s">
         <v>11</v>
       </c>
@@ -12141,7 +12140,7 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="105"/>
+      <c r="A18" s="125"/>
       <c r="B18" s="54" t="s">
         <v>27</v>
       </c>
@@ -12159,7 +12158,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="105"/>
+      <c r="A19" s="125"/>
       <c r="B19" s="53" t="s">
         <v>29</v>
       </c>
@@ -12176,7 +12175,7 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106"/>
+      <c r="A20" s="126"/>
       <c r="B20" s="54" t="s">
         <v>98</v>
       </c>
@@ -12204,7 +12203,7 @@
       <c r="F21" s="96"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="124" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="16"/>
@@ -12222,7 +12221,7 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="105"/>
+      <c r="A23" s="125"/>
       <c r="B23" s="14"/>
       <c r="C23" s="67" t="s">
         <v>80</v>
@@ -12238,7 +12237,7 @@
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="106"/>
+      <c r="A24" s="126"/>
       <c r="B24" s="15"/>
       <c r="C24" s="68" t="s">
         <v>81</v>
@@ -12324,7 +12323,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="124" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="69" t="s">
@@ -12343,7 +12342,7 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="70" t="s">
         <v>62</v>
       </c>
@@ -12362,7 +12361,7 @@
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="106"/>
+      <c r="A11" s="126"/>
       <c r="B11" s="71" t="s">
         <v>63</v>
       </c>
@@ -12422,7 +12421,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="110" t="s">
+      <c r="A15" s="130" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="86" t="s">
@@ -12441,7 +12440,7 @@
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="111"/>
+      <c r="A16" s="131"/>
       <c r="B16" s="53" t="s">
         <v>58</v>
       </c>
@@ -12460,7 +12459,7 @@
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="111"/>
+      <c r="A17" s="131"/>
       <c r="B17" s="54" t="s">
         <v>59</v>
       </c>
@@ -12478,12 +12477,12 @@
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="112"/>
+      <c r="A18" s="132"/>
       <c r="B18" s="103" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D18" s="79">
         <v>0.78129899999999997</v>
@@ -12503,7 +12502,7 @@
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="107" t="s">
+      <c r="A20" s="127" t="s">
         <v>92</v>
       </c>
       <c r="B20" s="82" t="s">
@@ -12523,7 +12522,7 @@
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="108"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="54" t="s">
         <v>56</v>
       </c>
@@ -12541,7 +12540,7 @@
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="53" t="s">
         <v>29</v>
       </c>
@@ -12558,7 +12557,7 @@
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="54" t="s">
         <v>66</v>
       </c>
@@ -12576,7 +12575,7 @@
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="108"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="54" t="s">
         <v>68</v>
       </c>
@@ -12594,7 +12593,7 @@
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="108"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="53" t="s">
         <v>70</v>
       </c>
@@ -12611,7 +12610,7 @@
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="109"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="85" t="s">
         <v>75</v>
       </c>
@@ -12637,7 +12636,7 @@
       <c r="F27" s="96"/>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="127" t="s">
         <v>83</v>
       </c>
       <c r="B28" s="86" t="s">
@@ -12656,7 +12655,7 @@
       <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
+      <c r="A29" s="128"/>
       <c r="B29" s="53" t="s">
         <v>94</v>
       </c>
@@ -12676,7 +12675,7 @@
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="109"/>
+      <c r="A30" s="129"/>
       <c r="B30" s="85"/>
       <c r="C30" s="68" t="s">
         <v>86</v>
@@ -12774,7 +12773,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="133" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="53" t="s">
@@ -12791,14 +12790,14 @@
         <v>18</v>
       </c>
       <c r="F9" s="94" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="111"/>
+      <c r="A10" s="131"/>
       <c r="B10" s="53" t="s">
         <v>102</v>
       </c>
@@ -12816,11 +12815,11 @@
         <v>107</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="111"/>
+      <c r="A11" s="131"/>
       <c r="B11" s="54" t="s">
         <v>104</v>
       </c>
@@ -12838,7 +12837,7 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="111"/>
+      <c r="A12" s="131"/>
       <c r="B12" s="53" t="s">
         <v>108</v>
       </c>
@@ -12852,17 +12851,17 @@
         <v>18</v>
       </c>
       <c r="F12" s="94" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="112"/>
+      <c r="A13" s="132"/>
       <c r="B13" s="55" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D13" s="61">
         <v>0.1</v>
@@ -12871,7 +12870,7 @@
         <v>18</v>
       </c>
       <c r="F13" s="98" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G13" s="10"/>
     </row>
@@ -12956,7 +12955,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="134" t="s">
         <v>109</v>
       </c>
       <c r="B9" s="87"/>
@@ -12974,7 +12973,7 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="115"/>
+      <c r="A10" s="135"/>
       <c r="B10" s="88"/>
       <c r="C10" s="67" t="s">
         <v>113</v>
@@ -12990,7 +12989,7 @@
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="115"/>
+      <c r="A11" s="135"/>
       <c r="B11" s="88"/>
       <c r="C11" s="67" t="s">
         <v>117</v>
@@ -13010,7 +13009,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="115"/>
+      <c r="A12" s="135"/>
       <c r="B12" s="88"/>
       <c r="C12" s="67" t="s">
         <v>110</v>
@@ -13025,7 +13024,7 @@
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="115"/>
+      <c r="A13" s="135"/>
       <c r="B13" s="89" t="s">
         <v>125</v>
       </c>
@@ -13045,7 +13044,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
+      <c r="A14" s="135"/>
       <c r="B14" s="88" t="s">
         <v>124</v>
       </c>
@@ -13065,7 +13064,7 @@
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="116"/>
+      <c r="A15" s="136"/>
       <c r="B15" s="71" t="s">
         <v>118</v>
       </c>
@@ -13093,7 +13092,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="134" t="s">
         <v>130</v>
       </c>
       <c r="B17" s="87"/>
@@ -13111,7 +13110,7 @@
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="115"/>
+      <c r="A18" s="135"/>
       <c r="B18" s="88" t="s">
         <v>132</v>
       </c>
@@ -13131,7 +13130,7 @@
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="115"/>
+      <c r="A19" s="135"/>
       <c r="B19" s="88"/>
       <c r="C19" s="67" t="s">
         <v>135</v>
@@ -13147,7 +13146,7 @@
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="115"/>
+      <c r="A20" s="135"/>
       <c r="B20" s="88"/>
       <c r="C20" s="67" t="s">
         <v>139</v>
@@ -13164,7 +13163,7 @@
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="115"/>
+      <c r="A21" s="135"/>
       <c r="B21" s="88"/>
       <c r="C21" s="67" t="s">
         <v>140</v>
@@ -13179,7 +13178,7 @@
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="115"/>
+      <c r="A22" s="135"/>
       <c r="B22" s="88"/>
       <c r="C22" s="67" t="s">
         <v>141</v>
@@ -13195,7 +13194,7 @@
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
+      <c r="A23" s="135"/>
       <c r="B23" s="88"/>
       <c r="C23" s="67" t="s">
         <v>136</v>
@@ -13215,7 +13214,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="115"/>
+      <c r="A24" s="135"/>
       <c r="B24" s="88"/>
       <c r="C24" s="67" t="s">
         <v>110</v>
@@ -13230,7 +13229,7 @@
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="115"/>
+      <c r="A25" s="135"/>
       <c r="B25" s="89" t="s">
         <v>125</v>
       </c>
@@ -13250,7 +13249,7 @@
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="115"/>
+      <c r="A26" s="135"/>
       <c r="B26" s="88" t="s">
         <v>124</v>
       </c>
@@ -13270,7 +13269,7 @@
       <c r="G26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="116"/>
+      <c r="A27" s="136"/>
       <c r="B27" s="71" t="s">
         <v>118</v>
       </c>
@@ -13297,7 +13296,7 @@
       <c r="F28" s="96"/>
     </row>
     <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="114" t="s">
+      <c r="A29" s="134" t="s">
         <v>143</v>
       </c>
       <c r="B29" s="87"/>
@@ -13315,7 +13314,7 @@
       <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.3">
-      <c r="A30" s="115"/>
+      <c r="A30" s="135"/>
       <c r="B30" s="88" t="s">
         <v>145</v>
       </c>
@@ -13334,7 +13333,7 @@
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="115"/>
+      <c r="A31" s="135"/>
       <c r="B31" s="88" t="s">
         <v>146</v>
       </c>
@@ -13354,7 +13353,7 @@
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="115"/>
+      <c r="A32" s="135"/>
       <c r="B32" s="88" t="s">
         <v>149</v>
       </c>
@@ -13370,7 +13369,7 @@
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="116"/>
+      <c r="A33" s="136"/>
       <c r="B33" s="71" t="s">
         <v>150</v>
       </c>
@@ -13395,7 +13394,7 @@
       <c r="F34" s="96"/>
     </row>
     <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="137" t="s">
         <v>154</v>
       </c>
       <c r="B35" s="87"/>
@@ -13413,7 +13412,7 @@
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="118"/>
+      <c r="A36" s="138"/>
       <c r="B36" s="71" t="s">
         <v>155</v>
       </c>
@@ -13446,7 +13445,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="B1:I22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -13469,25 +13468,25 @@
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="27"/>
       <c r="C4" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>176</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -13495,24 +13494,22 @@
         <v>159</v>
       </c>
       <c r="C5" s="31">
-        <v>1150</v>
+        <v>773</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="38">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F5" s="25">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" s="39">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="H5" s="35">
-        <v>2</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>178</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I5" s="41"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
@@ -13525,15 +13522,15 @@
       <c r="E6" s="40">
         <v>53.2</v>
       </c>
-      <c r="F6" s="119" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="120"/>
+      <c r="F6" s="139" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="140"/>
       <c r="H6" s="32">
         <v>4</v>
       </c>
       <c r="I6" s="42" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -13544,11 +13541,11 @@
         <v>180</v>
       </c>
       <c r="D7" s="46"/>
-      <c r="E7" s="121" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" s="122"/>
-      <c r="G7" s="120"/>
+      <c r="E7" s="141" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="142"/>
+      <c r="G7" s="140"/>
       <c r="H7" s="32">
         <v>4</v>
       </c>
@@ -13575,12 +13572,12 @@
         <v>4</v>
       </c>
       <c r="I8" s="42" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
-        <v>163</v>
+      <c r="B9" s="144" t="s">
+        <v>198</v>
       </c>
       <c r="C9" s="33">
         <v>70</v>
@@ -13601,58 +13598,62 @@
       <c r="I9" s="42"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="29" t="s">
-        <v>164</v>
+      <c r="B10" s="144" t="s">
+        <v>197</v>
       </c>
       <c r="C10" s="33">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D10" s="46"/>
-      <c r="E10" s="40"/>
+      <c r="E10" s="40">
+        <v>38.700000000000003</v>
+      </c>
       <c r="F10" s="4">
-        <v>56</v>
+        <v>20.2</v>
       </c>
       <c r="G10" s="6">
-        <v>85</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="H10" s="32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" s="42"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="29" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C11" s="33">
-        <v>3000</v>
+        <v>37</v>
       </c>
       <c r="D11" s="46"/>
-      <c r="E11" s="40">
-        <v>230</v>
-      </c>
-      <c r="F11" s="4">
-        <v>300</v>
-      </c>
-      <c r="G11" s="6">
-        <v>200</v>
-      </c>
+      <c r="E11" s="40"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="32">
         <v>1</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="42" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C12" s="33">
+        <v>3000</v>
+      </c>
+      <c r="D12" s="46"/>
+      <c r="E12" s="40">
+        <v>230</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="6">
         <v>200</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6"/>
       <c r="H12" s="32">
         <v>1</v>
       </c>
@@ -13660,10 +13661,10 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="29" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C13" s="33">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="40"/>
@@ -13676,10 +13677,10 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C14" s="33">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="46"/>
       <c r="E14" s="40"/>
@@ -13692,10 +13693,10 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C15" s="33">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="46"/>
       <c r="E15" s="40"/>
@@ -13708,120 +13709,128 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="29" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C16" s="33">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="D16" s="46"/>
       <c r="E16" s="40"/>
       <c r="F16" s="4"/>
       <c r="G16" s="6"/>
       <c r="H16" s="32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="42"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="123" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="124">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="33">
+        <v>250</v>
+      </c>
+      <c r="D17" s="46"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="32">
+        <v>4</v>
+      </c>
+      <c r="I17" s="42"/>
+    </row>
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="104" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="105">
         <v>2000</v>
       </c>
-      <c r="D17" s="125"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="129">
+      <c r="D18" s="106"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="110">
         <v>1</v>
       </c>
-      <c r="I17" s="130"/>
+      <c r="I18" s="111"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="131" t="s">
+    <row r="19" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="112" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="27">
+        <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C11+C12+C13+C14+C15+C16+C17*H17</f>
+        <v>11939.8</v>
+      </c>
+      <c r="D19" s="113"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="117" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="118"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="12"/>
+      <c r="I20" s="119"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="120" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="139"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="121" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="121" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="121" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="121" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="27">
-        <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C10+C11+C12+C13+C14+C15+C16*H16</f>
-        <v>11160.8</v>
-      </c>
-      <c r="D18" s="132"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="136" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="137"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="138"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="140"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="138"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="142" t="s">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="119"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" s="144" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="142" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="145">
+      <c r="C22" s="123">
         <f>'Overall AC'!D36-0.05*'Overall AC'!D36</f>
         <v>0.52143447932973053</v>
       </c>
-      <c r="D21" s="145">
+      <c r="D22" s="123">
         <f>'Overall AC'!D36-0.1*'Overall AC'!D36</f>
         <v>0.4939905593650078</v>
       </c>
-      <c r="E21" s="143" t="s">
+      <c r="E22" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="143" t="s">
+      <c r="F22" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="143" t="s">
+      <c r="G22" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="143" t="s">
+      <c r="H22" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="144" t="s">
-        <v>190</v>
+      <c r="I22" s="122" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="E7:G7"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173B746A-BEF6-433C-B857-613A564B81A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74D14F6-5E5D-45E1-88DF-F65748F1327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="200">
   <si>
     <t>kg</t>
   </si>
@@ -1193,6 +1193,9 @@
   </si>
   <si>
     <t>servos motors</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1967,7 +1970,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
@@ -2147,7 +2149,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -2164,6 +2165,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2224,7 +2226,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11540,14 +11551,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>280035</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>159003</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>426819</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>106779</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>49529</xdr:rowOff>
     </xdr:to>
@@ -11572,8 +11583,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9324975" y="159003"/>
-          <a:ext cx="5313144" cy="4498721"/>
+          <a:off x="11892915" y="159003"/>
+          <a:ext cx="5313144" cy="4310126"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11983,273 +11994,273 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <v>15</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="92"/>
+      <c r="F9" s="91"/>
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="125"/>
-      <c r="B10" s="53" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="58">
+      <c r="C10" s="65"/>
+      <c r="D10" s="57">
         <v>14</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="93"/>
+      <c r="F10" s="92"/>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="125"/>
-      <c r="B11" s="53" t="s">
+      <c r="A11" s="124"/>
+      <c r="B11" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="58">
+      <c r="C11" s="65"/>
+      <c r="D11" s="57">
         <v>24</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="93"/>
+      <c r="F11" s="92"/>
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="125"/>
-      <c r="B12" s="53" t="s">
+      <c r="A12" s="124"/>
+      <c r="B12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="57">
         <v>1.4</v>
       </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="94" t="s">
+      <c r="E12" s="57"/>
+      <c r="F12" s="93" t="s">
         <v>55</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="125"/>
-      <c r="B13" s="54" t="s">
+      <c r="A13" s="124"/>
+      <c r="B13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="57">
         <f>(D11*D14)/D15</f>
         <v>500000</v>
       </c>
-      <c r="E13" s="58"/>
-      <c r="F13" s="93" t="s">
+      <c r="E13" s="57"/>
+      <c r="F13" s="92" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="125"/>
-      <c r="B14" s="53" t="s">
+      <c r="A14" s="124"/>
+      <c r="B14" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="57">
         <v>0.3</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="93"/>
+      <c r="F14" s="92"/>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="125"/>
-      <c r="B15" s="53" t="s">
+      <c r="A15" s="124"/>
+      <c r="B15" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="57">
         <v>1.4399999999999999E-5</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="94" t="s">
+      <c r="F15" s="93" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="125"/>
-      <c r="B16" s="53" t="s">
+      <c r="A16" s="124"/>
+      <c r="B16" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="57">
         <v>1.17</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="93" t="s">
+      <c r="F16" s="92" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="125"/>
-      <c r="B17" s="54" t="s">
+      <c r="A17" s="124"/>
+      <c r="B17" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="58">
         <f>(2*D9*Constants!C6)/(Wing!D16*Wing!D12*Wing!D10*Wing!D10)</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="93"/>
+      <c r="F17" s="92"/>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="125"/>
-      <c r="B18" s="54" t="s">
+      <c r="A18" s="124"/>
+      <c r="B18" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="59">
         <f>SQRT(D19*D17)</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="93"/>
+      <c r="F18" s="92"/>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="125"/>
-      <c r="B19" s="53" t="s">
+      <c r="A19" s="124"/>
+      <c r="B19" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="57">
         <v>10</v>
       </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="94" t="s">
+      <c r="E19" s="57"/>
+      <c r="F19" s="93" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="126"/>
-      <c r="B20" s="54" t="s">
+      <c r="A20" s="125"/>
+      <c r="B20" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="60">
         <f>0.25*D14</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="95" t="s">
+      <c r="F20" s="94" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="91" t="s">
+      <c r="G20" s="90" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="96"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="95"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="124" t="s">
+      <c r="A22" s="123" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="16"/>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D22" s="62">
         <f>D18/4</f>
         <v>0.75679105362627686</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="92"/>
+      <c r="F22" s="91"/>
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="125"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="14"/>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="57">
         <f>D14/4</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="93"/>
+      <c r="F23" s="92"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="126"/>
+      <c r="A24" s="125"/>
       <c r="B24" s="15"/>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="64">
+      <c r="D24" s="63">
         <f>0.05*D18</f>
         <v>0.15135821072525538</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="95" t="s">
+      <c r="F24" s="94" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="7"/>
@@ -12323,370 +12334,370 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <v>0.03</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="97" t="s">
+      <c r="E9" s="56"/>
+      <c r="F9" s="96" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="125"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="57">
         <v>0.9</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="93" t="s">
+      <c r="F10" s="92" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="126"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="125"/>
+      <c r="B11" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="72">
         <f>(D9*D12*D13)/D10</f>
         <v>9.2466982956369487E-2</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="E11" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="98"/>
+      <c r="F11" s="97"/>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="75">
         <f>Wing!D18</f>
         <v>3.0271642145051074</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="99"/>
+      <c r="F12" s="98"/>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="78">
         <f>Wing!D17</f>
         <v>0.91637231815803244</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="98"/>
+      <c r="F13" s="97"/>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="62"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="96"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="95"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="129" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="79">
         <v>0.5</v>
       </c>
-      <c r="E15" s="57"/>
-      <c r="F15" s="97" t="s">
+      <c r="E15" s="56"/>
+      <c r="F15" s="96" t="s">
         <v>42</v>
       </c>
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="131"/>
-      <c r="B16" s="53" t="s">
+      <c r="A16" s="130"/>
+      <c r="B16" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="57">
         <v>0.9</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="93" t="s">
+      <c r="F16" s="92" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="131"/>
-      <c r="B17" s="54" t="s">
+      <c r="A17" s="130"/>
+      <c r="B17" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="58">
         <f>(D15*Wing!D14*'V-tail'!D13)/'V-tail'!D16</f>
         <v>0.15272871969300542</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="93"/>
+      <c r="F17" s="92"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="132"/>
-      <c r="B18" s="103" t="s">
+      <c r="A18" s="131"/>
+      <c r="B18" s="102" t="s">
         <v>195</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="79">
+      <c r="D18" s="78">
         <v>0.78129899999999997</v>
       </c>
-      <c r="E18" s="61" t="s">
+      <c r="E18" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="98"/>
+      <c r="F18" s="97"/>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="62"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="96"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="95"/>
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="82">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="92"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="128"/>
-      <c r="B21" s="54" t="s">
+      <c r="A21" s="127"/>
+      <c r="B21" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="58">
         <f>D17+D11</f>
         <v>0.2451957026493749</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="93"/>
+      <c r="F21" s="92"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="128"/>
-      <c r="B22" s="53" t="s">
+      <c r="A22" s="127"/>
+      <c r="B22" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="57">
         <v>4</v>
       </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="94" t="s">
+      <c r="E22" s="57"/>
+      <c r="F22" s="93" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="128"/>
-      <c r="B23" s="54" t="s">
+      <c r="A23" s="127"/>
+      <c r="B23" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="84">
+      <c r="D23" s="83">
         <f>SQRT(D21*D22)</f>
         <v>0.99034479379532236</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="93"/>
+      <c r="F23" s="92"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="128"/>
-      <c r="B24" s="54" t="s">
+      <c r="A24" s="127"/>
+      <c r="B24" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="84">
+      <c r="D24" s="83">
         <f>D23/D22</f>
         <v>0.24758619844883059</v>
       </c>
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="93"/>
+      <c r="F24" s="92"/>
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="128"/>
-      <c r="B25" s="53" t="s">
+      <c r="A25" s="127"/>
+      <c r="B25" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="57">
         <v>0</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="93" t="s">
+      <c r="E25" s="57"/>
+      <c r="F25" s="92" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="129"/>
-      <c r="B26" s="85" t="s">
+      <c r="A26" s="128"/>
+      <c r="B26" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="60">
         <v>-10</v>
       </c>
-      <c r="E26" s="61" t="s">
+      <c r="E26" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="95" t="s">
+      <c r="F26" s="94" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="96"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="95"/>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="127" t="s">
+      <c r="A28" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="63"/>
-      <c r="E28" s="57" t="s">
+      <c r="D28" s="62"/>
+      <c r="E28" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="92" t="s">
+      <c r="F28" s="91" t="s">
         <v>88</v>
       </c>
       <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="128"/>
-      <c r="B29" s="53" t="s">
+      <c r="A29" s="127"/>
+      <c r="B29" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="83">
         <f>0.4*D24</f>
         <v>9.9034479379532248E-2</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="94" t="s">
+      <c r="F29" s="93" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="129"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="128"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="61">
+      <c r="D30" s="60">
         <v>0</v>
       </c>
-      <c r="E30" s="61" t="s">
+      <c r="E30" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="95" t="s">
+      <c r="F30" s="94" t="s">
         <v>95</v>
       </c>
       <c r="G30" s="7"/>
@@ -12752,44 +12763,44 @@
       <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="51" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="132" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="57">
         <f>1.5*Wing!D14</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="94" t="s">
+      <c r="F9" s="93" t="s">
         <v>193</v>
       </c>
       <c r="G9" s="9" t="s">
@@ -12797,21 +12808,21 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="131"/>
-      <c r="B10" s="53" t="s">
+      <c r="A10" s="130"/>
+      <c r="B10" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="57">
         <f>3*Wing!D14</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="93" t="s">
+      <c r="F10" s="92" t="s">
         <v>107</v>
       </c>
       <c r="G10" s="9" t="s">
@@ -12819,57 +12830,57 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="54" t="s">
+      <c r="A11" s="130"/>
+      <c r="B11" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="83">
         <f>D9+D10+Wing!D14</f>
         <v>1.65</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="93"/>
+      <c r="F11" s="92"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="131"/>
-      <c r="B12" s="53" t="s">
+      <c r="A12" s="130"/>
+      <c r="B12" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="59">
         <v>0.3</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="94" t="s">
+      <c r="F12" s="93" t="s">
         <v>171</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="132"/>
-      <c r="B13" s="55" t="s">
+      <c r="A13" s="131"/>
+      <c r="B13" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="60">
         <v>0.1</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="97" t="s">
         <v>191</v>
       </c>
       <c r="G13" s="10"/>
@@ -12955,478 +12966,478 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="65" t="s">
+      <c r="B9" s="86"/>
+      <c r="C9" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <f>(Fuselage!D9+(Wing!$D$14*0.25))/Wing!$D$14</f>
         <v>1.7499999999999998</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="97"/>
+      <c r="F9" s="96"/>
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="67" t="s">
+      <c r="A10" s="134"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="59">
         <f>-D11*D9</f>
         <v>-9.6764591226254897</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="93"/>
+      <c r="F10" s="92"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="135"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="67" t="s">
+      <c r="A11" s="134"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="59">
         <f>(2*(22/7)*Wing!D19)/(2+(SQRT((Wing!D19^2)*('Overall AC'!D13)/'Overall AC'!D14+4)))</f>
         <v>5.529405212928852</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="102" t="s">
+      <c r="G11" s="101" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="135"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="67" t="s">
+      <c r="A12" s="134"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="59">
         <v>0</v>
       </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="100" t="s">
+      <c r="E12" s="57"/>
+      <c r="F12" s="99" t="s">
         <v>128</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="135"/>
-      <c r="B13" s="89" t="s">
+      <c r="A13" s="134"/>
+      <c r="B13" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="58">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="100" t="s">
+      <c r="F13" s="99" t="s">
         <v>126</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="135"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="134"/>
+      <c r="B14" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="59">
         <f>(1+0.75*D15)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="99" t="s">
         <v>129</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="71" t="s">
+      <c r="A15" s="135"/>
+      <c r="B15" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="63">
         <f>(0.12*0.3)/0.3</f>
         <v>0.12</v>
       </c>
-      <c r="E15" s="61" t="s">
+      <c r="E15" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="101" t="s">
+      <c r="F15" s="100" t="s">
         <v>123</v>
       </c>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="62"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="96"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="95"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="134" t="s">
+      <c r="A17" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="65" t="s">
+      <c r="B17" s="86"/>
+      <c r="C17" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="82">
         <f>(D18+(0.25*'V-tail'!D24))/'V-tail'!D24</f>
         <v>5.9143456312893408</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="97"/>
+      <c r="F17" s="96"/>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="135"/>
-      <c r="B18" s="88" t="s">
+      <c r="A18" s="134"/>
+      <c r="B18" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="59">
         <f>Fuselage!D11-'V-tail'!D24</f>
         <v>1.4024138015511693</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="94" t="s">
+      <c r="F18" s="93" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="135"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="67" t="s">
+      <c r="A19" s="134"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="60">
+      <c r="D19" s="59">
         <f>-(D20*D21*D22)*D23*D17</f>
         <v>-2.5300219037859915</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="93"/>
+      <c r="F19" s="92"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="135"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="67" t="s">
+      <c r="A20" s="134"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="60">
+      <c r="D20" s="59">
         <v>0.9</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="94" t="s">
+      <c r="F20" s="93" t="s">
         <v>138</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="135"/>
-      <c r="B21" s="88"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="134"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="60">
+      <c r="D21" s="59">
         <v>0.7</v>
       </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="94" t="s">
+      <c r="E21" s="57"/>
+      <c r="F21" s="93" t="s">
         <v>138</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="135"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="134"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="60">
+      <c r="D22" s="59">
         <f>'V-tail'!D17/Wing!D17</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F22" s="93"/>
+      <c r="F22" s="92"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="135"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="134"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="60">
+      <c r="D23" s="59">
         <f>(2*(22/7)*'V-tail'!D22)/(2+(SQRT(('V-tail'!D22^2)*('Overall AC'!D25)/'Overall AC'!D26+4)))</f>
         <v>4.0740680719180196</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="100" t="s">
+      <c r="F23" s="99" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="102" t="s">
+      <c r="G23" s="101" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="135"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="67" t="s">
+      <c r="A24" s="134"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="59">
         <v>0</v>
       </c>
-      <c r="E24" s="58"/>
-      <c r="F24" s="100" t="s">
+      <c r="E24" s="57"/>
+      <c r="F24" s="99" t="s">
         <v>142</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="135"/>
-      <c r="B25" s="89" t="s">
+      <c r="A25" s="134"/>
+      <c r="B25" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="58">
         <f>1-(0.07)^2</f>
         <v>0.99509999999999998</v>
       </c>
-      <c r="E25" s="59" t="s">
+      <c r="E25" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="100" t="s">
+      <c r="F25" s="99" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="135"/>
-      <c r="B26" s="88" t="s">
+      <c r="A26" s="134"/>
+      <c r="B26" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="60">
+      <c r="D26" s="59">
         <f>(1+0.75*D27)^2</f>
         <v>1.1881000000000002</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="100" t="s">
+      <c r="F26" s="99" t="s">
         <v>129</v>
       </c>
       <c r="G26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="136"/>
-      <c r="B27" s="71" t="s">
+      <c r="A27" s="135"/>
+      <c r="B27" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="64">
+      <c r="D27" s="63">
         <f>(0.12*0.248)/0.248</f>
         <v>0.12</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="E27" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="101" t="s">
+      <c r="F27" s="100" t="s">
         <v>123</v>
       </c>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="96"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="95"/>
     </row>
     <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="134" t="s">
+      <c r="A29" s="133" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="87"/>
-      <c r="C29" s="65" t="s">
+      <c r="B29" s="86"/>
+      <c r="C29" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="82">
         <f>45*((D30*(D31^2)*Fuselage!D11)/Wing!D14*Wing!D17)</f>
         <v>0.20412193386970173</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="92"/>
+      <c r="F29" s="91"/>
       <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.3">
-      <c r="A30" s="135"/>
-      <c r="B30" s="88" t="s">
+      <c r="A30" s="134"/>
+      <c r="B30" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="67" t="s">
+      <c r="C30" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="57">
         <v>0.01</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="100" t="s">
+      <c r="F30" s="99" t="s">
         <v>152</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="135"/>
-      <c r="B31" s="88" t="s">
+      <c r="A31" s="134"/>
+      <c r="B31" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="65" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="60">
+      <c r="D31" s="59">
         <f>Fuselage!D12</f>
         <v>0.3</v>
       </c>
-      <c r="E31" s="58" t="s">
+      <c r="E31" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="100" t="s">
+      <c r="F31" s="99" t="s">
         <v>153</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="135"/>
-      <c r="B32" s="88" t="s">
+      <c r="A32" s="134"/>
+      <c r="B32" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="60">
+      <c r="C32" s="65"/>
+      <c r="D32" s="59">
         <f>D33/Fuselage!D11</f>
         <v>0.31818181818181812</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="93"/>
+      <c r="F32" s="92"/>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="136"/>
-      <c r="B33" s="71" t="s">
+      <c r="A33" s="135"/>
+      <c r="B33" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="60">
         <f>Fuselage!D9+Wing!D14*0.25</f>
         <v>0.52499999999999991</v>
       </c>
-      <c r="E33" s="61" t="s">
+      <c r="E33" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="98"/>
+      <c r="F33" s="97"/>
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="96"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="95"/>
     </row>
     <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="137" t="s">
+      <c r="A35" s="136" t="s">
         <v>154</v>
       </c>
-      <c r="B35" s="87"/>
-      <c r="C35" s="65" t="s">
+      <c r="B35" s="86"/>
+      <c r="C35" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="83">
+      <c r="D35" s="82">
         <f>(D10-D29+D19)/D11+D23</f>
         <v>1.8295946643148437</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="92"/>
+      <c r="F35" s="91"/>
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="138"/>
-      <c r="B36" s="71" t="s">
+      <c r="A36" s="137"/>
+      <c r="B36" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="90">
+      <c r="D36" s="89">
         <f>D35*0.3</f>
         <v>0.54887839929445315</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="95" t="s">
+      <c r="F36" s="94" t="s">
         <v>158</v>
       </c>
       <c r="G36" s="7"/>
@@ -13445,7 +13456,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
-  <dimension ref="B1:I22"/>
+  <dimension ref="B1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -13458,14 +13469,14 @@
     <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B1" s="43"/>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="42"/>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="44"/>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="43"/>
     </row>
-    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="27"/>
       <c r="C4" s="30" t="s">
         <v>175</v>
@@ -13485,18 +13496,21 @@
       <c r="H4" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="143" t="s">
         <v>176</v>
       </c>
+      <c r="J4" s="144" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="28" t="s">
         <v>159</v>
       </c>
       <c r="C5" s="31">
         <v>773</v>
       </c>
-      <c r="D5" s="45"/>
+      <c r="D5" s="44"/>
       <c r="E5" s="38">
         <v>51</v>
       </c>
@@ -13509,56 +13523,59 @@
       <c r="H5" s="35">
         <v>4</v>
       </c>
-      <c r="I5" s="41"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>160</v>
       </c>
       <c r="C6" s="33">
         <v>142.69999999999999</v>
       </c>
-      <c r="D6" s="46"/>
+      <c r="D6" s="45"/>
       <c r="E6" s="40">
         <v>53.2</v>
       </c>
-      <c r="F6" s="139" t="s">
+      <c r="F6" s="138" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="140"/>
+      <c r="G6" s="139"/>
       <c r="H6" s="32">
         <v>4</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="41" t="s">
         <v>177</v>
       </c>
+      <c r="J6" s="33"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="29" t="s">
         <v>161</v>
       </c>
       <c r="C7" s="33">
         <v>180</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="141" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="140" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="142"/>
-      <c r="G7" s="140"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="139"/>
       <c r="H7" s="32">
         <v>4</v>
       </c>
-      <c r="I7" s="42"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="33"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
         <v>162</v>
       </c>
       <c r="C8" s="33">
         <v>110</v>
       </c>
-      <c r="D8" s="46"/>
+      <c r="D8" s="45"/>
       <c r="E8" s="40">
         <v>19.5</v>
       </c>
@@ -13571,18 +13588,19 @@
       <c r="H8" s="32">
         <v>4</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="41" t="s">
         <v>181</v>
       </c>
+      <c r="J8" s="33"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="144" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="122" t="s">
         <v>198</v>
       </c>
       <c r="C9" s="33">
         <v>70</v>
       </c>
-      <c r="D9" s="46"/>
+      <c r="D9" s="45"/>
       <c r="E9" s="40">
         <v>38.700000000000003</v>
       </c>
@@ -13595,16 +13613,17 @@
       <c r="H9" s="32">
         <v>4</v>
       </c>
-      <c r="I9" s="42"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="33"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="144" t="s">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="122" t="s">
         <v>197</v>
       </c>
       <c r="C10" s="33">
         <v>70</v>
       </c>
-      <c r="D10" s="46"/>
+      <c r="D10" s="45"/>
       <c r="E10" s="40">
         <v>38.700000000000003</v>
       </c>
@@ -13617,34 +13636,36 @@
       <c r="H10" s="32">
         <v>4</v>
       </c>
-      <c r="I10" s="42"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="33"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="29" t="s">
         <v>163</v>
       </c>
       <c r="C11" s="33">
         <v>37</v>
       </c>
-      <c r="D11" s="46"/>
+      <c r="D11" s="45"/>
       <c r="E11" s="40"/>
       <c r="F11" s="4"/>
       <c r="G11" s="6"/>
       <c r="H11" s="32">
         <v>1</v>
       </c>
-      <c r="I11" s="42" t="s">
+      <c r="I11" s="41" t="s">
         <v>196</v>
       </c>
+      <c r="J11" s="33"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="29" t="s">
         <v>164</v>
       </c>
       <c r="C12" s="33">
         <v>3000</v>
       </c>
-      <c r="D12" s="46"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="40">
         <v>230</v>
       </c>
@@ -13657,172 +13678,180 @@
       <c r="H12" s="32">
         <v>1</v>
       </c>
-      <c r="I12" s="42"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="29" t="s">
         <v>165</v>
       </c>
       <c r="C13" s="33">
         <v>200</v>
       </c>
-      <c r="D13" s="46"/>
+      <c r="D13" s="45"/>
       <c r="E13" s="40"/>
       <c r="F13" s="4"/>
       <c r="G13" s="6"/>
       <c r="H13" s="32">
         <v>1</v>
       </c>
-      <c r="I13" s="42"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="33"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="29" t="s">
         <v>184</v>
       </c>
       <c r="C14" s="33">
         <v>1200</v>
       </c>
-      <c r="D14" s="46"/>
+      <c r="D14" s="45"/>
       <c r="E14" s="40"/>
       <c r="F14" s="4"/>
       <c r="G14" s="6"/>
       <c r="H14" s="32">
         <v>1</v>
       </c>
-      <c r="I14" s="42"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="33"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>185</v>
       </c>
       <c r="C15" s="33">
         <v>1000</v>
       </c>
-      <c r="D15" s="46"/>
+      <c r="D15" s="45"/>
       <c r="E15" s="40"/>
       <c r="F15" s="4"/>
       <c r="G15" s="6"/>
       <c r="H15" s="32">
         <v>1</v>
       </c>
-      <c r="I15" s="42"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="33"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="29" t="s">
         <v>186</v>
       </c>
       <c r="C16" s="33">
         <v>400</v>
       </c>
-      <c r="D16" s="46"/>
+      <c r="D16" s="45"/>
       <c r="E16" s="40"/>
       <c r="F16" s="4"/>
       <c r="G16" s="6"/>
       <c r="H16" s="32">
         <v>1</v>
       </c>
-      <c r="I16" s="42"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="33"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>166</v>
       </c>
       <c r="C17" s="33">
         <v>250</v>
       </c>
-      <c r="D17" s="46"/>
+      <c r="D17" s="45"/>
       <c r="E17" s="40"/>
       <c r="F17" s="4"/>
       <c r="G17" s="6"/>
       <c r="H17" s="32">
         <v>4</v>
       </c>
-      <c r="I17" s="42"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="33"/>
     </row>
-    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="104" t="s">
+    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="105">
+      <c r="C18" s="104">
         <v>2000</v>
       </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="110">
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="109">
         <v>1</v>
       </c>
-      <c r="I18" s="111"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="148"/>
     </row>
-    <row r="19" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="112" t="s">
+    <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="110" t="s">
         <v>187</v>
       </c>
       <c r="C19" s="27">
         <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C11+C12+C13+C14+C15+C16+C17*H17</f>
         <v>11939.8</v>
       </c>
-      <c r="D19" s="113"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="117" t="s">
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="115" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="118"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="27"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="12"/>
-      <c r="I20" s="119"/>
+      <c r="I20" s="117"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="120" t="s">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="139"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="121" t="s">
+      <c r="C21" s="138"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="121" t="s">
+      <c r="F21" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="121" t="s">
+      <c r="G21" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="121" t="s">
+      <c r="H21" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="120" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="120" t="s">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="123">
+      <c r="C22" s="121">
         <f>'Overall AC'!D36-0.05*'Overall AC'!D36</f>
         <v>0.52143447932973053</v>
       </c>
-      <c r="D22" s="123">
+      <c r="D22" s="121">
         <f>'Overall AC'!D36-0.1*'Overall AC'!D36</f>
         <v>0.4939905593650078</v>
       </c>
-      <c r="E22" s="121" t="s">
+      <c r="E22" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="F22" s="121" t="s">
+      <c r="F22" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="121" t="s">
+      <c r="G22" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="121" t="s">
+      <c r="H22" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="122" t="s">
+      <c r="I22" s="120" t="s">
         <v>188</v>
       </c>
     </row>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74D14F6-5E5D-45E1-88DF-F65748F1327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02002259-6CDD-402B-985A-F138DDD3CF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="202">
   <si>
     <t>kg</t>
   </si>
@@ -1186,9 +1186,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Arduino Mega 2560 </t>
-  </si>
-  <si>
     <t>servos flight controls</t>
   </si>
   <si>
@@ -1196,15 +1193,25 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>with respect to the horizon</t>
+  </si>
+  <si>
+    <t>This is the whole V-tail span. Half span is 0.495</t>
+  </si>
+  <si>
+    <t>Arduino Mega 2560 (ArduPilot)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1896,7 +1903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2125,9 +2132,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2166,6 +2170,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2226,16 +2237,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4051,8 +4073,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>441959</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>124918</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>142847</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11994,7 +12016,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="123" t="s">
+      <c r="A9" s="127" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="55" t="s">
@@ -12013,7 +12035,7 @@
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="124"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="52" t="s">
         <v>52</v>
       </c>
@@ -12028,7 +12050,7 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
+      <c r="A11" s="128"/>
       <c r="B11" s="52" t="s">
         <v>51</v>
       </c>
@@ -12043,7 +12065,7 @@
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="124"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="52" t="s">
         <v>20</v>
       </c>
@@ -12060,7 +12082,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="124"/>
+      <c r="A13" s="128"/>
       <c r="B13" s="53" t="s">
         <v>19</v>
       </c>
@@ -12078,7 +12100,7 @@
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="124"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="52" t="s">
         <v>15</v>
       </c>
@@ -12095,7 +12117,7 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="124"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="52" t="s">
         <v>16</v>
       </c>
@@ -12114,7 +12136,7 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="124"/>
+      <c r="A16" s="128"/>
       <c r="B16" s="52" t="s">
         <v>5</v>
       </c>
@@ -12133,7 +12155,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124"/>
+      <c r="A17" s="128"/>
       <c r="B17" s="53" t="s">
         <v>11</v>
       </c>
@@ -12151,7 +12173,7 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="124"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="53" t="s">
         <v>27</v>
       </c>
@@ -12169,7 +12191,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="124"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="52" t="s">
         <v>29</v>
       </c>
@@ -12186,7 +12208,7 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="125"/>
+      <c r="A20" s="129"/>
       <c r="B20" s="53" t="s">
         <v>98</v>
       </c>
@@ -12214,7 +12236,7 @@
       <c r="F21" s="95"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="127" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="16"/>
@@ -12232,7 +12254,7 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="124"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="14"/>
       <c r="C23" s="66" t="s">
         <v>80</v>
@@ -12248,7 +12270,7 @@
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="125"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="15"/>
       <c r="C24" s="67" t="s">
         <v>81</v>
@@ -12334,7 +12356,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="123" t="s">
+      <c r="A9" s="127" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="68" t="s">
@@ -12347,13 +12369,13 @@
         <v>0.03</v>
       </c>
       <c r="E9" s="56"/>
-      <c r="F9" s="96" t="s">
+      <c r="F9" s="149" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="124"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="69" t="s">
         <v>62</v>
       </c>
@@ -12366,13 +12388,13 @@
       <c r="E10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="92" t="s">
+      <c r="F10" s="150" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="125"/>
+      <c r="A11" s="129"/>
       <c r="B11" s="70" t="s">
         <v>63</v>
       </c>
@@ -12386,7 +12408,7 @@
       <c r="E11" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="97"/>
+      <c r="F11" s="151"/>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -12403,7 +12425,7 @@
       <c r="E12" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="98"/>
+      <c r="F12" s="152"/>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -12420,7 +12442,7 @@
       <c r="E13" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="97"/>
+      <c r="F13" s="151"/>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -12428,11 +12450,11 @@
       <c r="C14" s="46"/>
       <c r="D14" s="61"/>
       <c r="E14" s="61"/>
-      <c r="F14" s="95"/>
+      <c r="F14" s="153"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="129" t="s">
+      <c r="A15" s="133" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="85" t="s">
@@ -12445,13 +12467,13 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="56"/>
-      <c r="F15" s="96" t="s">
+      <c r="F15" s="149" t="s">
         <v>42</v>
       </c>
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="130"/>
+      <c r="A16" s="134"/>
       <c r="B16" s="52" t="s">
         <v>58</v>
       </c>
@@ -12464,13 +12486,13 @@
       <c r="E16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="92" t="s">
+      <c r="F16" s="150" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="130"/>
+      <c r="A17" s="134"/>
       <c r="B17" s="53" t="s">
         <v>59</v>
       </c>
@@ -12484,12 +12506,12 @@
       <c r="E17" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="92"/>
+      <c r="F17" s="150"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="131"/>
-      <c r="B18" s="102" t="s">
+      <c r="A18" s="135"/>
+      <c r="B18" s="101" t="s">
         <v>195</v>
       </c>
       <c r="C18" s="67" t="s">
@@ -12501,7 +12523,7 @@
       <c r="E18" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="97"/>
+      <c r="F18" s="151"/>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -12509,11 +12531,11 @@
       <c r="C19" s="47"/>
       <c r="D19" s="80"/>
       <c r="E19" s="61"/>
-      <c r="F19" s="95"/>
+      <c r="F19" s="153"/>
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="130" t="s">
         <v>92</v>
       </c>
       <c r="B20" s="81" t="s">
@@ -12522,18 +12544,20 @@
       <c r="C20" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="82">
+      <c r="D20" s="147">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
       <c r="E20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="91"/>
+      <c r="F20" s="148" t="s">
+        <v>199</v>
+      </c>
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="127"/>
+      <c r="A21" s="131"/>
       <c r="B21" s="53" t="s">
         <v>56</v>
       </c>
@@ -12547,11 +12571,11 @@
       <c r="E21" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="92"/>
+      <c r="F21" s="150"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="127"/>
+      <c r="A22" s="131"/>
       <c r="B22" s="52" t="s">
         <v>29</v>
       </c>
@@ -12562,13 +12586,13 @@
         <v>4</v>
       </c>
       <c r="E22" s="57"/>
-      <c r="F22" s="93" t="s">
+      <c r="F22" s="98" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="127"/>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="131"/>
       <c r="B23" s="53" t="s">
         <v>66</v>
       </c>
@@ -12582,11 +12606,13 @@
       <c r="E23" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="92"/>
+      <c r="F23" s="98" t="s">
+        <v>200</v>
+      </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="127"/>
+      <c r="A24" s="131"/>
       <c r="B24" s="53" t="s">
         <v>68</v>
       </c>
@@ -12600,11 +12626,11 @@
       <c r="E24" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="92"/>
+      <c r="F24" s="150"/>
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="127"/>
+      <c r="A25" s="131"/>
       <c r="B25" s="52" t="s">
         <v>70</v>
       </c>
@@ -12615,13 +12641,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="57"/>
-      <c r="F25" s="92" t="s">
+      <c r="F25" s="150" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="128"/>
+      <c r="A26" s="132"/>
       <c r="B26" s="84" t="s">
         <v>75</v>
       </c>
@@ -12634,7 +12660,7 @@
       <c r="E26" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="94" t="s">
+      <c r="F26" s="99" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="7"/>
@@ -12644,10 +12670,10 @@
       <c r="C27" s="61"/>
       <c r="D27" s="61"/>
       <c r="E27" s="61"/>
-      <c r="F27" s="95"/>
+      <c r="F27" s="153"/>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
+      <c r="A28" s="130" t="s">
         <v>83</v>
       </c>
       <c r="B28" s="85" t="s">
@@ -12660,13 +12686,13 @@
       <c r="E28" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="91" t="s">
+      <c r="F28" s="148" t="s">
         <v>88</v>
       </c>
       <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="127"/>
+      <c r="A29" s="131"/>
       <c r="B29" s="52" t="s">
         <v>94</v>
       </c>
@@ -12680,13 +12706,13 @@
       <c r="E29" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="93" t="s">
+      <c r="F29" s="98" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="128"/>
+      <c r="A30" s="132"/>
       <c r="B30" s="84"/>
       <c r="C30" s="67" t="s">
         <v>86</v>
@@ -12697,7 +12723,7 @@
       <c r="E30" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="94" t="s">
+      <c r="F30" s="99" t="s">
         <v>95</v>
       </c>
       <c r="G30" s="7"/>
@@ -12784,7 +12810,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="132" t="s">
+      <c r="A9" s="136" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="52" t="s">
@@ -12808,7 +12834,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="130"/>
+      <c r="A10" s="134"/>
       <c r="B10" s="52" t="s">
         <v>102</v>
       </c>
@@ -12830,7 +12856,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="130"/>
+      <c r="A11" s="134"/>
       <c r="B11" s="53" t="s">
         <v>104</v>
       </c>
@@ -12848,7 +12874,7 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="130"/>
+      <c r="A12" s="134"/>
       <c r="B12" s="52" t="s">
         <v>108</v>
       </c>
@@ -12867,7 +12893,7 @@
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="131"/>
+      <c r="A13" s="135"/>
       <c r="B13" s="54" t="s">
         <v>192</v>
       </c>
@@ -12966,7 +12992,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="137" t="s">
         <v>109</v>
       </c>
       <c r="B9" s="86"/>
@@ -12984,7 +13010,7 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="134"/>
+      <c r="A10" s="138"/>
       <c r="B10" s="87"/>
       <c r="C10" s="66" t="s">
         <v>113</v>
@@ -13000,7 +13026,7 @@
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="134"/>
+      <c r="A11" s="138"/>
       <c r="B11" s="87"/>
       <c r="C11" s="66" t="s">
         <v>117</v>
@@ -13012,15 +13038,15 @@
       <c r="E11" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="99" t="s">
+      <c r="F11" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="101" t="s">
+      <c r="G11" s="100" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="134"/>
+      <c r="A12" s="138"/>
       <c r="B12" s="87"/>
       <c r="C12" s="66" t="s">
         <v>110</v>
@@ -13029,13 +13055,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="57"/>
-      <c r="F12" s="99" t="s">
+      <c r="F12" s="98" t="s">
         <v>128</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="134"/>
+      <c r="A13" s="138"/>
       <c r="B13" s="88" t="s">
         <v>125</v>
       </c>
@@ -13049,13 +13075,13 @@
       <c r="E13" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="F13" s="98" t="s">
         <v>126</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="134"/>
+      <c r="A14" s="138"/>
       <c r="B14" s="87" t="s">
         <v>124</v>
       </c>
@@ -13069,13 +13095,13 @@
       <c r="E14" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="99" t="s">
+      <c r="F14" s="98" t="s">
         <v>129</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="135"/>
+      <c r="A15" s="139"/>
       <c r="B15" s="70" t="s">
         <v>118</v>
       </c>
@@ -13089,7 +13115,7 @@
       <c r="E15" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="100" t="s">
+      <c r="F15" s="99" t="s">
         <v>123</v>
       </c>
       <c r="G15" s="10"/>
@@ -13103,7 +13129,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="137" t="s">
         <v>130</v>
       </c>
       <c r="B17" s="86"/>
@@ -13121,7 +13147,7 @@
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="134"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="87" t="s">
         <v>132</v>
       </c>
@@ -13141,7 +13167,7 @@
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="134"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="87"/>
       <c r="C19" s="66" t="s">
         <v>135</v>
@@ -13157,7 +13183,7 @@
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="134"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="87"/>
       <c r="C20" s="66" t="s">
         <v>139</v>
@@ -13174,7 +13200,7 @@
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="134"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="87"/>
       <c r="C21" s="66" t="s">
         <v>140</v>
@@ -13189,7 +13215,7 @@
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="134"/>
+      <c r="A22" s="138"/>
       <c r="B22" s="87"/>
       <c r="C22" s="66" t="s">
         <v>141</v>
@@ -13205,7 +13231,7 @@
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="134"/>
+      <c r="A23" s="138"/>
       <c r="B23" s="87"/>
       <c r="C23" s="66" t="s">
         <v>136</v>
@@ -13217,15 +13243,15 @@
       <c r="E23" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="99" t="s">
+      <c r="F23" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="101" t="s">
+      <c r="G23" s="100" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="134"/>
+      <c r="A24" s="138"/>
       <c r="B24" s="87"/>
       <c r="C24" s="66" t="s">
         <v>110</v>
@@ -13234,13 +13260,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="57"/>
-      <c r="F24" s="99" t="s">
+      <c r="F24" s="98" t="s">
         <v>142</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="134"/>
+      <c r="A25" s="138"/>
       <c r="B25" s="88" t="s">
         <v>125</v>
       </c>
@@ -13254,13 +13280,13 @@
       <c r="E25" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="99" t="s">
+      <c r="F25" s="98" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="134"/>
+      <c r="A26" s="138"/>
       <c r="B26" s="87" t="s">
         <v>124</v>
       </c>
@@ -13274,13 +13300,13 @@
       <c r="E26" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="99" t="s">
+      <c r="F26" s="98" t="s">
         <v>129</v>
       </c>
       <c r="G26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="135"/>
+      <c r="A27" s="139"/>
       <c r="B27" s="70" t="s">
         <v>118</v>
       </c>
@@ -13294,7 +13320,7 @@
       <c r="E27" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="100" t="s">
+      <c r="F27" s="99" t="s">
         <v>123</v>
       </c>
       <c r="G27" s="10"/>
@@ -13307,7 +13333,7 @@
       <c r="F28" s="95"/>
     </row>
     <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="133" t="s">
+      <c r="A29" s="137" t="s">
         <v>143</v>
       </c>
       <c r="B29" s="86"/>
@@ -13325,7 +13351,7 @@
       <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.3">
-      <c r="A30" s="134"/>
+      <c r="A30" s="138"/>
       <c r="B30" s="87" t="s">
         <v>145</v>
       </c>
@@ -13338,13 +13364,13 @@
       <c r="E30" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="99" t="s">
+      <c r="F30" s="98" t="s">
         <v>152</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="134"/>
+      <c r="A31" s="138"/>
       <c r="B31" s="87" t="s">
         <v>146</v>
       </c>
@@ -13358,13 +13384,13 @@
       <c r="E31" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="99" t="s">
+      <c r="F31" s="98" t="s">
         <v>153</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="134"/>
+      <c r="A32" s="138"/>
       <c r="B32" s="87" t="s">
         <v>149</v>
       </c>
@@ -13380,7 +13406,7 @@
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="135"/>
+      <c r="A33" s="139"/>
       <c r="B33" s="70" t="s">
         <v>150</v>
       </c>
@@ -13405,7 +13431,7 @@
       <c r="F34" s="95"/>
     </row>
     <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="136" t="s">
+      <c r="A35" s="140" t="s">
         <v>154</v>
       </c>
       <c r="B35" s="86"/>
@@ -13423,7 +13449,7 @@
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="137"/>
+      <c r="A36" s="141"/>
       <c r="B36" s="70" t="s">
         <v>155</v>
       </c>
@@ -13496,11 +13522,11 @@
       <c r="H4" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="143" t="s">
+      <c r="I4" s="122" t="s">
         <v>176</v>
       </c>
-      <c r="J4" s="144" t="s">
-        <v>199</v>
+      <c r="J4" s="30" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -13523,8 +13549,8 @@
       <c r="H5" s="35">
         <v>4</v>
       </c>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
@@ -13537,10 +13563,10 @@
       <c r="E6" s="40">
         <v>53.2</v>
       </c>
-      <c r="F6" s="138" t="s">
+      <c r="F6" s="142" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="139"/>
+      <c r="G6" s="143"/>
       <c r="H6" s="32">
         <v>4</v>
       </c>
@@ -13557,11 +13583,11 @@
         <v>180</v>
       </c>
       <c r="D7" s="45"/>
-      <c r="E7" s="140" t="s">
+      <c r="E7" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="141"/>
-      <c r="G7" s="139"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="143"/>
       <c r="H7" s="32">
         <v>4</v>
       </c>
@@ -13594,8 +13620,8 @@
       <c r="J8" s="33"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="122" t="s">
-        <v>198</v>
+      <c r="B9" s="121" t="s">
+        <v>197</v>
       </c>
       <c r="C9" s="33">
         <v>70</v>
@@ -13617,8 +13643,8 @@
       <c r="J9" s="33"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="122" t="s">
-        <v>197</v>
+      <c r="B10" s="121" t="s">
+        <v>196</v>
       </c>
       <c r="C10" s="33">
         <v>70</v>
@@ -13654,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J11" s="33"/>
     </row>
@@ -13767,91 +13793,91 @@
       <c r="J17" s="33"/>
     </row>
     <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="104">
+      <c r="C18" s="103">
         <v>2000</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="109">
+      <c r="D18" s="104"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="108">
         <v>1</v>
       </c>
-      <c r="I18" s="146"/>
-      <c r="J18" s="148"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="126"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="110" t="s">
+      <c r="B19" s="109" t="s">
         <v>187</v>
       </c>
       <c r="C19" s="27">
         <f>C5*H5+C6*H6+C7*H7+C8*H8+C9*H9+C11+C12+C13+C14+C15+C16+C17*H17</f>
         <v>11939.8</v>
       </c>
-      <c r="D19" s="111"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="115" t="s">
+      <c r="D19" s="110"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="116"/>
+      <c r="I19" s="115"/>
       <c r="J19" s="27"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="12"/>
-      <c r="I20" s="117"/>
+      <c r="I20" s="116"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="118" t="s">
+      <c r="B21" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="138"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="119" t="s">
+      <c r="C21" s="142"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="119" t="s">
+      <c r="F21" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="119" t="s">
+      <c r="G21" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="119" t="s">
+      <c r="H21" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="120" t="s">
+      <c r="I21" s="119" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="117" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="121">
+      <c r="C22" s="120">
         <f>'Overall AC'!D36-0.05*'Overall AC'!D36</f>
         <v>0.52143447932973053</v>
       </c>
-      <c r="D22" s="121">
+      <c r="D22" s="120">
         <f>'Overall AC'!D36-0.1*'Overall AC'!D36</f>
         <v>0.4939905593650078</v>
       </c>
-      <c r="E22" s="119" t="s">
+      <c r="E22" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="F22" s="119" t="s">
+      <c r="F22" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="119" t="s">
+      <c r="G22" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="119" t="s">
+      <c r="H22" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="120" t="s">
+      <c r="I22" s="119" t="s">
         <v>188</v>
       </c>
     </row>

--- a/Design_Formulas.xlsx
+++ b/Design_Formulas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A1097411\Documents\GitHub\ORGOfly-CAD-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02002259-6CDD-402B-985A-F138DDD3CF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9597FAC8-E3BA-4239-B29C-D9DA52C8E4BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="2" r:id="rId1"/>
@@ -2177,6 +2177,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2221,42 +2257,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11936,9 +11936,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4018A4-7FF2-4E68-A485-08C5C78F0065}">
   <dimension ref="B6:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -11957,19 +11957,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A91C97-B0A7-4FD8-8682-2CCA08648534}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>53</v>
       </c>
@@ -11977,25 +11977,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="12"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
@@ -12015,8 +12015,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="139" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="55" t="s">
@@ -12034,8 +12034,8 @@
       <c r="F9" s="91"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="128"/>
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="140"/>
       <c r="B10" s="52" t="s">
         <v>52</v>
       </c>
@@ -12049,8 +12049,8 @@
       <c r="F10" s="92"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="128"/>
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="140"/>
       <c r="B11" s="52" t="s">
         <v>51</v>
       </c>
@@ -12064,8 +12064,8 @@
       <c r="F11" s="92"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="58.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="128"/>
+    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="140"/>
       <c r="B12" s="52" t="s">
         <v>20</v>
       </c>
@@ -12081,8 +12081,8 @@
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="128"/>
+    <row r="13" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="140"/>
       <c r="B13" s="53" t="s">
         <v>19</v>
       </c>
@@ -12099,8 +12099,8 @@
       </c>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="128"/>
+    <row r="14" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="140"/>
       <c r="B14" s="52" t="s">
         <v>15</v>
       </c>
@@ -12116,8 +12116,8 @@
       <c r="F14" s="92"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="128"/>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="140"/>
       <c r="B15" s="52" t="s">
         <v>16</v>
       </c>
@@ -12135,8 +12135,8 @@
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="128"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="140"/>
       <c r="B16" s="52" t="s">
         <v>5</v>
       </c>
@@ -12154,8 +12154,8 @@
       </c>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="128"/>
+    <row r="17" spans="1:7" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="140"/>
       <c r="B17" s="53" t="s">
         <v>11</v>
       </c>
@@ -12172,8 +12172,8 @@
       <c r="F17" s="92"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="128"/>
+    <row r="18" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="140"/>
       <c r="B18" s="53" t="s">
         <v>27</v>
       </c>
@@ -12190,8 +12190,8 @@
       <c r="F18" s="92"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="128"/>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="140"/>
       <c r="B19" s="52" t="s">
         <v>29</v>
       </c>
@@ -12207,8 +12207,8 @@
       </c>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="129"/>
+    <row r="20" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="141"/>
       <c r="B20" s="53" t="s">
         <v>98</v>
       </c>
@@ -12229,14 +12229,14 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" s="61"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
       <c r="F21" s="95"/>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="127" t="s">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="139" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="16"/>
@@ -12253,8 +12253,8 @@
       <c r="F22" s="91"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="128"/>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="140"/>
       <c r="B23" s="14"/>
       <c r="C23" s="66" t="s">
         <v>80</v>
@@ -12269,8 +12269,8 @@
       <c r="F23" s="92"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="129"/>
+    <row r="24" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="141"/>
       <c r="B24" s="15"/>
       <c r="C24" s="67" t="s">
         <v>81</v>
@@ -12300,18 +12300,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189935A4-45F1-46FF-93DA-944832471E2E}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>54</v>
       </c>
@@ -12319,23 +12319,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
@@ -12355,8 +12355,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="s">
+    <row r="9" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="139" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="68" t="s">
@@ -12369,13 +12369,13 @@
         <v>0.03</v>
       </c>
       <c r="E9" s="56"/>
-      <c r="F9" s="149" t="s">
+      <c r="F9" s="129" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128"/>
+    <row r="10" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="140"/>
       <c r="B10" s="69" t="s">
         <v>62</v>
       </c>
@@ -12388,13 +12388,13 @@
       <c r="E10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="150" t="s">
+      <c r="F10" s="130" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
+    <row r="11" spans="1:7" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="141"/>
       <c r="B11" s="70" t="s">
         <v>63</v>
       </c>
@@ -12408,10 +12408,10 @@
       <c r="E11" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="151"/>
+      <c r="F11" s="131"/>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
         <v>64</v>
       </c>
@@ -12425,10 +12425,10 @@
       <c r="E12" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="152"/>
+      <c r="F12" s="132"/>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="77" t="s">
         <v>60</v>
       </c>
@@ -12442,19 +12442,19 @@
       <c r="E13" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="151"/>
+      <c r="F13" s="131"/>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="61"/>
       <c r="C14" s="46"/>
       <c r="D14" s="61"/>
       <c r="E14" s="61"/>
-      <c r="F14" s="153"/>
+      <c r="F14" s="133"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="133" t="s">
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="145" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="85" t="s">
@@ -12467,13 +12467,13 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="56"/>
-      <c r="F15" s="149" t="s">
+      <c r="F15" s="129" t="s">
         <v>42</v>
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="146"/>
       <c r="B16" s="52" t="s">
         <v>58</v>
       </c>
@@ -12486,13 +12486,13 @@
       <c r="E16" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="150" t="s">
+      <c r="F16" s="130" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="134"/>
+    <row r="17" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="146"/>
       <c r="B17" s="53" t="s">
         <v>59</v>
       </c>
@@ -12506,11 +12506,11 @@
       <c r="E17" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="150"/>
+      <c r="F17" s="130"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="135"/>
+    <row r="18" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="147"/>
       <c r="B18" s="101" t="s">
         <v>195</v>
       </c>
@@ -12523,19 +12523,19 @@
       <c r="E18" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="151"/>
+      <c r="F18" s="131"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="61"/>
       <c r="C19" s="47"/>
       <c r="D19" s="80"/>
       <c r="E19" s="61"/>
-      <c r="F19" s="153"/>
+      <c r="F19" s="133"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="130" t="s">
+    <row r="20" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="142" t="s">
         <v>92</v>
       </c>
       <c r="B20" s="81" t="s">
@@ -12544,20 +12544,20 @@
       <c r="C20" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="147">
+      <c r="D20" s="127">
         <f>DEGREES(ATAN(SQRT(D11/D17)))</f>
         <v>37.886329893038969</v>
       </c>
       <c r="E20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="148" t="s">
+      <c r="F20" s="128" t="s">
         <v>199</v>
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="131"/>
+    <row r="21" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="143"/>
       <c r="B21" s="53" t="s">
         <v>56</v>
       </c>
@@ -12571,11 +12571,11 @@
       <c r="E21" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="150"/>
+      <c r="F21" s="130"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="131"/>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="143"/>
       <c r="B22" s="52" t="s">
         <v>29</v>
       </c>
@@ -12591,8 +12591,8 @@
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="131"/>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="143"/>
       <c r="B23" s="53" t="s">
         <v>66</v>
       </c>
@@ -12611,8 +12611,8 @@
       </c>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="131"/>
+    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="143"/>
       <c r="B24" s="53" t="s">
         <v>68</v>
       </c>
@@ -12626,11 +12626,11 @@
       <c r="E24" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="150"/>
+      <c r="F24" s="130"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="131"/>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="143"/>
       <c r="B25" s="52" t="s">
         <v>70</v>
       </c>
@@ -12641,13 +12641,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="57"/>
-      <c r="F25" s="150" t="s">
+      <c r="F25" s="130" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="132"/>
+    <row r="26" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="144"/>
       <c r="B26" s="84" t="s">
         <v>75</v>
       </c>
@@ -12665,15 +12665,15 @@
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
       <c r="D27" s="61"/>
       <c r="E27" s="61"/>
-      <c r="F27" s="153"/>
+      <c r="F27" s="133"/>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="130" t="s">
+    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="142" t="s">
         <v>83</v>
       </c>
       <c r="B28" s="85" t="s">
@@ -12686,13 +12686,13 @@
       <c r="E28" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="148" t="s">
+      <c r="F28" s="128" t="s">
         <v>88</v>
       </c>
       <c r="G28" s="13"/>
     </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="131"/>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="143"/>
       <c r="B29" s="52" t="s">
         <v>94</v>
       </c>
@@ -12711,8 +12711,8 @@
       </c>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="132"/>
+    <row r="30" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="144"/>
       <c r="B30" s="84"/>
       <c r="C30" s="67" t="s">
         <v>86</v>
@@ -12743,52 +12743,52 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6585412D-E6C6-4698-8307-A04D3DB6C7A6}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
       <c r="B8" s="49" t="s">
         <v>9</v>
@@ -12809,8 +12809,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="136" t="s">
+    <row r="9" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="148" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="52" t="s">
@@ -12833,8 +12833,8 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="134"/>
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="146"/>
       <c r="B10" s="52" t="s">
         <v>102</v>
       </c>
@@ -12855,8 +12855,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="134"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="146"/>
       <c r="B11" s="53" t="s">
         <v>104</v>
       </c>
@@ -12873,8 +12873,8 @@
       <c r="F11" s="92"/>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="134"/>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="146"/>
       <c r="B12" s="52" t="s">
         <v>108</v>
       </c>
@@ -12892,8 +12892,8 @@
       </c>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="135"/>
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="147"/>
       <c r="B13" s="54" t="s">
         <v>192</v>
       </c>
@@ -12923,18 +12923,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1379866-2160-4925-834D-A41ED5331C38}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="41.5546875" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>111</v>
       </c>
@@ -12943,34 +12943,34 @@
       </c>
       <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22"/>
       <c r="B8" s="23" t="s">
         <v>9</v>
@@ -12991,8 +12991,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="137" t="s">
+    <row r="9" spans="1:7" ht="85.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="149" t="s">
         <v>109</v>
       </c>
       <c r="B9" s="86"/>
@@ -13009,8 +13009,8 @@
       <c r="F9" s="96"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="138"/>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="150"/>
       <c r="B10" s="87"/>
       <c r="C10" s="66" t="s">
         <v>113</v>
@@ -13025,8 +13025,8 @@
       <c r="F10" s="92"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="138"/>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="150"/>
       <c r="B11" s="87"/>
       <c r="C11" s="66" t="s">
         <v>117</v>
@@ -13045,8 +13045,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="138"/>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="150"/>
       <c r="B12" s="87"/>
       <c r="C12" s="66" t="s">
         <v>110</v>
@@ -13060,8 +13060,8 @@
       </c>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="138"/>
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="150"/>
       <c r="B13" s="88" t="s">
         <v>125</v>
       </c>
@@ -13080,8 +13080,8 @@
       </c>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="138"/>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="150"/>
       <c r="B14" s="87" t="s">
         <v>124</v>
       </c>
@@ -13100,8 +13100,8 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="139"/>
+    <row r="15" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="151"/>
       <c r="B15" s="70" t="s">
         <v>118</v>
       </c>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="61"/>
       <c r="C16" s="46"/>
       <c r="D16" s="61"/>
@@ -13128,8 +13128,8 @@
       <c r="F16" s="95"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="137" t="s">
+    <row r="17" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="149" t="s">
         <v>130</v>
       </c>
       <c r="B17" s="86"/>
@@ -13146,8 +13146,8 @@
       <c r="F17" s="96"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="138"/>
+    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="150"/>
       <c r="B18" s="87" t="s">
         <v>132</v>
       </c>
@@ -13166,8 +13166,8 @@
       </c>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="138"/>
+    <row r="19" spans="1:7" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="150"/>
       <c r="B19" s="87"/>
       <c r="C19" s="66" t="s">
         <v>135</v>
@@ -13182,8 +13182,8 @@
       <c r="F19" s="92"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="138"/>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="150"/>
       <c r="B20" s="87"/>
       <c r="C20" s="66" t="s">
         <v>139</v>
@@ -13199,8 +13199,8 @@
       </c>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="138"/>
+    <row r="21" spans="1:7" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="150"/>
       <c r="B21" s="87"/>
       <c r="C21" s="66" t="s">
         <v>140</v>
@@ -13214,8 +13214,8 @@
       </c>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="138"/>
+    <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="150"/>
       <c r="B22" s="87"/>
       <c r="C22" s="66" t="s">
         <v>141</v>
@@ -13230,8 +13230,8 @@
       <c r="F22" s="92"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="138"/>
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="150"/>
       <c r="B23" s="87"/>
       <c r="C23" s="66" t="s">
         <v>136</v>
@@ -13250,8 +13250,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="138"/>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="150"/>
       <c r="B24" s="87"/>
       <c r="C24" s="66" t="s">
         <v>110</v>
@@ -13265,8 +13265,8 @@
       </c>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="138"/>
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="150"/>
       <c r="B25" s="88" t="s">
         <v>125</v>
       </c>
@@ -13285,8 +13285,8 @@
       </c>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="138"/>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="150"/>
       <c r="B26" s="87" t="s">
         <v>124</v>
       </c>
@@ -13305,8 +13305,8 @@
       </c>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="139"/>
+    <row r="27" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="151"/>
       <c r="B27" s="70" t="s">
         <v>118</v>
       </c>
@@ -13325,15 +13325,15 @@
       </c>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
       <c r="D28" s="61"/>
       <c r="E28" s="61"/>
       <c r="F28" s="95"/>
     </row>
-    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="137" t="s">
+    <row r="29" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="149" t="s">
         <v>143</v>
       </c>
       <c r="B29" s="86"/>
@@ -13350,8 +13350,8 @@
       <c r="F29" s="91"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.3">
-      <c r="A30" s="138"/>
+    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A30" s="150"/>
       <c r="B30" s="87" t="s">
         <v>145</v>
       </c>
@@ -13369,8 +13369,8 @@
       </c>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="138"/>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="150"/>
       <c r="B31" s="87" t="s">
         <v>146</v>
       </c>
@@ -13389,8 +13389,8 @@
       </c>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="138"/>
+    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="150"/>
       <c r="B32" s="87" t="s">
         <v>149</v>
       </c>
@@ -13405,8 +13405,8 @@
       <c r="F32" s="92"/>
       <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="139"/>
+    <row r="33" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="151"/>
       <c r="B33" s="70" t="s">
         <v>150</v>
       </c>
@@ -13423,15 +13423,15 @@
       <c r="F33" s="97"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="61"/>
       <c r="C34" s="61"/>
       <c r="D34" s="61"/>
       <c r="E34" s="61"/>
       <c r="F34" s="95"/>
     </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="140" t="s">
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="152" t="s">
         <v>154</v>
       </c>
       <c r="B35" s="86"/>
@@ -13448,8 +13448,8 @@
       <c r="F35" s="91"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="141"/>
+    <row r="36" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="153"/>
       <c r="B36" s="70" t="s">
         <v>155</v>
       </c>
@@ -13483,26 +13483,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F858FC13-65B8-4ADF-8133-431E42F1A0C9}">
   <dimension ref="B1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="34" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1" s="42"/>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="43"/>
     </row>
-    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="27"/>
       <c r="C4" s="30" t="s">
         <v>175</v>
@@ -13529,7 +13529,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
         <v>159</v>
       </c>
@@ -13552,7 +13552,7 @@
       <c r="I5" s="123"/>
       <c r="J5" s="125"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
         <v>160</v>
       </c>
@@ -13563,10 +13563,10 @@
       <c r="E6" s="40">
         <v>53.2</v>
       </c>
-      <c r="F6" s="142" t="s">
+      <c r="F6" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="143"/>
+      <c r="G6" s="135"/>
       <c r="H6" s="32">
         <v>4</v>
       </c>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J6" s="33"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="29" t="s">
         <v>161</v>
       </c>
@@ -13583,18 +13583,18 @@
         <v>180</v>
       </c>
       <c r="D7" s="45"/>
-      <c r="E7" s="144" t="s">
+      <c r="E7" s="136" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="145"/>
-      <c r="G7" s="143"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="135"/>
       <c r="H7" s="32">
         <v>4</v>
       </c>
       <c r="I7" s="41"/>
       <c r="J7" s="33"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
         <v>162</v>
       </c>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="J8" s="33"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="121" t="s">
         <v>197</v>
       </c>
@@ -13642,7 +13642,7 @@
       <c r="I9" s="41"/>
       <c r="J9" s="33"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="121" t="s">
         <v>196</v>
       </c>
@@ -13665,7 +13665,7 @@
       <c r="I10" s="41"/>
       <c r="J10" s="33"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="29" t="s">
         <v>163</v>
       </c>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="J11" s="33"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="29" t="s">
         <v>164</v>
       </c>
@@ -13707,7 +13707,7 @@
       <c r="I12" s="41"/>
       <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="29" t="s">
         <v>165</v>
       </c>
@@ -13724,7 +13724,7 @@
       <c r="I13" s="41"/>
       <c r="J13" s="33"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="29" t="s">
         <v>184</v>
       </c>
@@ -13741,7 +13741,7 @@
       <c r="I14" s="41"/>
       <c r="J14" s="33"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="29" t="s">
         <v>185</v>
       </c>
@@ -13758,7 +13758,7 @@
       <c r="I15" s="41"/>
       <c r="J15" s="33"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="29" t="s">
         <v>186</v>
       </c>
@@ -13775,7 +13775,7 @@
       <c r="I16" s="41"/>
       <c r="J16" s="33"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="29" t="s">
         <v>166</v>
       </c>
@@ -13792,7 +13792,7 @@
       <c r="I17" s="41"/>
       <c r="J17" s="33"/>
     </row>
-    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="102" t="s">
         <v>182</v>
       </c>
@@ -13809,7 +13809,7 @@
       <c r="I18" s="124"/>
       <c r="J18" s="126"/>
     </row>
-    <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="109" t="s">
         <v>187</v>
       </c>
@@ -13827,16 +13827,16 @@
       <c r="I19" s="115"/>
       <c r="J19" s="27"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="12"/>
       <c r="I20" s="116"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="142"/>
-      <c r="D21" s="146"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="138"/>
       <c r="E21" s="118" t="s">
         <v>122</v>
       </c>
@@ -13853,7 +13853,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="117" t="s">
         <v>168</v>
       </c>
